--- a/FOA SETS/Dining-Set.xlsx
+++ b/FOA SETS/Dining-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD372"/>
+  <dimension ref="A1:AG372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,6 +741,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -871,7 +886,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ADALIA</t>
+          <t>Dining, Dining Set, ADALIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1032,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ADELINA</t>
+          <t>Dining, Dining Set, ADELINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1178,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ADELINA</t>
+          <t>Dining, Dining Set, ADELINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1321,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALENA</t>
+          <t>Dining, Dining Set, ALENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1464,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALENA</t>
+          <t>Dining, Dining Set, ALENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1607,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALESSIA</t>
+          <t>Dining, Dining Set, ALESSIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1756,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1900,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1909,7 +2044,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2188,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2332,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2480,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2623,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2766,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALFRED</t>
+          <t>Dining, Dining Set, ALFRED, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2909,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALISHA</t>
+          <t>Dining, Dining Set, ALISHA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2785,7 +3025,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALNWICK</t>
+          <t>Dining, Dining Set, ALNWICK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2918,7 +3173,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALPENA</t>
+          <t>Dining, Dining Set, ALPENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3322,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALPENA</t>
+          <t>Dining, Dining Set, ALPENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3470,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALPENA</t>
+          <t>Dining, Dining Set, ALPENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3619,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ALPENA</t>
+          <t>Dining, Dining Set, ALPENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3758,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3906,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3708,7 +4053,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3840,7 +4200,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3973,7 +4348,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4495,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AMINA</t>
+          <t>Dining, Dining Set, AMINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4639,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ANTON</t>
+          <t>Dining, Dining Set, ANTON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4789,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4938,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4639,7 +5089,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4774,7 +5239,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4905,7 +5385,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5535,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5679,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5818,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ARCADIA</t>
+          <t>Dining, Dining Set, ARCADIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5966,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AULETTA</t>
+          <t>Dining, Dining Set, AULETTA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5564,7 +6119,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AULETTA</t>
+          <t>Dining, Dining Set, AULETTA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5698,7 +6268,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AULETTA</t>
+          <t>Dining, Dining Set, AULETTA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5836,7 +6421,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, AULETTA</t>
+          <t>Dining, Dining Set, AULETTA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6568,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BARBARY</t>
+          <t>Dining, Dining Set, BARBARY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6714,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BARBARY</t>
+          <t>Dining, Dining Set, BARBARY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6860,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BASILICATA</t>
+          <t>Dining, Dining Set, BASILICATA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6361,7 +7006,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BASILICATA</t>
+          <t>Dining, Dining Set, BASILICATA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6492,7 +7152,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BASILICATA</t>
+          <t>Dining, Dining Set, BASILICATA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6623,7 +7298,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BASILICATA</t>
+          <t>Dining, Dining Set, BASILICATA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6755,7 +7445,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BEALE</t>
+          <t>Dining, Dining Set, BEALE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6887,7 +7592,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BEALE</t>
+          <t>Dining, Dining Set, BEALE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7741,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7890,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7289,7 +8039,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7423,7 +8188,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7551,7 +8331,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7679,7 +8474,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7807,7 +8617,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7935,7 +8760,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BELLAGIO</t>
+          <t>Dining, Dining Set, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8909,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BINGHAM</t>
+          <t>Dining, Dining Set, BINGHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8198,7 +9053,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BRENT</t>
+          <t>Dining, Dining Set, BRENT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8328,7 +9198,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BRENT II</t>
+          <t>Dining, Dining Set, BRENT II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8458,7 +9343,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BRENT II</t>
+          <t>Dining, Dining Set, BRENT II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8591,7 +9491,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8724,7 +9639,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8857,7 +9787,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8990,7 +9935,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9120,7 +10080,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9250,7 +10225,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BROAGER</t>
+          <t>Dining, Dining Set, BROAGER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9385,7 +10375,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BRULE</t>
+          <t>Dining, Dining Set, BRULE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9520,7 +10525,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, BRULE</t>
+          <t>Dining, Dining Set, BRULE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9652,7 +10672,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CALABRIA</t>
+          <t>Dining, Dining Set, CALABRIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9785,7 +10820,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CANYONVILLE</t>
+          <t>Dining, Dining Set, CANYONVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9912,7 +10962,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CANYONVILLE</t>
+          <t>Dining, Dining Set, CANYONVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10038,7 +11103,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CARLISLE</t>
+          <t>Dining, Dining Set, CARLISLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10172,7 +11252,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CASPER</t>
+          <t>Dining, Dining Set, CASPER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10305,7 +11400,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CASPER</t>
+          <t>Dining, Dining Set, CASPER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10434,7 +11544,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CATHALINA</t>
+          <t>Dining, Dining Set, CATHALINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10563,7 +11688,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CILEGON</t>
+          <t>Dining, Dining Set, CILEGON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10690,7 +11830,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, CIMMA</t>
+          <t>Dining, Dining Set, CIMMA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10821,7 +11976,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DANIELLA</t>
+          <t>Dining, Dining Set, DANIELLA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10948,7 +12118,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DICKINSON I</t>
+          <t>Dining, Dining Set, DICKINSON I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11075,7 +12260,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DICKINSON I</t>
+          <t>Dining, Dining Set, DICKINSON I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11202,7 +12402,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DICKINSON II</t>
+          <t>Dining, Dining Set, DICKINSON II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11329,7 +12544,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DICKINSON II</t>
+          <t>Dining, Dining Set, DICKINSON II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11460,7 +12690,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DIOCLES</t>
+          <t>Dining, Dining Set, DIOCLES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11590,7 +12835,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DIOCLES</t>
+          <t>Dining, Dining Set, DIOCLES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11723,7 +12983,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DULCE</t>
+          <t>Dining, Dining Set, DULCE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11855,7 +13130,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, DULCE</t>
+          <t>Dining, Dining Set, DULCE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11983,7 +13273,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EASINGWOLD</t>
+          <t>Dining, Dining Set, EASINGWOLD, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12115,7 +13420,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EBIKON</t>
+          <t>Dining, Dining Set, EBIKON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12217,7 +13537,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EBIKON</t>
+          <t>Dining, Dining Set, EBIKON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12343,7 +13678,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EBIKON</t>
+          <t>Dining, Dining Set, EBIKON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12471,7 +13821,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDENBRIDGE</t>
+          <t>Dining, Dining Set, EDENBRIDGE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12600,7 +13965,22 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDENBRIDGE</t>
+          <t>Dining, Dining Set, EDENBRIDGE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12728,7 +14108,22 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDENBRIDGE</t>
+          <t>Dining, Dining Set, EDENBRIDGE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12856,7 +14251,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDGEWOOD I</t>
+          <t>Dining, Dining Set, EDGEWOOD I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12984,7 +14394,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDGEWOOD I</t>
+          <t>Dining, Dining Set, EDGEWOOD I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13112,7 +14537,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDGEWOOD II</t>
+          <t>Dining, Dining Set, EDGEWOOD II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13240,7 +14680,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EDGEWOOD II</t>
+          <t>Dining, Dining Set, EDGEWOOD II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13370,7 +14825,22 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELANA</t>
+          <t>Dining, Dining Set, ELANA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13499,7 +14969,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELANA</t>
+          <t>Dining, Dining Set, ELANA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13628,7 +15113,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELANA</t>
+          <t>Dining, Dining Set, ELANA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13764,7 +15264,22 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELFREDO</t>
+          <t>Dining, Dining Set, ELFREDO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13900,7 +15415,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELFREDO</t>
+          <t>Dining, Dining Set, ELFREDO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14036,7 +15566,22 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELFREDO</t>
+          <t>Dining, Dining Set, ELFREDO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14165,7 +15710,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELLESMERE</t>
+          <t>Dining, Dining Set, ELLESMERE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14294,7 +15854,22 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ELLESMERE</t>
+          <t>Dining, Dining Set, ELLESMERE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14421,7 +15996,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ESSEN</t>
+          <t>Dining, Dining Set, ESSEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14549,7 +16139,22 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EVA</t>
+          <t>Dining, Dining Set, EVA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14679,7 +16284,22 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, EVANGELINE</t>
+          <t>Dining, Dining Set, EVANGELINE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14809,7 +16429,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, FAULK</t>
+          <t>Dining, Dining Set, FAULK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14938,7 +16573,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, FAULK</t>
+          <t>Dining, Dining Set, FAULK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15068,7 +16718,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, FERRONE</t>
+          <t>Dining, Dining Set, FERRONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15197,7 +16862,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, FOSKEY</t>
+          <t>Dining, Dining Set, FOSKEY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15330,7 +17010,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, FREDONIA</t>
+          <t>Dining, Dining Set, FREDONIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15459,7 +17154,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GEORGETOWN</t>
+          <t>Dining, Dining Set, GEORGETOWN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15590,7 +17300,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GEORGIA</t>
+          <t>Dining, Dining Set, GEORGIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15720,7 +17445,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GEORGIA</t>
+          <t>Dining, Dining Set, GEORGIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15857,7 +17597,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15994,7 +17749,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16130,7 +17900,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16266,7 +18051,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16403,7 +18203,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16540,7 +18355,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16671,7 +18501,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16803,7 +18648,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GIANNA</t>
+          <t>Dining, Dining Set, GIANNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16931,7 +18791,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLADSTONE</t>
+          <t>Dining, Dining Set, GLADSTONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17059,7 +18934,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLADSTONE</t>
+          <t>Dining, Dining Set, GLADSTONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17187,7 +19077,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLADSTONE</t>
+          <t>Dining, Dining Set, GLADSTONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17317,7 +19222,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLENBROOK</t>
+          <t>Dining, Dining Set, GLENBROOK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17449,7 +19369,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLENVIEW</t>
+          <t>Dining, Dining Set, GLENVIEW, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17583,7 +19518,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLENVIEW</t>
+          <t>Dining, Dining Set, GLENVIEW, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17716,7 +19666,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GLENVIEW</t>
+          <t>Dining, Dining Set, GLENVIEW, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17843,7 +19808,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GOSPORT</t>
+          <t>Dining, Dining Set, GOSPORT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17969,7 +19949,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRASTEN</t>
+          <t>Dining, Dining Set, GRASTEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18096,7 +20091,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRASTEN</t>
+          <t>Dining, Dining Set, GRASTEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18222,7 +20232,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRASTEN</t>
+          <t>Dining, Dining Set, GRASTEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18352,7 +20377,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRASTEN</t>
+          <t>Dining, Dining Set, GRASTEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18482,7 +20522,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRASTEN</t>
+          <t>Dining, Dining Set, GRASTEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18610,7 +20665,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRISTALT</t>
+          <t>Dining, Dining Set, GRISTALT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18732,7 +20802,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GRISTALT</t>
+          <t>Dining, Dining Set, GRISTALT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18860,7 +20945,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, GUISBOROUGH</t>
+          <t>Dining, Dining Set, GUISBOROUGH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18993,7 +21093,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HAGERMAN</t>
+          <t>Dining, Dining Set, HAGERMAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19125,7 +21240,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HAGERMAN</t>
+          <t>Dining, Dining Set, HAGERMAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19253,7 +21383,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HALEIGH</t>
+          <t>Dining, Dining Set, HALEIGH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19386,7 +21531,22 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HALSEY</t>
+          <t>Dining, Dining Set, HALSEY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19519,7 +21679,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HANNORIA</t>
+          <t>Dining, Dining Set, HANNORIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19652,7 +21827,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HANNORIA</t>
+          <t>Dining, Dining Set, HANNORIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19783,7 +21973,22 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HARRISBURG</t>
+          <t>Dining, Dining Set, HARRISBURG, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19914,7 +22119,22 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HARRISBURG</t>
+          <t>Dining, Dining Set, HARRISBURG, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20045,7 +22265,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HEIDELBERG</t>
+          <t>Dining, Dining Set, HEIDELBERG, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20143,7 +22378,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HEPBURNE</t>
+          <t>Dining, Dining Set, HEPBURNE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20282,7 +22532,22 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINES</t>
+          <t>Dining, Dining Set, HINES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20427,7 +22692,22 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINES</t>
+          <t>Dining, Dining Set, HINES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20559,7 +22839,22 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINWITZ</t>
+          <t>Dining, Dining Set, HINWITZ, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20691,7 +22986,22 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINWITZ</t>
+          <t>Dining, Dining Set, HINWITZ, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20823,7 +23133,22 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINWITZ</t>
+          <t>Dining, Dining Set, HINWITZ, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20955,7 +23280,22 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HINWITZ</t>
+          <t>Dining, Dining Set, HINWITZ, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21084,7 +23424,22 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HOLCROFT</t>
+          <t>Dining, Dining Set, HOLCROFT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21213,7 +23568,22 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HOLCROFT</t>
+          <t>Dining, Dining Set, HOLCROFT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21340,7 +23710,22 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HOLSWORTHY</t>
+          <t>Dining, Dining Set, HOLSWORTHY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21467,7 +23852,22 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HOLSWORTHY</t>
+          <t>Dining, Dining Set, HOLSWORTHY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21595,7 +23995,22 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HURLEY</t>
+          <t>Dining, Dining Set, HURLEY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21722,7 +24137,22 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, HURLEY</t>
+          <t>Dining, Dining Set, HURLEY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21850,7 +24280,22 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, IZZY</t>
+          <t>Dining, Dining Set, IZZY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21978,7 +24423,22 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, IZZY</t>
+          <t>Dining, Dining Set, IZZY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22108,7 +24568,22 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, JASMIN</t>
+          <t>Dining, Dining Set, JASMIN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22238,7 +24713,22 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, JULIA</t>
+          <t>Dining, Dining Set, JULIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22368,7 +24858,22 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, JULIA</t>
+          <t>Dining, Dining Set, JULIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22498,7 +25003,22 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, JULIA</t>
+          <t>Dining, Dining Set, JULIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22631,7 +25151,22 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KALAWAO</t>
+          <t>Dining, Dining Set, KALAWAO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22764,7 +25299,22 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KALAWAO</t>
+          <t>Dining, Dining Set, KALAWAO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -22899,7 +25449,22 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KATHRYN</t>
+          <t>Dining, Dining Set, KATHRYN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23033,7 +25598,22 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KATHRYN</t>
+          <t>Dining, Dining Set, KATHRYN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23164,7 +25744,22 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KENYADA</t>
+          <t>Dining, Dining Set, KENYADA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23293,7 +25888,22 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KEYNES</t>
+          <t>Dining, Dining Set, KEYNES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23421,7 +26031,22 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KIAN</t>
+          <t>Dining, Dining Set, KIAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23549,7 +26174,22 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KIAN I</t>
+          <t>Dining, Dining Set, KIAN I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23677,7 +26317,22 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KIAN I</t>
+          <t>Dining, Dining Set, KIAN I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23797,7 +26452,22 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KIAN II</t>
+          <t>Dining, Dining Set, KIAN II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -23929,7 +26599,22 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KONA I</t>
+          <t>Dining, Dining Set, KONA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24061,7 +26746,22 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, KONA I</t>
+          <t>Dining, Dining Set, KONA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24194,7 +26894,22 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LAQUILA</t>
+          <t>Dining, Dining Set, LAQUILA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24326,7 +27041,22 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LAQUILA</t>
+          <t>Dining, Dining Set, LAQUILA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24459,7 +27189,22 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LENVIK</t>
+          <t>Dining, Dining Set, LENVIK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24592,7 +27337,22 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LENVIK</t>
+          <t>Dining, Dining Set, LENVIK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24718,7 +27478,22 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LEOVANNI</t>
+          <t>Dining, Dining Set, LEOVANNI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24851,7 +27626,22 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LEOVANNI</t>
+          <t>Dining, Dining Set, LEOVANNI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -24981,7 +27771,22 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA I</t>
+          <t>Dining, Dining Set, LODIA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25111,7 +27916,22 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA I</t>
+          <t>Dining, Dining Set, LODIA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25241,7 +28061,22 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA I</t>
+          <t>Dining, Dining Set, LODIA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25371,7 +28206,22 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA I</t>
+          <t>Dining, Dining Set, LODIA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25499,7 +28349,22 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA II</t>
+          <t>Dining, Dining Set, LODIA II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25627,7 +28492,22 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LODIA II</t>
+          <t>Dining, Dining Set, LODIA II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25759,7 +28639,22 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LOMBARDY</t>
+          <t>Dining, Dining Set, LOMBARDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -25885,7 +28780,22 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LOMBARDY</t>
+          <t>Dining, Dining Set, LOMBARDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26015,7 +28925,22 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LOSONE</t>
+          <t>Dining, Dining Set, LOSONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26144,7 +29069,22 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LOSONE</t>
+          <t>Dining, Dining Set, LOSONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26272,7 +29212,22 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LUMINAR</t>
+          <t>Dining, Dining Set, LUMINAR, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26401,7 +29356,22 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LUMINAR II</t>
+          <t>Dining, Dining Set, LUMINAR II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26530,7 +29500,22 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, LUMINAR II</t>
+          <t>Dining, Dining Set, LUMINAR II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26661,7 +29646,22 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MANHATTAN</t>
+          <t>Dining, Dining Set, MANHATTAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26792,7 +29792,22 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MANHATTAN</t>
+          <t>Dining, Dining Set, MANHATTAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -26918,7 +29933,22 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MANHATTAN III</t>
+          <t>Dining, Dining Set, MANHATTAN III, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27047,7 +30077,22 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MARINA I</t>
+          <t>Dining, Dining Set, MARINA I, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27173,7 +30218,22 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MARINA II</t>
+          <t>Dining, Dining Set, MARINA II, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27306,7 +30366,22 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MAUNA</t>
+          <t>Dining, Dining Set, MAUNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27439,7 +30514,22 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MAUNA</t>
+          <t>Dining, Dining Set, MAUNA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27569,7 +30659,22 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MAYVILLE</t>
+          <t>Dining, Dining Set, MAYVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27699,7 +30804,22 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MAYVILLE</t>
+          <t>Dining, Dining Set, MAYVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27831,7 +30951,22 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MELINA</t>
+          <t>Dining, Dining Set, MELINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -27963,7 +31098,22 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MELINA</t>
+          <t>Dining, Dining Set, MELINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28096,7 +31246,22 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MIDVALE</t>
+          <t>Dining, Dining Set, MIDVALE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28231,7 +31396,22 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MIDVALE</t>
+          <t>Dining, Dining Set, MIDVALE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28362,7 +31542,22 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MODOC</t>
+          <t>Dining, Dining Set, MODOC, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28490,7 +31685,22 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MONCLOVA</t>
+          <t>Dining, Dining Set, MONCLOVA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28623,7 +31833,22 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MORGES</t>
+          <t>Dining, Dining Set, MORGES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28756,7 +31981,22 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MORGES</t>
+          <t>Dining, Dining Set, MORGES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28889,7 +32129,22 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, MORGES</t>
+          <t>Dining, Dining Set, MORGES, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29015,7 +32270,22 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NARVIK</t>
+          <t>Dining, Dining Set, NARVIK, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29117,7 +32387,22 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEASDEN</t>
+          <t>Dining, Dining Set, NEASDEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29250,7 +32535,22 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NERISSA</t>
+          <t>Dining, Dining Set, NERISSA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29383,7 +32683,22 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NERISSA</t>
+          <t>Dining, Dining Set, NERISSA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29516,7 +32831,22 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NERISSA</t>
+          <t>Dining, Dining Set, NERISSA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29650,7 +32980,22 @@
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NERISSA</t>
+          <t>Dining, Dining Set, NERISSA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29785,7 +33130,22 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29925,7 +33285,22 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30060,7 +33435,22 @@
       </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30195,7 +33585,22 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30335,7 +33740,22 @@
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30470,7 +33890,22 @@
       </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEUVEVILLE</t>
+          <t>Dining, Dining Set, NEUVEVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30600,7 +34035,22 @@
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NEWCASTLE</t>
+          <t>Dining, Dining Set, NEWCASTLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30733,7 +34183,22 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORELLI</t>
+          <t>Dining, Dining Set, NORELLI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30866,7 +34331,22 @@
       </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORELLI</t>
+          <t>Dining, Dining Set, NORELLI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -30998,7 +34478,22 @@
       </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORMANDY</t>
+          <t>Dining, Dining Set, NORMANDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31124,7 +34619,22 @@
       </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORMANDY</t>
+          <t>Dining, Dining Set, NORMANDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31225,7 +34735,22 @@
       </c>
       <c r="AD235" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHAM</t>
+          <t>Dining, Dining Set, NORTHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31326,7 +34851,22 @@
       </c>
       <c r="AD236" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHAM</t>
+          <t>Dining, Dining Set, NORTHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31427,7 +34967,22 @@
       </c>
       <c r="AD237" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHOLT</t>
+          <t>Dining, Dining Set, NORTHOLT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31528,7 +35083,22 @@
       </c>
       <c r="AD238" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHOLT</t>
+          <t>Dining, Dining Set, NORTHOLT, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31629,7 +35199,22 @@
       </c>
       <c r="AD239" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHWICH</t>
+          <t>Dining, Dining Set, NORTHWICH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31730,7 +35315,22 @@
       </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NORTHWICH</t>
+          <t>Dining, Dining Set, NORTHWICH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31864,7 +35464,22 @@
       </c>
       <c r="AD241" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NOUVELLE</t>
+          <t>Dining, Dining Set, NOUVELLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -31993,7 +35608,22 @@
       </c>
       <c r="AD242" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, NOVA</t>
+          <t>Dining, Dining Set, NOVA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32124,7 +35754,22 @@
       </c>
       <c r="AD243" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, OAKHAM</t>
+          <t>Dining, Dining Set, OAKHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32255,7 +35900,22 @@
       </c>
       <c r="AD244" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, OAKHAM</t>
+          <t>Dining, Dining Set, OAKHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32387,7 +36047,22 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, OBERWIL</t>
+          <t>Dining, Dining Set, OBERWIL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32513,7 +36188,22 @@
       </c>
       <c r="AD246" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ORBETELLO</t>
+          <t>Dining, Dining Set, ORBETELLO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32637,7 +36327,22 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ORBETELLO</t>
+          <t>Dining, Dining Set, ORBETELLO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32763,7 +36468,22 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ORBETELLO</t>
+          <t>Dining, Dining Set, ORBETELLO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -32890,7 +36610,22 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ORBETELLO</t>
+          <t>Dining, Dining Set, ORBETELLO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33020,7 +36755,22 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ORLA</t>
+          <t>Dining, Dining Set, ORLA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33151,7 +36901,22 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33282,7 +37047,22 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33413,7 +37193,22 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33544,7 +37339,22 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33675,7 +37485,22 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33805,7 +37630,22 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PALAZZO</t>
+          <t>Dining, Dining Set, PALAZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33935,7 +37775,22 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PATIENCE</t>
+          <t>Dining, Dining Set, PATIENCE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34065,7 +37920,22 @@
       </c>
       <c r="AD258" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PATIENCE</t>
+          <t>Dining, Dining Set, PATIENCE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34194,7 +38064,22 @@
       </c>
       <c r="AD259" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PENDOLA</t>
+          <t>Dining, Dining Set, PENDOLA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34328,7 +38213,22 @@
       </c>
       <c r="AD260" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PICARDY</t>
+          <t>Dining, Dining Set, PICARDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34456,7 +38356,22 @@
       </c>
       <c r="AD261" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PICARDY</t>
+          <t>Dining, Dining Set, PICARDY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34589,7 +38504,22 @@
       </c>
       <c r="AD262" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PORTANOVA</t>
+          <t>Dining, Dining Set, PORTANOVA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34722,7 +38652,22 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PORTANOVA</t>
+          <t>Dining, Dining Set, PORTANOVA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34849,7 +38794,22 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, POTTON</t>
+          <t>Dining, Dining Set, POTTON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34981,7 +38941,22 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PROMENADE</t>
+          <t>Dining, Dining Set, PROMENADE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35113,7 +39088,22 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, PROMENADE</t>
+          <t>Dining, Dining Set, PROMENADE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35244,7 +39234,22 @@
       </c>
       <c r="AD267" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RAPIDVIEW</t>
+          <t>Dining, Dining Set, RAPIDVIEW, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35374,7 +39379,22 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RAPIDVIEW</t>
+          <t>Dining, Dining Set, RAPIDVIEW, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35476,7 +39496,22 @@
       </c>
       <c r="AD269" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RHEINFALL</t>
+          <t>Dining, Dining Set, RHEINFALL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35578,7 +39613,22 @@
       </c>
       <c r="AD270" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RHEINFALL</t>
+          <t>Dining, Dining Set, RHEINFALL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35712,7 +39762,22 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RICHFIELD</t>
+          <t>Dining, Dining Set, RICHFIELD, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35846,7 +39911,22 @@
       </c>
       <c r="AD272" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RICHFIELD</t>
+          <t>Dining, Dining Set, RICHFIELD, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35982,7 +40062,22 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RICHFIELD</t>
+          <t>Dining, Dining Set, RICHFIELD, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36117,7 +40212,22 @@
       </c>
       <c r="AD274" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, RICHFIELD</t>
+          <t>Dining, Dining Set, RICHFIELD, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36244,7 +40354,22 @@
       </c>
       <c r="AD275" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ROWAN</t>
+          <t>Dining, Dining Set, ROWAN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36374,7 +40499,22 @@
       </c>
       <c r="AD276" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ROXO</t>
+          <t>Dining, Dining Set, ROXO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36501,7 +40641,22 @@
       </c>
       <c r="AD277" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRINA</t>
+          <t>Dining, Dining Set, SABRINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36628,7 +40783,22 @@
       </c>
       <c r="AD278" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRINA</t>
+          <t>Dining, Dining Set, SABRINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36755,7 +40925,22 @@
       </c>
       <c r="AD279" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRINA</t>
+          <t>Dining, Dining Set, SABRINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36882,7 +41067,22 @@
       </c>
       <c r="AD280" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRINA</t>
+          <t>Dining, Dining Set, SABRINA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37010,7 +41210,22 @@
       </c>
       <c r="AD281" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37138,7 +41353,22 @@
       </c>
       <c r="AD282" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37266,7 +41496,22 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37394,7 +41639,22 @@
       </c>
       <c r="AD284" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37522,7 +41782,22 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37650,7 +41925,22 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37778,7 +42068,22 @@
       </c>
       <c r="AD287" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SABRO</t>
+          <t>Dining, Dining Set, SABRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37908,7 +42213,22 @@
       </c>
       <c r="AD288" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SAN ANTONIO</t>
+          <t>Dining, Dining Set, SAN ANTONIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38042,7 +42362,22 @@
       </c>
       <c r="AD289" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38180,7 +42515,22 @@
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38316,7 +42666,22 @@
       </c>
       <c r="AD291" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38453,7 +42818,22 @@
       </c>
       <c r="AD292" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38588,7 +42968,22 @@
       </c>
       <c r="AD293" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38725,7 +43120,22 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38856,7 +43266,22 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38991,7 +43416,22 @@
       </c>
       <c r="AD296" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39126,7 +43566,22 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39261,7 +43716,22 @@
       </c>
       <c r="AD298" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39396,7 +43866,22 @@
       </c>
       <c r="AD299" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39531,7 +44016,22 @@
       </c>
       <c r="AD300" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39666,7 +44166,22 @@
       </c>
       <c r="AD301" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39801,7 +44316,22 @@
       </c>
       <c r="AD302" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39936,7 +44466,22 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40071,7 +44616,22 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40206,7 +44766,22 @@
       </c>
       <c r="AD305" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40337,7 +44912,22 @@
       </c>
       <c r="AD306" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA III</t>
+          <t>Dining, Dining Set, SANIA III, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40468,7 +45058,22 @@
       </c>
       <c r="AD307" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SANIA</t>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40597,7 +45202,22 @@
       </c>
       <c r="AD308" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SASKIA</t>
+          <t>Dining, Dining Set, SASKIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40700,7 +45320,22 @@
       </c>
       <c r="AD309" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SILVERIA</t>
+          <t>Dining, Dining Set, SILVERIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40803,7 +45438,22 @@
       </c>
       <c r="AD310" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SILVERIA</t>
+          <t>Dining, Dining Set, SILVERIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -40907,7 +45557,22 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SILVESTRI</t>
+          <t>Dining, Dining Set, SILVESTRI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41011,7 +45676,22 @@
       </c>
       <c r="AD312" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SILVESTRI</t>
+          <t>Dining, Dining Set, SILVESTRI, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41139,7 +45819,22 @@
       </c>
       <c r="AD313" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SKIEN</t>
+          <t>Dining, Dining Set, SKIEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41268,7 +45963,22 @@
       </c>
       <c r="AD314" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ST GALLEN</t>
+          <t>Dining, Dining Set, ST GALLEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41402,7 +46112,22 @@
       </c>
       <c r="AD315" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STACIE</t>
+          <t>Dining, Dining Set, STACIE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41537,7 +46262,22 @@
       </c>
       <c r="AD316" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STACIE</t>
+          <t>Dining, Dining Set, STACIE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41666,7 +46406,22 @@
       </c>
       <c r="AD317" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STACIE</t>
+          <t>Dining, Dining Set, STACIE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41796,7 +46551,22 @@
       </c>
       <c r="AD318" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STACIE</t>
+          <t>Dining, Dining Set, STACIE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -41923,7 +46693,22 @@
       </c>
       <c r="AD319" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STELLA MIA</t>
+          <t>Dining, Dining Set, STELLA MIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42054,7 +46839,22 @@
       </c>
       <c r="AD320" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STELLA MIA</t>
+          <t>Dining, Dining Set, STELLA MIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42180,7 +46980,22 @@
       </c>
       <c r="AD321" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, STROM</t>
+          <t>Dining, Dining Set, STROM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42308,7 +47123,22 @@
       </c>
       <c r="AD322" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SUTTON</t>
+          <t>Dining, Dining Set, SUTTON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42441,7 +47271,22 @@
       </c>
       <c r="AD323" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SYLVANA</t>
+          <t>Dining, Dining Set, SYLVANA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42574,7 +47419,22 @@
       </c>
       <c r="AD324" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, SYLVANA</t>
+          <t>Dining, Dining Set, SYLVANA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42705,7 +47565,22 @@
       </c>
       <c r="AD325" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, TOTTENHAM</t>
+          <t>Dining, Dining Set, TOTTENHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42836,7 +47711,22 @@
       </c>
       <c r="AD326" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, TOTTENHAM</t>
+          <t>Dining, Dining Set, TOTTENHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -42964,7 +47854,22 @@
       </c>
       <c r="AD327" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, TOTTENHAM</t>
+          <t>Dining, Dining Set, TOTTENHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43091,7 +47996,22 @@
       </c>
       <c r="AD328" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, TOWNSVILLE</t>
+          <t>Dining, Dining Set, TOWNSVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43218,7 +48138,22 @@
       </c>
       <c r="AD329" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, TOWNSVILLE</t>
+          <t>Dining, Dining Set, TOWNSVILLE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43348,7 +48283,22 @@
       </c>
       <c r="AD330" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, UMBRIA</t>
+          <t>Dining, Dining Set, UMBRIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43477,7 +48427,22 @@
       </c>
       <c r="AD331" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, UPMINSTER</t>
+          <t>Dining, Dining Set, UPMINSTER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43605,7 +48570,22 @@
       </c>
       <c r="AD332" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, UPMINSTER</t>
+          <t>Dining, Dining Set, UPMINSTER, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43734,7 +48714,22 @@
       </c>
       <c r="AD333" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, UZWIL</t>
+          <t>Dining, Dining Set, UZWIL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -43866,7 +48861,22 @@
       </c>
       <c r="AD334" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, UZWIL</t>
+          <t>Dining, Dining Set, UZWIL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44006,7 +49016,22 @@
       </c>
       <c r="AD335" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VALDEVERS</t>
+          <t>Dining, Dining Set, VALDEVERS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44146,7 +49171,22 @@
       </c>
       <c r="AD336" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VALDEVERS</t>
+          <t>Dining, Dining Set, VALDEVERS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44286,7 +49326,22 @@
       </c>
       <c r="AD337" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VALDEVERS</t>
+          <t>Dining, Dining Set, VALDEVERS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44417,7 +49472,22 @@
       </c>
       <c r="AD338" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VALO</t>
+          <t>Dining, Dining Set, VALO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44550,7 +49620,22 @@
       </c>
       <c r="AD339" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VARDE</t>
+          <t>Dining, Dining Set, VARDE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44683,7 +49768,22 @@
       </c>
       <c r="AD340" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VARDE</t>
+          <t>Dining, Dining Set, VARDE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44809,7 +49909,22 @@
       </c>
       <c r="AD341" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VIKEN</t>
+          <t>Dining, Dining Set, VIKEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -44935,7 +50050,22 @@
       </c>
       <c r="AD342" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, VIKEN</t>
+          <t>Dining, Dining Set, VIKEN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45065,7 +50195,22 @@
       </c>
       <c r="AD343" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WADENSWIL</t>
+          <t>Dining, Dining Set, WADENSWIL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45197,7 +50342,22 @@
       </c>
       <c r="AD344" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WAILOA</t>
+          <t>Dining, Dining Set, WAILOA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45329,7 +50489,22 @@
       </c>
       <c r="AD345" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WAILOA</t>
+          <t>Dining, Dining Set, WAILOA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45427,7 +50602,22 @@
       </c>
       <c r="AD346" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WESTERHAM</t>
+          <t>Dining, Dining Set, WESTERHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45561,7 +50751,22 @@
       </c>
       <c r="AD347" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WHITEHALL</t>
+          <t>Dining, Dining Set, WHITEHALL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45695,7 +50900,22 @@
       </c>
       <c r="AD348" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WHITEHALL</t>
+          <t>Dining, Dining Set, WHITEHALL, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45826,7 +51046,22 @@
       </c>
       <c r="AD349" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WICHITA</t>
+          <t>Dining, Dining Set, WICHITA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF349" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -45956,7 +51191,22 @@
       </c>
       <c r="AD350" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WICHITA</t>
+          <t>Dining, Dining Set, WICHITA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46084,7 +51334,22 @@
       </c>
       <c r="AD351" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WOODSIDE</t>
+          <t>Dining, Dining Set, WOODSIDE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46211,7 +51476,22 @@
       </c>
       <c r="AD352" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WOODSIDE</t>
+          <t>Dining, Dining Set, WOODSIDE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46339,7 +51619,22 @@
       </c>
       <c r="AD353" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, WOOLWICH</t>
+          <t>Dining, Dining Set, WOOLWICH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46472,7 +51767,22 @@
       </c>
       <c r="AD354" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, YATE</t>
+          <t>Dining, Dining Set, YATE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46609,7 +51919,22 @@
       </c>
       <c r="AD355" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, YATE</t>
+          <t>Dining, Dining Set, YATE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE355" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF355" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46738,7 +52063,22 @@
       </c>
       <c r="AD356" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, YELENA</t>
+          <t>Dining, Dining Set, YELENA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46866,7 +52206,22 @@
       </c>
       <c r="AD357" t="inlineStr">
         <is>
-          <t>Dining, Dining Set, ZAIN</t>
+          <t>Dining, Dining Set, ZAIN, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -46997,7 +52352,22 @@
       </c>
       <c r="AD358" t="inlineStr">
         <is>
-          <t>Dining, Counter Ht. Set, ANAYA</t>
+          <t>Dining, Counter Ht. Set, ANAYA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -47129,7 +52499,22 @@
       </c>
       <c r="AD359" t="inlineStr">
         <is>
-          <t>Dining, Counter Ht. Set, DAKOTA</t>
+          <t>Dining, Counter Ht. Set, DAKOTA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -47240,7 +52625,22 @@
       </c>
       <c r="AD360" t="inlineStr">
         <is>
-          <t>Dining, Counter Ht. Set, EBIKON</t>
+          <t>Dining, Counter Ht. Set, EBIKON, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -47342,7 +52742,22 @@
       </c>
       <c r="AD361" t="inlineStr">
         <is>
-          <t>Dining, Counter Ht. Set, KLAMATH</t>
+          <t>Dining, Counter Ht. Set, KLAMATH, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -47444,7 +52859,22 @@
       </c>
       <c r="AD362" t="inlineStr">
         <is>
-          <t>Dining, Counter Ht. Set, STREATHAM</t>
+          <t>Dining, Counter Ht. Set, STREATHAM, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -47572,7 +53002,22 @@
       </c>
       <c r="AD363" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, BELLAGIO</t>
+          <t>Dining, Dining Table, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -47705,7 +53150,22 @@
       </c>
       <c r="AD364" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, BELLAGIO</t>
+          <t>Dining, Dining Table, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -47835,7 +53295,22 @@
       </c>
       <c r="AD365" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, BELLAGIO</t>
+          <t>Dining, Dining Table, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -47965,7 +53440,22 @@
       </c>
       <c r="AD366" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, BELLAGIO</t>
+          <t>Dining, Dining Table, BELLAGIO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE366" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF366" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG366" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48094,7 +53584,22 @@
       </c>
       <c r="AD367" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, CLEMENTS</t>
+          <t>Dining, Dining Table, CLEMENTS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48223,7 +53728,22 @@
       </c>
       <c r="AD368" t="inlineStr">
         <is>
-          <t>Dining, Dining Table, CLEMENTS</t>
+          <t>Dining, Dining Table, CLEMENTS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48356,7 +53876,22 @@
       </c>
       <c r="AD369" t="inlineStr">
         <is>
-          <t>Dining, Bar Table, ESDARGO</t>
+          <t>Dining, Bar Table, ESDARGO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48485,7 +54020,22 @@
       </c>
       <c r="AD370" t="inlineStr">
         <is>
-          <t>Dining, Bar Table, FOSKEY</t>
+          <t>Dining, Bar Table, FOSKEY, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE370" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF370" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG370" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48626,7 +54176,22 @@
       </c>
       <c r="AD371" t="inlineStr">
         <is>
-          <t>Dining, Bar Table, SANIA</t>
+          <t>Dining, Bar Table, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -48759,7 +54324,22 @@
       </c>
       <c r="AD372" t="inlineStr">
         <is>
-          <t>Dining, Bar Table, SANIA</t>
+          <t>Dining, Bar Table, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/Dining-Set.xlsx
+++ b/FOA SETS/Dining-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1663,11 +1663,11 @@
 - Antique Black or Gray&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Round Table: color: Antique Black or Ivory; dimensions: 48"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 170.5 lbs&lt;/p&gt;</t>
+- Round Table: color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
+Color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+Weight: 170.5 or 170.1 or 168.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1805,17 +1805,18 @@
       <c r="G9" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALFRED 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Linen-like Fabric, Metal, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;/p&gt;
+Gather around ALFRED 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Linen-like Fabric, Metal, Solid Wood, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 48"DIA X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Ivory&lt;br&gt;
+- Antique Black or Gray&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Round Table: color: Antique Black or Ivory; dimensions: 48"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Ivory; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 170.1 lbs&lt;/p&gt;</t>
+- Round Table: color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
+Color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+Weight: 170.5 or 170.1 or 168.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1895,7 +1896,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1949,17 +1950,18 @@
       <c r="G10" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALFRED 5 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Linen-like Fabric, Metal, Solid Wood, construction and Antique Black or Light Gray tones, it blends durability with visual warmth.&lt;/p&gt;
+Gather around ALFRED 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Linen-like Fabric, Metal, Solid Wood, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 48"DIA X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Light Gray&lt;br&gt;
+- Antique Black or Gray&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Round Table: color: Antique Black or Ivory; dimensions: 48"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Light Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Antique Black or Light Gray&lt;br&gt;
-Weight: 168.5 lbs&lt;/p&gt;</t>
+- Round Table: color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
+Color: Antique Black or Gray or Antique Black or Ivory or Antique Black or Light Gray&lt;br&gt;
+Weight: 170.5 or 170.1 or 168.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -2039,7 +2041,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2098,12 +2100,12 @@
 - Rustic&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Antique Black; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Ivory; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;br&gt;
-- Bench: color: Antique Black or Ivory; dimensions: 48" W x 16"D x 19 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
+- Dining Table: color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black&lt;br&gt;
+- Bench: color: Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
 Color: Antique Black&lt;br&gt;
-Weight: 240.6 lbs&lt;/p&gt;</t>
+Weight: 240.6 or 242 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -2183,7 +2185,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2237,17 +2239,17 @@
       <c r="G12" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALFRED 6 Pc. Dining Table Set w/ Bench anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Built from Linen-like Fabric, Metal, Solid Wood, and finished in Antique Black tones for a clean, cohesive look.&lt;/p&gt;
+Gather around ALFRED 6 Pc. Dining Table Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Finished in Antique Black tones, the Linen-like Fabric, Metal, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Antique Black; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Light Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;br&gt;
-- Bench: color: Antique Black or Light Gray; dimensions: 48" W x 16"D x 19 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
+- Dining Table: color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black&lt;br&gt;
+- Bench: color: Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
 Color: Antique Black&lt;br&gt;
-Weight: 242 lbs&lt;/p&gt;</t>
+Weight: 240.6 or 242 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
@@ -2327,7 +2329,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2387,11 +2389,11 @@
 - Rustic&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Antique Black; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
+- Dining Table: color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
 Color: Antique Black&lt;br&gt;
-Weight: 257 lbs&lt;/p&gt;</t>
+Weight: 257 or 256.4 or 254 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -2475,7 +2477,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2529,16 +2531,17 @@
       <c r="G14" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around ALFRED 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Linen-like Fabric, Metal, Solid Wood, construction and Antique Black tones, it blends durability with visual warmth.&lt;/p&gt;
+ALFRED 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Metal, Solid Wood, then finished in Antique Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Antique Black; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Ivory; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
+- Dining Table: color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
 Color: Antique Black&lt;br&gt;
-Weight: 256.4 lbs&lt;/p&gt;</t>
+Weight: 257 or 256.4 or 254 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -2618,7 +2621,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2672,16 +2675,17 @@
       <c r="G15" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALFRED 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Antique Black tones, the Linen-like Fabric, Metal, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+ALFRED 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Metal, Solid Wood, then finished in Antique Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Metal Accents Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Antique Black; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Light Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood.&lt;br&gt;
+- Dining Table: color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Metal, Solid Wood, Others.&lt;br&gt;
 Color: Antique Black&lt;br&gt;
-Weight: 254 lbs&lt;/p&gt;</t>
+Weight: 257 or 256.4 or 254 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -2761,7 +2765,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2904,7 +2908,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3020,7 +3024,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3080,11 +3084,11 @@
 - 24" Expandable Leaf&lt;br&gt;
 - Leaf Mechanism&lt;br&gt;
 - Double Pedestal Base Included items and dimensions:&lt;br&gt;
-- Arm Chair (2 / CTN): color: Gray or Silver; dimensions: 24 1 or 2" W x 26"D x 41" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Gray or Silver; dimensions: 21" W x 26"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 389.4 lbs&lt;/p&gt;</t>
+- Arm Chair (2 / CTN): color: Gray or Brown Cherry&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Leatherette, Solid Wood, Wood Veneers, Others.&lt;br&gt;
+Color: Gray or Brown Cherry&lt;br&gt;
+Weight: 389.4 or 388.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
@@ -3168,7 +3172,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3222,18 +3226,17 @@
       <c r="G19" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALPENA 7 Pc. Dining Table Set (2AC and 4SC) anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Leatherette, Solid Wood, Wood Veneers, construction and Brown Cherry tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around ALPENA 7 Pc. Dining Table Set (2AC and 4SC), designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Solid Wood, Wood Veneer, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 103"(79" + 1 X 24"LEAF)L X 47 1/2"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 24" Expandable Leaf&lt;br&gt;
 - Leaf Mechanism&lt;br&gt;
-- Double Pedestal Base&lt;br&gt;
-- Crisscross Pattern Table Top Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Brown Cherry or Espresso; dimensions: 21" W x 26"D x 41 1 or 2" H; feature: Transitional&lt;br&gt;
-- Arm Chair (2 / CTN): color: Brown Cherry or Espresso; dimensions: 24 1 or 2" W x 26"D x 41 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneers.&lt;br&gt;
-Color: Brown Cherry&lt;br&gt;
-Weight: 388.2 lbs&lt;/p&gt;</t>
+- Double Pedestal Base Included items and dimensions:&lt;br&gt;
+- Arm Chair (2 / CTN): color: Gray or Brown Cherry&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Leatherette, Solid Wood, Wood Veneers, Others.&lt;br&gt;
+Color: Gray or Brown Cherry&lt;br&gt;
+Weight: 389.4 or 388.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -3317,7 +3320,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3377,11 +3380,11 @@
 - 24" Expandable Leaf&lt;br&gt;
 - Leaf Mechanism&lt;br&gt;
 - Double Pedestal Base Included items and dimensions:&lt;br&gt;
-- Arm Chair (2 / CTN): color: Gray or Silver; dimensions: 24 1 or 2" W x 26"D x 41" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Gray or Silver; dimensions: 21" W x 26"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 435.6 lbs&lt;/p&gt;</t>
+- Arm Chair (2 / CTN): color: Gray or Brown Cherry&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Leatherette, Solid Wood, Wood Veneers, Others.&lt;br&gt;
+Color: Gray or Brown Cherry&lt;br&gt;
+Weight: 435.6 or 435.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -3465,7 +3468,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3519,18 +3522,17 @@
       <c r="G21" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around ALPENA 9 Pc. Dining Table Set (2AC and 6SC), designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, Wood Veneers, and finished in Brown Cherry tones for a clean, cohesive look.&lt;br&gt;
+ALPENA 9 Pc. Dining Table Set (2AC and 6SC) sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Gray tones, the Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 103"(79" + 1 X 24"LEAF)L X 47 1/2"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 24" Expandable Leaf&lt;br&gt;
 - Leaf Mechanism&lt;br&gt;
-- Double Pedestal Base&lt;br&gt;
-- Crisscross Pattern Table Top Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Brown Cherry or Espresso; dimensions: 21" W x 26"D x 41 1 or 2" H; feature: Transitional&lt;br&gt;
-- Arm Chair (2 / CTN): color: Brown Cherry or Espresso; dimensions: 24 1 or 2" W x 26"D x 41 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneers.&lt;br&gt;
-Color: Brown Cherry&lt;br&gt;
-Weight: 435.5 lbs&lt;/p&gt;</t>
+- Double Pedestal Base Included items and dimensions:&lt;br&gt;
+- Arm Chair (2 / CTN): color: Gray or Brown Cherry&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Leatherette, Solid Wood, Wood Veneers, Others.&lt;br&gt;
+Color: Gray or Brown Cherry&lt;br&gt;
+Weight: 435.6 or 435.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -3614,7 +3616,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3753,7 +3755,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3808,16 +3810,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around AMINA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Glass, Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"LEAF)L X 42"W X 30"H&lt;/p&gt;
+Product Dimensions: 84"(66" + 1 X 18"LEAF)L X 42"W X 30"H / 66"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 18" Expandable Leaf&lt;br&gt;
 - Two 5mm Tempered Glass Inserts&lt;br&gt;
 - Curving Legs Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Gray; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Gray; dimensions: 22" W x 26"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 322.9 lbs&lt;/p&gt;</t>
+- Dining Table: color: Gray or Champagne&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Champagne&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer, Others or Glass, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or Champagne&lt;br&gt;
+Weight: 322.9 or 294 or 325.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -3901,7 +3903,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3955,16 +3957,17 @@
       <c r="G24" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AMINA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Glass, Solid Wood, Wood Veneer, and finished in Champagne tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 66"L X 42"W X 30"H&lt;/p&gt;
+Gather around AMINA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Glass, Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 84"(66" + 1 X 18"LEAF)L X 42"W X 30"H / 66"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- 66" Dining Table&lt;br&gt;
-- Two 5mm Tempered Glass Inserts Included items and dimensions:&lt;br&gt;
-- 66" Dining Table: color: Champagne; dimensions: 66" L x 42" W x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Champagne; dimensions: 22" W x 25"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Champagne&lt;br&gt;
-Weight: 294 lbs&lt;/p&gt;</t>
+- 18" Expandable Leaf&lt;br&gt;
+- Two 5mm Tempered Glass Inserts&lt;br&gt;
+- Curving Legs Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Gray or Champagne&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Champagne&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer, Others or Glass, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or Champagne&lt;br&gt;
+Weight: 322.9 or 294 or 325.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -4048,7 +4051,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4102,16 +4105,17 @@
       <c r="G25" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AMINA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Glass, Solid Wood, Wood Veneer, then finished in Champagne tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+Gather around AMINA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Glass, Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 84"(66" + 1 X 18"LEAF)L X 42"W X 30"H / 66"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 18" Expandable Leaf&lt;br&gt;
-- Two 5mm Tempered Glass Inserts Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Champagne; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Champagne; dimensions: 22" W x 25"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Champagne&lt;br&gt;
-Weight: 325.9 lbs&lt;/p&gt;</t>
+- Two 5mm Tempered Glass Inserts&lt;br&gt;
+- Curving Legs Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Gray or Champagne&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Champagne&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer, Others or Glass, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or Champagne&lt;br&gt;
+Weight: 322.9 or 294 or 325.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -4195,7 +4199,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4255,11 +4259,11 @@
 - 18" Expandable Leaf&lt;br&gt;
 - Two 5mm Tempered Glass Inserts&lt;br&gt;
 - Curving Legs Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Gray; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Gray; dimensions: 22" W x 26"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 370.4 lbs&lt;/p&gt;</t>
+- Dining Table: color: Gray or Champagne&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Champagne&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer, Others or Glass, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or Champagne&lt;br&gt;
+Weight: 370.4 or 374.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="25" t="inlineStr">
@@ -4343,7 +4347,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4397,16 +4401,17 @@
       <c r="G27" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AMINA 9 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Champagne tones, the Glass, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+Gather around AMINA 9 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Glass, Leatherette, Solid Wood, Wood Veneer, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 84"(66" + 1 X 18"LEAF)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 18" Expandable Leaf&lt;br&gt;
-- Two 5mm Tempered Glass Inserts Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Champagne; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Champagne; dimensions: 22" W x 25"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Champagne&lt;br&gt;
-Weight: 374.4 lbs&lt;/p&gt;</t>
+- Two 5mm Tempered Glass Inserts&lt;br&gt;
+- Curving Legs Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Gray or Champagne&lt;br&gt;
+- Side Chair (2 / CTN): color: Gray or Champagne&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Solid Wood, Wood Veneer, Others or Glass, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or Champagne&lt;br&gt;
+Weight: 370.4 or 374.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="25" t="inlineStr">
@@ -4490,7 +4495,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4634,7 +4639,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4696,11 +4701,11 @@
 - Pedestal Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Rustic Natural Tone or Ivory; dimensions: 60"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory; dimensions: 22 1 or 4" W x 25 3 or 8"D x 43" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Natural Tone or Ivory&lt;br&gt;
-Weight: 262.82 lbs&lt;/p&gt;</t>
+- Round Dining Table: color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 262.82 or 259.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
@@ -4784,7 +4789,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4838,18 +4843,19 @@
       <c r="G30" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARCADIA 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and Antique White tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around ARCADIA 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Rustic Natural Tone or Ivory tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 60"DIA X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
+- Rustic Natural Tone or Ivory&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Antique White or Ivory; dimensions: 60"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique White; dimensions: 22 1 or 4" W x 26"D x 42 1 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique White&lt;br&gt;
-Weight: 259.52 lbs&lt;/p&gt;</t>
+- Round Dining Table: color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 262.82 or 259.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="27" t="inlineStr">
@@ -4933,7 +4939,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -4988,7 +4994,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ARCADIA 7 Pc. Dining Table Set (2AC and 4SC) sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Rustic Natural Tone or Ivory tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 96"(78" + 1 X 18"Leaf) L X 44"W X 30 1/2"H&lt;/p&gt;
+Product Dimensions: 96"(78" + 1 X 18"Leaf) L X 44"W X 30 1/2"H / Table: 96"(78" + 1 X 18"LEAF) L X 44"W X 30 1/2"H  Chair: 22 1/4"W X 26"D X 42 1/4"H (SEAT HT: 19", SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Natural Tone or Ivory&lt;br&gt;
@@ -4996,11 +5002,11 @@
 - Trestle Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory; dimensions: 22 1 or 4" W x 25 3 or 8"D x 43" H; feature: Rustic&lt;br&gt;
-- Arm Chair (2 / CTN): color: Rustic Natural Tone or Ivory; dimensions: 27 1 or 2" W x 25 3 or 8"D x 43" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Natural Tone or Ivory&lt;br&gt;
-Weight: 373.89 lbs&lt;/p&gt;</t>
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Arm Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 373.89 or 370.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
@@ -5084,7 +5090,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5138,19 +5144,20 @@
       <c r="G32" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around ARCADIA 7 Pc. Dining Table Set (2AC and 4SC), designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Antique White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Table: 96"(78" + 1 X 18"LEAF) L X 44"W X 30 1/2"H Chair: 22 1/4"W X 26"D X 42 1/4"H (SEAT HT: 19", SEAT DP: 18")&lt;/p&gt;
+ARCADIA 7 Pc. Dining Table Set (2AC and 4SC) sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Rustic Natural Tone or Ivory tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 96"(78" + 1 X 18"Leaf) L X 44"W X 30 1/2"H / Table: 96"(78" + 1 X 18"LEAF) L X 44"W X 30 1/2"H  Chair: 22 1/4"W X 26"D X 42 1/4"H (SEAT HT: 19", SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
+- Rustic Natural Tone or Ivory&lt;br&gt;
 - 18" Expandable Leaf&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique White; dimensions: 22 1 or 4" W x 26"D x 42 1 or 4" H; feature: Rustic&lt;br&gt;
-- Arm Chair (2 / CTN): color: Antique White; dimensions: 27 1 or 2" W x 26"D x 42 1 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique White&lt;br&gt;
-Weight: 370.47 lbs&lt;/p&gt;</t>
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Arm Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 373.89 or 370.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
@@ -5234,7 +5241,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5380,7 +5387,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5442,11 +5449,11 @@
 - Pedestal Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Rustic Natural Tone or Ivory; dimensions: 60"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory; dimensions: 22 1 or 4" W x 25 3 or 8"D x 43" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Natural Tone or Ivory&lt;br&gt;
-Weight: 315.58 lbs&lt;/p&gt;</t>
+- Round Dining Table: color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 315.58 or 312.28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="31" t="inlineStr">
@@ -5530,7 +5537,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5584,17 +5591,19 @@
       <c r="G35" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around ARCADIA 7 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Finished in Antique White tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;/p&gt;
+ARCADIA 7 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Fabric, Solid Wood, Wood Veneer, construction and Rustic Natural Tone or Ivory tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 60"DIA X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
+- Rustic Natural Tone or Ivory&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Intricate Wood Inlay Details&lt;br&gt;
 - Upholstered Seat Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Antique White or Ivory; dimensions: 60"DIA x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique White; dimensions: 22 1 or 4" W x 26"D x 42 1 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique White&lt;br&gt;
-Weight: 312.28 lbs&lt;/p&gt;</t>
+- Round Dining Table: color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Natural Tone or Ivory or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Natural Tone or Ivory or Antique White&lt;br&gt;
+Weight: 315.58 or 312.28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="31" t="inlineStr">
@@ -5674,7 +5683,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5813,7 +5822,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5868,16 +5877,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around AULETTA 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Distressed White or Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 54" DIA X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4")&lt;/p&gt;
+Product Dimensions: 54" DIA X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4") / 54"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Distressed White or Gray&lt;br&gt;
 - Pronounced Wood Grain Top Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Distressed White or Gray; dimensions: 54" DIA x 30" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Distressed White or Gray; dimensions: 20" W x 22 1 or 2"D x 38 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Distressed White or Gray&lt;br&gt;
-Weight: 198 lbs&lt;/p&gt;</t>
+- Round Dining Table: color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+Weight: 198 or 199.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" s="33" t="inlineStr">
@@ -5961,7 +5970,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6015,22 +6024,17 @@
       <c r="G38" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AULETTA 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Distressed White or Distressed Dark Oak tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 54"DIA X 30"H&lt;/p&gt;
+Gather around AULETTA 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Distressed White or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 54" DIA X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4") / 54"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Distressed White or Distressed Dark Oak&lt;br&gt;
-- Pedestal Base&lt;br&gt;
-- Wood Grain Top&lt;br&gt;
-- Two-tone Finish&lt;br&gt;
-- Distressed Wood&lt;br&gt;
-- Padded Fabric Seat&lt;br&gt;
-- Decorative Back Rest Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Distressed White or Distressed Dark Oak; dimensions: 54"DIA x 30" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Distressed White or Gray; dimensions: 20" W x 22 1 or 2"D x 38 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Distressed White or Distressed Dark Oak&lt;br&gt;
-Weight: 199.1 lbs&lt;/p&gt;</t>
+- Distressed White or Gray&lt;br&gt;
+- Pronounced Wood Grain Top Included items and dimensions:&lt;br&gt;
+- Round Dining Table: color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+Weight: 198 or 199.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="33" t="inlineStr">
@@ -6114,7 +6118,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6169,17 +6173,17 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 AULETTA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Fabric, Solid Wood, Wood Veneer, construction and Distressed White or Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4")&lt;/p&gt;
+Product Dimensions: 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4") / 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Distressed White or Gray&lt;br&gt;
 - Padded Fabric Seat&lt;br&gt;
 - Pronounced Wood Grain Top&lt;br&gt;
 - Decorative Back Rest Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Distressed White or Gray; dimensions: 20" W x 22 1 or 2"D x 38 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Distressed White or Gray&lt;br&gt;
-Weight: 292.5 lbs&lt;/p&gt;</t>
+- Side Chair (2 / CTN): color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+Weight: 292.5 or 290.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="35" t="inlineStr">
@@ -6263,7 +6267,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6317,22 +6321,18 @@
       <c r="G40" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around AULETTA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Finished in Distressed White or Distressed Dark Oak tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H&lt;/p&gt;
+AULETTA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Fabric, Solid Wood, Wood Veneer, construction and Distressed White or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H (SEAT HT: 18 1/2", SEAT DP: 17 1/4") / 86"(68" + 1 X 18"LEAF)L X 40"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Distressed White or Distressed Dark Oak&lt;br&gt;
-- Trestle Base&lt;br&gt;
-- Wood Grain Top&lt;br&gt;
-- Two-tone Finish&lt;br&gt;
-- Distressed Wood&lt;br&gt;
+- Distressed White or Gray&lt;br&gt;
 - Padded Fabric Seat&lt;br&gt;
-- Decorative Back Rest&lt;br&gt;
-- Multiple Storage Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Distressed White or Gray; dimensions: 20" W x 22 1 or 2"D x 38 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Distressed White or Distressed Dark Oak&lt;br&gt;
-Weight: 290.4 lbs&lt;/p&gt;</t>
+- Pronounced Wood Grain Top&lt;br&gt;
+- Decorative Back Rest Included items and dimensions:&lt;br&gt;
+- Side Chair (2 / CTN): color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Distressed White or Gray or Distressed White or Distressed Dark Oak&lt;br&gt;
+Weight: 292.5 or 290.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="35" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6770,8 +6770,8 @@
 - 2 Table Base Configurations&lt;br&gt;
 - Velvet Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone Top, Stainless Steel.&lt;br&gt;
-Color: Gold or Black&lt;br&gt;
-Weight: 590.4 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Gray or Chrome or Black or Chrome or Gray&lt;br&gt;
+Weight: 590.4 or 594 or 594.84 or 591 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6909,15 +6909,15 @@
       <c r="G44" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BASILICATA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Fabric, Sintered Stone Top, Stainless Steel construction and Gold or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+BASILICATA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Fabric, Sintered Stone Top, Stainless Steel, then finished in Gold or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Gold or Gray&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - 2 Table Base Configurations&lt;br&gt;
 - Velvet Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone Top, Stainless Steel.&lt;br&gt;
-Color: Gold or Gray&lt;br&gt;
-Weight: 594 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Gray or Chrome or Black or Chrome or Gray&lt;br&gt;
+Weight: 590.4 or 594 or 594.84 or 591 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="37" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7055,15 +7055,15 @@
       <c r="G45" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around BASILICATA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Chrome or Black tones, the Fabric, Sintered Stone Top, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
+BASILICATA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Fabric, Sintered Stone Top, Stainless Steel, then finished in Gold or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Black&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - 2 Table Base Configurations&lt;br&gt;
 - Velvet Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone Top, Stainless Steel.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
-Weight: 594.84 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Gray or Chrome or Black or Chrome or Gray&lt;br&gt;
+Weight: 590.4 or 594 or 594.84 or 591 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="37" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7201,15 +7201,15 @@
       <c r="G46" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BASILICATA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Built from Fabric, Sintered Stone Top, Stainless Steel and finished in Chrome or Gray tones for a clean, cohesive look.&lt;br&gt;
+BASILICATA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Fabric, Sintered Stone Top, Stainless Steel, then finished in Gold or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Gray&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - 2 Table Base Configurations&lt;br&gt;
 - Velvet Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone Top, Stainless Steel.&lt;br&gt;
-Color: Chrome or Gray&lt;br&gt;
-Weight: 591 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Gray or Chrome or Black or Chrome or Gray&lt;br&gt;
+Weight: 590.4 or 594 or 594.84 or 591 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="37" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7352,11 +7352,11 @@
 &lt;p&gt;Features&lt;br&gt;
 - Spindle Back&lt;br&gt;
 - Molded Seats Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black; dimensions: 60" W x 36"D x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 20.5" W x 20.5"D x 32.5" H (SEAT HT: 18", SEAT DP: 16.5"); feature: Mid-Century Modern&lt;/p&gt;
+- Dining Table: color: Black or Walnut&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 181.5 lbs&lt;/p&gt;</t>
+Color: Black or Walnut&lt;br&gt;
+Weight: 181.5 or 182.99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="39" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7494,16 +7494,16 @@
       <c r="G48" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around BEALE 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Rubberwood, Oak Veneer, Engineered Wood, then finished in Walnut tones to suit a range of interiors.&lt;br&gt;
+BEALE 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Rubberwood, Oak Veneer, Engineered Wood and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 60"W X 36"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Spindle Back&lt;br&gt;
 - Molded Seats Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Walnut; dimensions: 60" W x 36"D x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Walnut; dimensions: 20.3" W x 20.7"D x 32.1" H (SEAT HT: 18", SEAT DP: 16.5"); feature: Mid-Century Modern&lt;/p&gt;
+- Dining Table: color: Black or Walnut&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Walnut&lt;br&gt;
-Weight: 182.99 lbs&lt;/p&gt;</t>
+Color: Black or Walnut&lt;br&gt;
+Weight: 181.5 or 182.99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="39" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7642,17 +7642,17 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around BELLAGIO 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Solid Wood, Wood Veneer, then finished in Brown Cherry tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H&lt;/p&gt;
+Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H / 60"DIA X 30H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Two 18" Expandable Leaf&lt;br&gt;
 - Double Pedestal Base&lt;br&gt;
 - Rope Carved Table Edge&lt;br&gt;
 - 2 Chair Options Included items and dimensions:&lt;br&gt;
-- Leatherette Side Chair (2 / CTN): color: Brown Cherry or Dark Brown; dimensions: 27" W x 22 1 or 2"D x 43 1 or 4" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Leatherette Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
-Weight: 457.6 lbs&lt;/p&gt;</t>
+Weight: 457.6 or 467.5 or 367.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="41" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7790,18 +7790,18 @@
       <c r="G50" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELLAGIO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Leatherette, Solid Wood, Wood Veneer, construction and Brown Cherry tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H&lt;/p&gt;
+Gather around BELLAGIO 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Solid Wood, Wood Veneer, then finished in Brown Cherry tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H / 60"DIA X 30H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Two 18" Expandable Leaf&lt;br&gt;
 - Double Pedestal Base&lt;br&gt;
 - Rope Carved Table Edge&lt;br&gt;
 - 2 Chair Options Included items and dimensions:&lt;br&gt;
-- Wooden Side Chair (2 / CTN): color: Brown Cherry or Dark Brown; dimensions: 25 1 or 2" W x 23"D x 42 1 or 2" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Leatherette Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
-Weight: 467.5 lbs&lt;/p&gt;</t>
+Weight: 457.6 or 467.5 or 367.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="41" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7947,10 +7947,10 @@
 - Double Pedestal Base&lt;br&gt;
 - Rope Carved Table Edge&lt;br&gt;
 - 2 Chair Options Included items and dimensions:&lt;br&gt;
-- Leatherette Side Chair (2 / CTN): color: Brown Cherry or Dark Brown; dimensions: 27" W x 22 1 or 2"D x 43 1 or 4" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Leatherette Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
-Weight: 514.8 lbs&lt;/p&gt;</t>
+Weight: 514.8 or 528 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8088,7 +8088,7 @@
       <c r="G52" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELLAGIO 9 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, Wood Veneer, then finished in Brown Cherry tones to suit a range of interiors.&lt;br&gt;
+Gather around BELLAGIO 9 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, Wood Veneer, and finished in Brown Cherry tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
@@ -8096,10 +8096,10 @@
 - Double Pedestal Base&lt;br&gt;
 - Rope Carved Table Edge&lt;br&gt;
 - 2 Chair Options Included items and dimensions:&lt;br&gt;
-- Wooden Side Chair (2 / CTN): color: Brown Cherry or Dark Brown; dimensions: 25 1 or 2" W x 23"D x 42 1 or 2" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Leatherette Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
-Weight: 528 lbs&lt;/p&gt;</t>
+Weight: 514.8 or 528 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9399,10 +9399,10 @@
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Swivel Rotates 360°&lt;br&gt;
 - Removable Back Pillow on 6 Casters on Side Chair Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: Light Gray; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 331.6 lbs&lt;/p&gt;</t>
+Weight: 331.6 or 337.6 or 336 or 372.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="15" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9540,17 +9540,17 @@
       <c r="G62" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BROAGER 5 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal and finished in Rustic Oak or Dark Walnut tones for a clean, cohesive look.&lt;br&gt;
+BROAGER 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Rustic Oak or Dark Walnut tones, the Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 54"DIA X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Oak or Dark Walnut&lt;br&gt;
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Swivel Rotates 360°&lt;br&gt;
 - Removable Back Pillow on 6 Casters on Side Chair Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: White; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 337.6 lbs&lt;/p&gt;</t>
+Weight: 331.6 or 337.6 or 336 or 372.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="15" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9688,17 +9688,17 @@
       <c r="G63" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around BROAGER 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal, then finished in Rustic Oak or Dark Walnut tones to suit a range of interiors.&lt;br&gt;
+BROAGER 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Rustic Oak or Dark Walnut tones, the Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 54"DIA X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Oak or Dark Walnut&lt;br&gt;
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Swivel Rotates 360°&lt;br&gt;
 - Removable Back Pillow on 6 Casters on Side Chair Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: Light Gray; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 336 lbs&lt;/p&gt;</t>
+Weight: 331.6 or 337.6 or 336 or 372.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9836,17 +9836,17 @@
       <c r="G64" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BROAGER 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal construction and Rustic Oak or Dark Walnut tones, it blends durability with visual warmth.&lt;br&gt;
+BROAGER 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Rustic Oak or Dark Walnut tones, the Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 54"DIA X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Oak or Dark Walnut&lt;br&gt;
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Swivel Rotates 360°&lt;br&gt;
 - Removable Back Pillow on 6 Casters on Side Chair Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: White; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 372.4 lbs&lt;/p&gt;</t>
+Weight: 331.6 or 337.6 or 336 or 372.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9988,10 +9988,10 @@
 Product Dimensions: 54"W X 54"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Oak or Dark Walnut Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: White; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 382.44 lbs&lt;/p&gt;</t>
+Weight: 382.44 or 417.24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10129,14 +10129,14 @@
       <c r="G66" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around BROAGER 5 Pc. Square Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal and finished in Rustic Oak or Dark Walnut tones for a clean, cohesive look.&lt;br&gt;
+BROAGER 5 Pc. Square Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Rustic Oak or Dark Walnut tones, the Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 54"W X 54"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Oak or Dark Walnut Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: White; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Rustic Oak or Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Solid Wood, White Oak Veneer, Engineered Wood, Metal.&lt;br&gt;
 Color: Rustic Oak or Dark Walnut&lt;br&gt;
-Weight: 417.24 lbs&lt;/p&gt;</t>
+Weight: 382.44 or 417.24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10282,11 +10282,11 @@
 - Two-Tone Design&lt;br&gt;
 - Genuine Marble Top&lt;br&gt;
 - Padded Fabric Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: White or Antique Black; dimensions: 60" L x 30" W x 36" H; feature: Transitional&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Gray; dimensions: 19" W x 23 1 or 2"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Genuine Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+- Counter Height Table: color: White or Antique Black&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: White or Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Genuine Marble, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White or Antique Black&lt;br&gt;
-Weight: 243.6 lbs&lt;/p&gt;</t>
+Weight: 243.6 or 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10424,7 +10424,7 @@
       <c r="G68" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around BRULE 5 Pc. Counter Height Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Antique Black tones, the Fabric, Genuine Marble, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+BRULE 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Genuine Marble, Solid Wood, Wood Veneer, construction and White or Antique Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 60"L X 30"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - White or Antique Black&lt;br&gt;
@@ -10432,11 +10432,11 @@
 - Two-Tone Design&lt;br&gt;
 - Genuine Marble Top&lt;br&gt;
 - Padded Fabric Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: White or Antique Black; dimensions: 60" L x 30" W x 36" H; feature: Transitional&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Light Gray; dimensions: 19" W x 23 1 or 2"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Genuine Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+- Counter Height Table: color: White or Antique Black&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: White or Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Genuine Marble, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White or Antique Black&lt;br&gt;
-Weight: 246 lbs&lt;/p&gt;</t>
+Weight: 243.6 or 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11160,10 +11160,10 @@
 - 12mm Tempered Glass&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Clear Acrylic Legs Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Chrome; dimensions: 17 3 or 4" W x 22 7 or 8"D x 38 3 or 4" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Acrylic, Leatherette, Metal.&lt;br&gt;
+- Side Chair (2 / CTN): color: Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Acrylic, Leatherette, Metal, Others.&lt;br&gt;
 Color: Chrome&lt;br&gt;
-Weight: 325.6 lbs&lt;/p&gt;</t>
+Weight: 325.6 or 323.86 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="21" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11301,17 +11301,18 @@
       <c r="G74" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around CASPER 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Glass, Acrylic, Leatherette, Metal, then finished in Chrome tones to suit a range of interiors.&lt;/p&gt;
+CASPER 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Glass, Acrylic, Leatherette, Metal, and finished in Chrome tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 72"L X 40"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Metal Frame Construction&lt;br&gt;
 - Minimalist Design&lt;br&gt;
 - 12mm Tempered Glass&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Clear Acrylic Legs Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Black; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Acrylic, Leatherette, Metal.&lt;br&gt;
+- Side Chair (2 / CTN): color: Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Acrylic, Leatherette, Metal, Others.&lt;br&gt;
 Color: Chrome&lt;br&gt;
-Weight: 323.86 lbs&lt;/p&gt;</t>
+Weight: 325.6 or 323.86 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="21" t="inlineStr">
@@ -11395,7 +11396,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11539,7 +11540,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11683,7 +11684,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11825,7 +11826,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11971,7 +11972,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -12113,7 +12114,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12255,7 +12256,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12397,7 +12398,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12539,7 +12540,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12685,7 +12686,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12830,7 +12831,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12978,7 +12979,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -13125,7 +13126,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -13268,7 +13269,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13323,15 +13324,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 EBIKON 5 Pc. Counter Height Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Solid Wood, Engineered Wood, Wood Veneer, Boucle, construction and Walnut tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: Table: 59.1"L X 21.7"W X 36"H&lt;/p&gt;
+Product Dimensions: Table: 59.1"L X 21.7"W X 36"H / 59"W X 35.5"D X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Curved Panel Back Chair&lt;br&gt;
 - Padded Seats Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: Walnut; dimensions: 59" W x 21.5"D x 36" H; feature: Mid-Century Modern&lt;br&gt;
-- Counter Stool (2 / CTN): color: Walnut or Beige; dimensions: 21.5" W x 23"D x 34" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Engineered Wood, Wood Veneer, Boucle.&lt;br&gt;
+- Counter Height Table: color: Walnut&lt;br&gt;
+- Counter Stool (2 / CTN): color: Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood, Wood Veneer, Boucle, Others.&lt;br&gt;
 Color: Walnut&lt;br&gt;
-Weight: 120.68 lbs&lt;/p&gt;</t>
+Weight: 120.68 or 147.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="23" t="inlineStr">
@@ -13415,7 +13416,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13532,7 +13533,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13673,7 +13674,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13816,7 +13817,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13960,7 +13961,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -14103,7 +14104,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -14246,7 +14247,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14389,7 +14390,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14532,7 +14533,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14675,7 +14676,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14820,7 +14821,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14964,7 +14965,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -15108,7 +15109,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -15172,10 +15173,10 @@
 - Pedestal Base&lt;br&gt;
 - Scroll Back&lt;br&gt;
 - Button Tufted Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: White or Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White or Antique Black&lt;br&gt;
-Weight: 250 lbs&lt;/p&gt;</t>
+Weight: 250 or 249.6 or 248 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="25" t="inlineStr">
@@ -15259,7 +15260,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15313,7 +15314,7 @@
       <c r="G102" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELFREDO 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in White or Antique Black tones, the Genuine Marble, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Gather around ELFREDO 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Genuine Marble, Solid Wood, Wood Veneer, construction and White or Antique Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: Table: 48"DIA X 30 1/2"H, Chair: 18 1/2"W X 26 1/2"D X 38 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
@@ -15323,10 +15324,10 @@
 - Pedestal Base&lt;br&gt;
 - Scroll Back&lt;br&gt;
 - Button Tufted Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Ivory; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: White or Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White or Antique Black&lt;br&gt;
-Weight: 249.6 lbs&lt;/p&gt;</t>
+Weight: 250 or 249.6 or 248 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="25" t="inlineStr">
@@ -15410,7 +15411,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15464,7 +15465,7 @@
       <c r="G103" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELFREDO 5 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Built from Genuine Marble, Solid Wood, Wood Veneer, and finished in White or Antique Black tones for a clean, cohesive look.&lt;br&gt;
+Gather around ELFREDO 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Genuine Marble, Solid Wood, Wood Veneer, construction and White or Antique Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: Table: 48"DIA X 30 1/2"H, Chair: 18 1/2"W X 26 1/2"D X 38 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
@@ -15474,10 +15475,10 @@
 - Pedestal Base&lt;br&gt;
 - Scroll Back&lt;br&gt;
 - Button Tufted Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique Black or Light Gray; dimensions: 18 1 or 2" W x 26 1 or 2"D x 40" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: White or Antique Black&lt;/p&gt;
+&lt;p&gt;Materials: Genuine Marble, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White or Antique Black&lt;br&gt;
-Weight: 248 lbs&lt;/p&gt;</t>
+Weight: 250 or 249.6 or 248 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="25" t="inlineStr">
@@ -15561,7 +15562,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15705,7 +15706,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15849,7 +15850,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -15991,7 +15992,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -16134,7 +16135,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -16279,7 +16280,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -16424,7 +16425,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16568,7 +16569,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16713,7 +16714,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16857,7 +16858,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -17005,7 +17006,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -17149,7 +17150,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -17295,7 +17296,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -17440,7 +17441,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -17495,7 +17496,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around GIANNA 6 Pc. Dining Table Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Rustic Pine or Brown tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 96"L X 42"W X 30"H&lt;/p&gt;
+Product Dimensions: 96"L X 42"W X 30"H / 77"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -17504,11 +17505,11 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Brown; dimensions: 20" W x 23"D x 39" H; feature: Rustic&lt;br&gt;
-- Fabric Bench: color: Rustic Oak or Brown; dimensions: 72" W x 19"D x 19 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;br&gt;
+- Fabric Bench: color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 324.9 lbs&lt;/p&gt;</t>
+Weight: 324.9 or 288.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="27" t="inlineStr">
@@ -17592,7 +17593,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -17646,8 +17647,8 @@
       <c r="G118" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GIANNA 6 Pc. Dining Table Set w/ Bench anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and Rustic Pine or Brown tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 77"L X 42"W X 30"H&lt;/p&gt;
+Gather around GIANNA 6 Pc. Dining Table Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Rustic Pine or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 96"L X 42"W X 30"H / 77"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -17656,11 +17657,11 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Brown; dimensions: 20" W x 23"D x 39" H; feature: Rustic&lt;br&gt;
-- Wooden Bench: color: Rustic Oak; dimensions: 53" W x 17"D x 18" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;br&gt;
+- Fabric Bench: color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 288.2 lbs&lt;/p&gt;</t>
+Weight: 324.9 or 288.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" s="27" t="inlineStr">
@@ -17744,7 +17745,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17799,7 +17800,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 GIANNA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Rustic Pine or Brown tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 77"L X 42"W X 30"H&lt;/p&gt;
+Product Dimensions: 77"L X 42"W X 30"H / 96"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -17808,10 +17809,10 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Brown; dimensions: 20" W x 23"D x 39" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 298.2 lbs&lt;/p&gt;</t>
+Weight: 298.2 or 326.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" s="29" t="inlineStr">
@@ -17895,7 +17896,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17949,8 +17950,8 @@
       <c r="G120" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around GIANNA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Rustic Pine or Brown tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 96"L X 42"W X 30"H&lt;/p&gt;
+GIANNA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Rustic Pine or Brown tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 77"L X 42"W X 30"H / 96"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -17959,10 +17960,10 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Brown; dimensions: 20" W x 23"D x 39" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 326.8 lbs&lt;/p&gt;</t>
+Weight: 298.2 or 326.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" s="29" t="inlineStr">
@@ -18046,7 +18047,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -18101,7 +18102,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 GIANNA 7 Pc. Dining Table Set (w/ 2 Wingback Chairs) anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Rustic Pine or Brown tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 96"L X 42"W X 30"H&lt;/p&gt;
+Product Dimensions: 96"L X 42"W X 30"H / 77"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -18110,11 +18111,11 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Ivory; dimensions: 20 3 or 4 x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Rustic Oak or Ivory; dimensions: 22 1 or 2 x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;br&gt;
+- Wingback Chair (2 / CTN): color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 327.92 lbs&lt;/p&gt;</t>
+Weight: 327.92 or 299.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" s="31" t="inlineStr">
@@ -18198,7 +18199,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -18252,8 +18253,8 @@
       <c r="G122" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GIANNA 7 Pc. Dining Table Set (w/ 2 Wingback Chairs) sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Fabric, Solid Wood, Wood Veneer, construction and Rustic Pine or Brown tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 77"L X 42"W X 30"H&lt;/p&gt;
+GIANNA 7 Pc. Dining Table Set (w/ 2 Wingback Chairs) anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Rustic Pine or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 96"L X 42"W X 30"H / 77"L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Rustic Pine or Brown&lt;br&gt;
@@ -18262,11 +18263,11 @@
 - Center Support Beam&lt;br&gt;
 - Upholstered Seat&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Ivory; dimensions: 20 3 or 4 x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Rustic Oak or Ivory; dimensions: 22 1 or 2 x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Pine or Brown&lt;br&gt;
+- Wingback Chair (2 / CTN): color: Rustic Pine or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rustic Pine or Brown&lt;br&gt;
-Weight: 299.32 lbs&lt;/p&gt;</t>
+Weight: 327.92 or 299.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" s="31" t="inlineStr">
@@ -18350,7 +18351,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18496,7 +18497,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -18643,7 +18644,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18786,7 +18787,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18929,7 +18930,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -19072,7 +19073,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -19217,7 +19218,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -19277,9 +19278,9 @@
 - Table Base w/ Chrome Trim&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - High Gloss Lacquer Coating Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 17" W x 25 1 or 2"D x 38 1 or 4" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Gray or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Others or Leatherette, Glass, Metal.&lt;br&gt;
+Color: Black or Gray or Chrome or White or Chrome&lt;br&gt;
 Weight: 304.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19364,7 +19365,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19418,17 +19419,15 @@
       <c r="G130" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GLENVIEW 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leatherette, Glass, Metal, then finished in Gray or Chrome tones to suit a range of interiors.&lt;br&gt;
+GLENVIEW 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leatherette, Glass, and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Gray or Chrome&lt;br&gt;
 - Table Base w/ Chrome Trim&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
-- High Gloss Lacquer Coating&lt;br&gt;
-- Padded Leatherette Chair w/ Chrome Legs Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Gray or Chrome; dimensions: 17" W x 25 1 or 2"D x 38 1 or 4" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass, Metal.&lt;br&gt;
-Color: Gray or Chrome&lt;br&gt;
+- High Gloss Lacquer Coating Included items and dimensions:&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Gray or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Others or Leatherette, Glass, Metal.&lt;br&gt;
+Color: Black or Gray or Chrome or White or Chrome&lt;br&gt;
 Weight: 304.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19513,7 +19512,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -19567,16 +19566,15 @@
       <c r="G131" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around GLENVIEW 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Leatherette, Glass, Metal construction and White or Chrome tones, it blends durability with visual warmth.&lt;br&gt;
+GLENVIEW 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leatherette, Glass, and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Chrome&lt;br&gt;
 - Table Base w/ Chrome Trim&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - High Gloss Lacquer Coating Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 25 1 or 2" W x 16 1 or 2"D x 30 1 or 2" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass, Metal.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Gray or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Others or Leatherette, Glass, Metal.&lt;br&gt;
+Color: Black or Gray or Chrome or White or Chrome&lt;br&gt;
 Weight: 304.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19661,7 +19659,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19803,7 +19801,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19944,7 +19942,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -20086,7 +20084,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -20227,7 +20225,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -20285,10 +20283,10 @@
 Product Dimensions: 70"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Marble Table Top Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Dark Walnut or Light Gray; dimensions: 21" W x 19.5"D x 34" H (SEAT HT: 21", SEAT DP: 17.5"); feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Marble, Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: Dark Walnut&lt;br&gt;
-Weight: 406.8 lbs&lt;/p&gt;</t>
+Weight: 406.8 or 532.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" s="35" t="inlineStr">
@@ -20372,7 +20370,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20426,14 +20424,14 @@
       <c r="G137" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around GRASTEN 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Marble, Rubberwood, Oak Veneer, Engineered Wood, then finished in Dark Walnut tones to suit a range of interiors.&lt;br&gt;
+GRASTEN 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Marble, Rubberwood, Oak Veneer, Engineered Wood and finished in Dark Walnut tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 70"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Marble Table Top Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: White; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Dark Walnut&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Marble, Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: Dark Walnut&lt;br&gt;
-Weight: 532.8 lbs&lt;/p&gt;</t>
+Weight: 406.8 or 532.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" s="35" t="inlineStr">
@@ -20517,7 +20515,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -20660,7 +20658,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20797,7 +20795,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -20940,7 +20938,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -21088,7 +21086,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -21235,7 +21233,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -21378,7 +21376,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -21526,7 +21524,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -21586,11 +21584,11 @@
 - Upholstered Seats&lt;br&gt;
 - Turned Fluted Legs&lt;br&gt;
 - Silverware Tray Storage &amp;amp; Wine Rack on Server Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black; dimensions: 84" W x 43"D x 30" H; feature: Glam&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 20" W x 23"D x 43" H; feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 306.9 lbs&lt;/p&gt;</t>
+- Dining Table: color: Black or Silver&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Silver&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
+Weight: 306.9 or 310.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="37" t="inlineStr">
@@ -21674,7 +21672,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21728,17 +21726,17 @@
       <c r="G146" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HANNORIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Finished in Silver tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+HANNORIA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: Table: 84"L X 43"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Upholstered Seats&lt;br&gt;
 - Turned Fluted Legs&lt;br&gt;
 - Silverware Tray Storage &amp;amp; Wine Rack on Server Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Silver; dimensions: 84" W x 43"D x 30" H; feature: Glam&lt;br&gt;
-- Side Chair (2 / CTN): color: Silver; dimensions: 20" W x 23"D x 43" H; feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 310.2 lbs&lt;/p&gt;</t>
+- Dining Table: color: Black or Silver&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Silver&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
+Weight: 306.9 or 310.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="37" t="inlineStr">
@@ -21822,7 +21820,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -21968,7 +21966,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -22114,7 +22112,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -22260,7 +22258,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -22373,7 +22371,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -22435,11 +22433,11 @@
 - Option of 3 Chair Colors&lt;br&gt;
 - Spindle Back&lt;br&gt;
 - Molded Seats Included items and dimensions:&lt;br&gt;
-- Oval Dining Table: color: White Oak; dimensions: 78"(60" and 1 x 18" LEAF)W x 42"D x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: White Oak; dimensions: 20.5" W x 20.5"D x 32.5" H (SEAT HT: 18", SEAT DP: 16.5"); feature: Mid-Century Modern&lt;/p&gt;
+- Oval Dining Table: color: White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: White Oak&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: White Oak&lt;br&gt;
-Weight: 260.13 lbs&lt;/p&gt;</t>
+Weight: 260.13 or 261.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="39" t="inlineStr">
@@ -22527,7 +22525,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22585,21 +22583,19 @@
       <c r="G152" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HINES 7 Pc. Oval Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Rubberwood, Oak Veneer, Engineered Wood construction and White Oak tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 78"(60" + 1 X 18" LEAF)W X 42"D X 30"H&lt;br&gt;
-Size: (2Bk and 4Nt)&lt;/p&gt;
+Gather around HINES 7 Pc. Oval Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Rubberwood, Oak Veneer, Engineered Wood, then finished in White Oak tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 78"(60" + 1 X 18" LEAF)W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Table Extendable w/ Leaf&lt;br&gt;
 - Double Pedestal Base&lt;br&gt;
 - Option of 3 Chair Colors&lt;br&gt;
 - Spindle Back&lt;br&gt;
 - Molded Seats Included items and dimensions:&lt;br&gt;
-- Oval Dining Table: color: White Oak; dimensions: 78"(60" and 1 x 18" LEAF)W x 42"D x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 20.5" W x 20.5"D x 32.5" H (SEAT HT: 18", SEAT DP: 16.5"); feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: White Oak; dimensions: 20.5" W x 20.5"D x 32.5" H (SEAT HT: 18", SEAT DP: 16.5"); feature: Mid-Century Modern&lt;/p&gt;
+- Oval Dining Table: color: White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: White Oak&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: White Oak&lt;br&gt;
-Weight: 261.16 lbs&lt;/p&gt;</t>
+Weight: 260.13 or 261.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="39" t="inlineStr">
@@ -22687,7 +22683,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -22742,15 +22738,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 HINWITZ 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Espresso tones, the Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: Table: 42.01"L X 89.96"W X 30"H&lt;/p&gt;
+Product Dimensions: Table: 42.01"L X 89.96"W X 30"H / 90"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Faceted Panel Back Chair&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Espresso; dimensions: 90" W x 42"D x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Espresso or Dark Gray; dimensions: 18.5" W x 24"D x 38" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 298.1 lbs&lt;/p&gt;</t>
+- Dining Table: color: Espresso or White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Espresso or White Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Poplar &amp; Pine Wood, Oak Veneer, Others.&lt;br&gt;
+Color: Espresso or White Oak&lt;br&gt;
+Weight: 298.1 or 303.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="41" t="inlineStr">
@@ -22834,7 +22830,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -22888,16 +22884,16 @@
       <c r="G154" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around HINWITZ 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer, and finished in White Oak tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 90"W X 42"D X 30"H&lt;/p&gt;
+HINWITZ 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Espresso tones, the Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 42.01"L X 89.96"W X 30"H / 90"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Faceted Panel Back Chair&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Dining Table: color: White Oak; dimensions: 90" W x 42"D x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: White Oak or Dark Gray; dimensions: 18.5" W x 24"D x 38" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer.&lt;br&gt;
-Color: White Oak&lt;br&gt;
-Weight: 303.6 lbs&lt;/p&gt;</t>
+- Dining Table: color: Espresso or White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Espresso or White Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Poplar &amp; Pine Wood, Oak Veneer, Others.&lt;br&gt;
+Color: Espresso or White Oak&lt;br&gt;
+Weight: 298.1 or 303.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="41" t="inlineStr">
@@ -22981,7 +22977,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -23040,11 +23036,11 @@
 &lt;p&gt;Features&lt;br&gt;
 - Faceted Panel Back Chair&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Espresso; dimensions: 90" W x 42"D x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: Espresso or Dark Gray; dimensions: 18.5" W x 24"D x 38" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 343.2 lbs&lt;/p&gt;</t>
+- Dining Table: color: Espresso or White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Espresso or White Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Poplar &amp; Pine Wood, Oak Veneer, Others.&lt;br&gt;
+Color: Espresso or White Oak&lt;br&gt;
+Weight: 343.2 or 352 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -23128,7 +23124,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -23182,16 +23178,16 @@
       <c r="G156" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HINWITZ 9 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer, construction and White Oak tones, it blends durability with visual warmth.&lt;br&gt;
+HINWITZ 9 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer, then finished in Espresso tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: Table: 42.01"L X 89.96"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Faceted Panel Back Chair&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Dining Table: color: White Oak; dimensions: 90" W x 42"D x 30" H; feature: Transitional&lt;br&gt;
-- Side Chair (2 / CTN): color: White Oak or Dark Gray; dimensions: 18.5" W x 24"D x 38" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Poplar &amp;amp; Pine Wood, Oak Veneer.&lt;br&gt;
-Color: White Oak&lt;br&gt;
-Weight: 352 lbs&lt;/p&gt;</t>
+- Dining Table: color: Espresso or White Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Espresso or White Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Poplar &amp; Pine Wood, Oak Veneer, Others.&lt;br&gt;
+Color: Espresso or White Oak&lt;br&gt;
+Weight: 343.2 or 352 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
@@ -23275,7 +23271,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -23419,7 +23415,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -23563,7 +23559,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -23705,7 +23701,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23847,7 +23843,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -23990,7 +23986,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -24132,7 +24128,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -24275,7 +24271,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -24418,7 +24414,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -24563,7 +24559,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -24708,7 +24704,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -24853,7 +24849,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -24998,7 +24994,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -25059,9 +25055,9 @@
 - Bold Chrome Legs&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 17 1 or 4" W x 22 3 or 8"D x 40" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Chrome or Black or Chrome or White&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal or Leatherette, Chrome, Tempered Glass.&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 192.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25146,7 +25142,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -25200,16 +25196,16 @@
       <c r="G170" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KALAWAO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Chrome or White tones, the Leatherette, Chrome, Tempered Glass build keeps the look polished and practical.&lt;br&gt;
+Gather around KALAWAO 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Glass, Metal construction and Chrome or Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 59"L X 35 1/2"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or White&lt;br&gt;
+- Chrome or Black&lt;br&gt;
 - Bold Chrome Legs&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 17 1 or 4" W x 22 3 or 8"D x 40" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Chrome, Tempered Glass.&lt;br&gt;
-Color: Chrome or White&lt;br&gt;
+- Side Chair (2 / CTN): color: Chrome or Black or Chrome or White&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal or Leatherette, Chrome, Tempered Glass.&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 192.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25294,7 +25290,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -25357,9 +25353,9 @@
 - Hanging Stemware Rack&lt;br&gt;
 - Wine Bottle Storage&lt;br&gt;
 - Felt-lined Drawer Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Rustic Oak or Beige; dimensions: 21" W x 25 1 or 2"D x 37 3 or 4" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Oak or Beige&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Oak or Beige or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Oak or Beige or Antique White&lt;br&gt;
 Weight: 187.44 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25444,7 +25440,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -25498,17 +25494,18 @@
       <c r="G172" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around KATHRYN 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, Wood Veneer, construction and Antique White tones, it blends durability with visual warmth.&lt;br&gt;
+KATHRYN 5 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in Rustic Oak or Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 48"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Rustic Oak or Beige&lt;br&gt;
 - Pedestal Base&lt;br&gt;
 - Padded Fabric Seat&lt;br&gt;
 - Hanging Stemware Rack&lt;br&gt;
 - Wine Bottle Storage&lt;br&gt;
 - Felt-lined Drawer Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Antique White or Gray; dimensions: 21" W x 24 1 or 2"D x 37 3 or 4" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique White&lt;br&gt;
+- Side Chair (2 / CTN): color: Rustic Oak or Beige or Antique White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rustic Oak or Beige or Antique White&lt;br&gt;
 Weight: 187.44 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25593,7 +25590,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25739,7 +25736,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -25883,7 +25880,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -26026,7 +26023,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -26169,7 +26166,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -26312,7 +26309,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -26447,7 +26444,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -26507,10 +26504,10 @@
 - Bold Chrome Legs&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 21 1 or 2" W x 20"D x 33" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 147.1 lbs&lt;/p&gt;</t>
+Color: Black or White&lt;br&gt;
+Weight: 147.1 or 147.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" s="19" t="inlineStr">
@@ -26594,7 +26591,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -26648,16 +26645,16 @@
       <c r="G180" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KONA I 5 Pc. Round Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Glass, Metal, then finished in White tones to suit a range of interiors.&lt;br&gt;
+KONA I 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Glass, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 45"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bold Chrome Legs&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 21 1 or 2" W x 20"D x 33" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 147.3 lbs&lt;/p&gt;</t>
+Color: Black or White&lt;br&gt;
+Weight: 147.1 or 147.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="19" t="inlineStr">
@@ -26741,7 +26738,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -26889,7 +26886,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -27036,7 +27033,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -27097,10 +27094,10 @@
 - Ceramic Table Top&lt;br&gt;
 - Powder-Coated Iron X-Shaped Pedestal Base&lt;br&gt;
 - Fully Upholstered Chair in Leatherette w/ Top Stitching Creating an Arch Design Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black or White; dimensions: 19" L x 23" W x 32" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White or Brown or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Ceramic, Metal.&lt;br&gt;
-Color: Black or White&lt;br&gt;
-Weight: 350.6 lbs&lt;/p&gt;</t>
+Color: Black or White or Brown or White&lt;br&gt;
+Weight: 350.6 or 351.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" s="21" t="inlineStr">
@@ -27184,7 +27181,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -27238,17 +27235,17 @@
       <c r="G184" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around LENVIK 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Foam, Ceramic, Metal, then finished in Brown or White tones to suit a range of interiors.&lt;br&gt;
+LENVIK 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Foam, Ceramic, Metal and finished in Black or White tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 71"W X 35"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Brown or White&lt;br&gt;
+- Black or White&lt;br&gt;
 - Ceramic Table Top&lt;br&gt;
 - Powder-Coated Iron X-Shaped Pedestal Base&lt;br&gt;
 - Fully Upholstered Chair in Leatherette w/ Top Stitching Creating an Arch Design Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Brown; dimensions: 19" L x 23" W x 32" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White or Brown or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Ceramic, Metal.&lt;br&gt;
-Color: Brown or White&lt;br&gt;
-Weight: 351.3 lbs&lt;/p&gt;</t>
+Color: Black or White or Brown or White&lt;br&gt;
+Weight: 350.6 or 351.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" s="21" t="inlineStr">
@@ -27332,7 +27329,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -27473,7 +27470,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -27621,7 +27618,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -27679,9 +27676,9 @@
 Product Dimensions: 48"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Leatherette Chair W or Chrome Legs Included items and dimensions:&lt;br&gt;
-- I Side Chair (2 / CTN): color: Black or Chrome; dimensions: 17" W x 21"D x 36" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Tempered Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+- I Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Tempered Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 208.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27766,7 +27763,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -27820,13 +27817,13 @@
       <c r="G188" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LODIA I 5 Pc. Round Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in White tones, the Leatherette, Tempered Glass, build keeps the look polished and practical.&lt;br&gt;
+Gather around LODIA I 5 Pc. Round Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Leatherette, Tempered Glass, construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 48"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Leatherette Chair W or Chrome Legs Included items and dimensions:&lt;br&gt;
-- I Side Chair (2 / CTN): color: White; dimensions: 17" W x 21"D x 36" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Tempered Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+- I Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Tempered Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 208.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27911,7 +27908,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -27969,9 +27966,9 @@
 Product Dimensions: 63"L X 35 1/2"W X 30H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Leatherette Chair W or Chrome Legs Included items and dimensions:&lt;br&gt;
-- I Side Chair (2 / CTN): color: Black or Chrome; dimensions: 17" W x 21"D x 36" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Tempered Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+- I Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Tempered Glass, Others or Leatherete, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 269.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28056,7 +28053,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -28110,13 +28107,13 @@
       <c r="G190" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around LODIA I 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Leatherete, Tempered Glass, Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+LODIA I 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Tempered Glass, and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 63"L X 35 1/2"W X 30H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Leatherette Chair W or Chrome Legs Included items and dimensions:&lt;br&gt;
-- I Side Chair (2 / CTN): color: White; dimensions: 17" W x 21"D x 36" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherete, Tempered Glass, Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+- I Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Tempered Glass, Others or Leatherete, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 269.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28201,7 +28198,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -28344,7 +28341,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -28487,7 +28484,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -28634,7 +28631,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -28775,7 +28772,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -28920,7 +28917,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -29064,7 +29061,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -29207,7 +29204,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -29351,7 +29348,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -29495,7 +29492,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29554,8 +29551,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - 12mm Beveled Glass Top&lt;br&gt;
 - Available in 2 Table Types Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Dark Cherry or Brown; dimensions: 20" W x 24"D x 41" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass, Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
 Weight: 341.3 lbs&lt;/p&gt;</t>
         </is>
@@ -29641,7 +29638,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -29695,13 +29692,13 @@
       <c r="G201" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MANHATTAN 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Tempered Glass, Leatherette, Solid Wood, Wood Veneer, then finished in Brown Cherry tones to suit a range of interiors.&lt;br&gt;
+MANHATTAN 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Tempered Glass, Leatherette, Solid Wood, Wood Veneer, and finished in Brown Cherry tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 72"L X 42"W X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - 12mm Beveled Glass Top&lt;br&gt;
 - Available in 2 Table Types Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Dark Cherry or White; dimensions: 20" W x 24"D x 41" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass, Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
 Weight: 341.3 lbs&lt;/p&gt;</t>
         </is>
@@ -29787,7 +29784,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -29928,7 +29925,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -30072,7 +30069,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -30213,7 +30210,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -30274,9 +30271,9 @@
 - Square Pedestal Design&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 17" W x 22"D x 38" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Glass, Lacquer, Solid Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 181.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30361,7 +30358,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -30415,16 +30412,16 @@
       <c r="G206" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MAUNA 5 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Glass, Lacquer, Solid Wood and finished in White tones for a clean, cohesive look.&lt;br&gt;
+MAUNA 5 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black tones, the Leatherette, Glass, Lacquer, Solid Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 45"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - High Gloss Lacquer Coating&lt;br&gt;
 - Square Pedestal Design&lt;br&gt;
 - 12mm Tempered Glass Top&lt;br&gt;
 - Available in 2 Colors Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 17" W x 22"D x 38" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Glass, Lacquer, Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 181.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30509,7 +30506,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -30654,7 +30651,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -30799,7 +30796,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -30854,15 +30851,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MELINA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and Brown Cherry tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 88"L X 46"W X 30"H ( Up To 31"H&lt;/p&gt;
+Product Dimensions: 88"L X 46"W X 30"H ( Up To 31"H / 88"W X 46"D X 30 - 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Inter-Changeable Design&lt;br&gt;
 - Double Pedestal Base&lt;br&gt;
 - Built-In Cup Holders Included items and dimensions:&lt;br&gt;
-- Arm Chair: color: Brown Cherry or Black; dimensions: ARM CHAIR: 26 1 or 4" W x 29"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Brown Cherry&lt;br&gt;
-Weight: 492.5 lbs&lt;/p&gt;</t>
+- Arm Chair: color: Brown Cherry or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Brown Cherry or Gray&lt;br&gt;
+Weight: 492.5 or 491.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" s="31" t="inlineStr">
@@ -30946,7 +30943,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -31000,16 +30997,16 @@
       <c r="G210" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around MELINA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 88"W X 46"D X 30 - 31"H&lt;/p&gt;
+MELINA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and Brown Cherry tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 88"L X 46"W X 30"H ( Up To 31"H / 88"W X 46"D X 30 - 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Inter-Changeable Design&lt;br&gt;
 - Double Pedestal Base&lt;br&gt;
 - Built-In Cup Holders Included items and dimensions:&lt;br&gt;
-- Arm Chair: color: Gray; dimensions: 26" W x 29"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 491.2 lbs&lt;/p&gt;</t>
+- Arm Chair: color: Brown Cherry or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Brown Cherry or Gray&lt;br&gt;
+Weight: 492.5 or 491.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" s="31" t="inlineStr">
@@ -31093,7 +31090,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -31148,15 +31145,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MIDVALE 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leatherette, Metal, Engineered Wood, then finished in Black or Chrome tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 78"(64"+ 1 X 14" LEAF)L X 42"W X 30"H&lt;/p&gt;
+Product Dimensions: 78"(64"+ 1 X 14" LEAF)L X 42"W X 30"H / 78"(64" + 1 X 14"LEAF)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or Chrome&lt;br&gt;
 - High Gloss Lacquer Coating&lt;br&gt;
 - 14" Expandable Leaf&lt;br&gt;
 - Table Base w/ Chrome Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black or Chrome; dimensions: 24 1 or 2" W x 18"D x 37 1 or 2" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Metal, Engineered Wood.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 366.49 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -31241,7 +31238,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -31295,18 +31292,16 @@
       <c r="G212" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around MIDVALE 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Leatherette, Metal, Engineered Wood construction and White or Chrome tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 78"(64" + 1 X 14"LEAF)L X 42"W X 30"H&lt;/p&gt;
+MIDVALE 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leatherette, Metal, Engineered Wood, then finished in Black or Chrome tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 78"(64"+ 1 X 14" LEAF)L X 42"W X 30"H / 78"(64" + 1 X 14"LEAF)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Chrome&lt;br&gt;
-- 14" Butterfly Leaf&lt;br&gt;
-- Z-Shaped Chair Base&lt;br&gt;
-- Easy Leaf Expansion&lt;br&gt;
+- Black or Chrome&lt;br&gt;
 - High Gloss Lacquer Coating&lt;br&gt;
+- 14" Expandable Leaf&lt;br&gt;
 - Table Base w/ Chrome Trim Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White or Chrome; dimensions: 18" W x 24 1 or 2"D x 37 1 or 2" H; feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Metal, Engineered Wood.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 366.49 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -31391,7 +31386,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -31537,7 +31532,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -31680,7 +31675,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -31741,10 +31736,10 @@
 - Marble Table Top&lt;br&gt;
 - Reeded Plinth Base with Gold Trim&lt;br&gt;
 - Removable Back Pillow on 6 Casters Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: White; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Marble, Engineered Wood, Metal.&lt;br&gt;
 Color: Black or White&lt;br&gt;
-Weight: 394.96 lbs&lt;/p&gt;</t>
+Weight: 394.96 or 393.36 or 429.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" s="35" t="inlineStr">
@@ -31828,7 +31823,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -31882,17 +31877,17 @@
       <c r="G216" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORGES 5 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Boucle Chenille Fabric, Marble, Engineered Wood, Metal, then finished in Black or White tones to suit a range of interiors.&lt;br&gt;
+Gather around MORGES 5 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle Chenille Fabric, Marble, Engineered Wood, Metal and finished in Black or White tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 72"W X 40"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or White&lt;br&gt;
 - Marble Table Top&lt;br&gt;
 - Reeded Plinth Base with Gold Trim&lt;br&gt;
 - Removable Back Pillow on 6 Casters Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: Light Gray; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Marble, Engineered Wood, Metal.&lt;br&gt;
 Color: Black or White&lt;br&gt;
-Weight: 393.36 lbs&lt;/p&gt;</t>
+Weight: 394.96 or 393.36 or 429.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" s="35" t="inlineStr">
@@ -31976,7 +31971,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -32030,17 +32025,17 @@
       <c r="G217" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORGES 5 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Boucle Chenille Fabric, Marble, Engineered Wood, Metal construction and Black or White tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around MORGES 5 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle Chenille Fabric, Marble, Engineered Wood, Metal and finished in Black or White tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 72"W X 40"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or White&lt;br&gt;
 - Marble Table Top&lt;br&gt;
 - Reeded Plinth Base with Gold Trim&lt;br&gt;
-- Swivel Chair Rotates 360° Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: White; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Removable Back Pillow on 6 Casters Included items and dimensions:&lt;br&gt;
+- Dining Chair w/ Caster: color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Marble, Engineered Wood, Metal.&lt;br&gt;
 Color: Black or White&lt;br&gt;
-Weight: 429.76 lbs&lt;/p&gt;</t>
+Weight: 394.96 or 393.36 or 429.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" s="35" t="inlineStr">
@@ -32124,7 +32119,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -32265,7 +32260,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -32382,7 +32377,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -32443,9 +32438,9 @@
 - Antique Black or Ivory&lt;br&gt;
 - Pedestal base&lt;br&gt;
 - Button Tufted Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
 Weight: 198.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32530,7 +32525,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -32584,16 +32579,16 @@
       <c r="G221" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NERISSA 5 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and Antique Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around NERISSA 5 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 48"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Pedestal base&lt;br&gt;
 - Button Tufted Included items and dimensions:&lt;br&gt;
-- III Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
 Weight: 198.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32678,7 +32673,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -32739,9 +32734,9 @@
 - Trestle Base&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Scrolled Chair Backs Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Antique Black or Gray&lt;br&gt;
 Weight: 323.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32826,7 +32821,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -32880,17 +32875,16 @@
       <c r="G223" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around NERISSA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Linen-like Fabric, Solid Wood, Wood Veneer, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
+NERISSA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black tones, the Linen-like Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 84"W X 42"D X 30 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Scrolled Chair Backs Included items and dimensions:&lt;br&gt;
-- III Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Antique Black or Gray&lt;br&gt;
 Weight: 323.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32975,7 +32969,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -33038,10 +33032,10 @@
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Black; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
-Weight: 327.3 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H224" s="41" t="inlineStr">
@@ -33125,7 +33119,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -33179,8 +33173,7 @@
       <c r="G225" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEUVEVILLE 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Flannelette, Stainless Steel,Tempered Glass construction and Black or Chrome tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 79"L X 39"W X 3"H&lt;/p&gt;
+NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in Black or Chrome tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or Chrome&lt;br&gt;
 - 12mm Beveled Tempered Glass Top&lt;br&gt;
@@ -33189,10 +33182,10 @@
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Gray; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
-Weight: 324.39 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H225" s="41" t="inlineStr">
@@ -33280,7 +33273,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -33334,7 +33327,7 @@
       <c r="G226" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around NEUVEVILLE 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Black or Chrome tones, the Flannelette, Stainless Steel,Tempered Glass build keeps the look polished and practical.&lt;/p&gt;
+NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in Black or Chrome tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or Chrome&lt;br&gt;
 - 12mm Beveled Tempered Glass Top&lt;br&gt;
@@ -33343,10 +33336,10 @@
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Blue; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
-Weight: 327.3 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H226" s="41" t="inlineStr">
@@ -33430,7 +33423,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -33484,19 +33477,19 @@
       <c r="G227" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Built from Flannelette, Stainless Steel, Tempered Glass and finished in White or Chrome tones for a clean, cohesive look.&lt;/p&gt;
+NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in Black or Chrome tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Chrome&lt;br&gt;
+- Black or Chrome&lt;br&gt;
 - 12mm Beveled Tempered Glass Top&lt;br&gt;
 - Metal Construction&lt;br&gt;
 - Cabriole Legs&lt;br&gt;
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Black; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
-Weight: 327.3 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H227" s="41" t="inlineStr">
@@ -33580,7 +33573,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -33634,20 +33627,19 @@
       <c r="G228" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEUVEVILLE 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in White or Chrome tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 79"L X 39"W X 3"H&lt;/p&gt;
+NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in Black or Chrome tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Chrome&lt;br&gt;
+- Black or Chrome&lt;br&gt;
 - 12mm Beveled Tempered Glass Top&lt;br&gt;
 - Metal Construction&lt;br&gt;
 - Cabriole Legs&lt;br&gt;
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Gray; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
-Weight: 324.39 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H228" s="41" t="inlineStr">
@@ -33735,7 +33727,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -33789,19 +33781,19 @@
       <c r="G229" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around NEUVEVILLE 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. With Flannelette, Stainless Steel,Tempered Glass construction and White or Chrome tones, it blends durability with visual warmth.&lt;/p&gt;
+NEUVEVILLE 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Flannelette, Stainless Steel,Tempered Glass, then finished in Black or Chrome tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Chrome&lt;br&gt;
+- Black or Chrome&lt;br&gt;
 - 12mm Beveled Tempered Glass Top&lt;br&gt;
 - Metal Construction&lt;br&gt;
 - Cabriole Legs&lt;br&gt;
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Blue; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
-Weight: 327.3 lbs&lt;/p&gt;</t>
+- Chair (2 / CTN): color: Black or Chrome or White or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Stainless Steel,Tempered Glass or Flannelette, Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
+Weight: 327.3 or 324.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H229" s="41" t="inlineStr">
@@ -33885,7 +33877,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -34030,7 +34022,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -34091,10 +34083,10 @@
 - Ceramic Table Top&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Fully Upholstered Round Chair in Leatherette Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Gold or Taupe; dimensions: 19" W x 23"D x 32" H (SEAT HT: 19", SEAT DP: 18"); feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Gold or White or Silver or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Ceramic, Metal.&lt;br&gt;
-Color: Gold or White&lt;br&gt;
-Weight: 253.7 lbs&lt;/p&gt;</t>
+Color: Gold or White or Silver or White&lt;br&gt;
+Weight: 253.7 or 250.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H231" s="13" t="inlineStr">
@@ -34178,7 +34170,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -34232,17 +34224,17 @@
       <c r="G232" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NORELLI 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Foam, Ceramic, Metal and finished in Silver or White tones for a clean, cohesive look.&lt;br&gt;
+NORELLI 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gold or White tones, the Fabric, Foam, Ceramic, Metal build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 71"W X 35"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Silver or White&lt;br&gt;
+- Gold or White&lt;br&gt;
 - Ceramic Table Top&lt;br&gt;
 - Trestle Base&lt;br&gt;
 - Fully Upholstered Round Chair in Leatherette Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Silver or Taupe; dimensions: 19" W x 23"D x 32" H (SEAT HT: 19", SEAT DP: 18"); feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Gold or White or Silver or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Ceramic, Metal.&lt;br&gt;
-Color: Silver or White&lt;br&gt;
-Weight: 250.8 lbs&lt;/p&gt;</t>
+Color: Gold or White or Silver or White&lt;br&gt;
+Weight: 253.7 or 250.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H232" s="13" t="inlineStr">
@@ -34326,7 +34318,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -34473,7 +34465,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -34614,7 +34606,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -34730,7 +34722,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -34846,7 +34838,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -34962,7 +34954,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -35078,7 +35070,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -35194,7 +35186,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -35310,7 +35302,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -35459,7 +35451,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -35603,7 +35595,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -35749,7 +35741,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -35895,7 +35887,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -36042,7 +36034,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -36183,7 +36175,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -36322,7 +36314,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -36463,7 +36455,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -36605,7 +36597,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -36750,7 +36742,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -36896,7 +36888,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36957,8 +36949,8 @@
 - Cross-Shaped Pedestal Base&lt;br&gt;
 - Tiger-Printed Leatherette Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel.&lt;br&gt;
-Color: Gold or Black&lt;br&gt;
-Weight: 677.62 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Silver or Chrome or Black or Chrome or Silver or Glam&lt;br&gt;
+Weight: 677.62 or 666.28 or 675.5 or 660.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" s="15" t="inlineStr">
@@ -37042,7 +37034,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -37096,15 +37088,15 @@
       <c r="G253" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PALAZZO 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Built from Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel and finished in Gold or Silver tones for a clean, cohesive look.&lt;br&gt;
+PALAZZO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Gold or Black tones, the Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Gold or Silver&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - Cross-Shaped Pedestal Base&lt;br&gt;
 - Tiger-Printed Leatherette Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel.&lt;br&gt;
-Color: Gold or Silver&lt;br&gt;
-Weight: 666.28 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Silver or Chrome or Black or Chrome or Silver or Glam&lt;br&gt;
+Weight: 677.62 or 666.28 or 675.5 or 660.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" s="15" t="inlineStr">
@@ -37188,7 +37180,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -37242,15 +37234,15 @@
       <c r="G254" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around PALAZZO 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel, then finished in Chrome or Black tones to suit a range of interiors.&lt;br&gt;
+PALAZZO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Gold or Black tones, the Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Black&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - Cross-Shaped Pedestal Base&lt;br&gt;
 - Tiger-Printed Leatherette Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
-Weight: 675.5 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Silver or Chrome or Black or Chrome or Silver or Glam&lt;br&gt;
+Weight: 677.62 or 666.28 or 675.5 or 660.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" s="15" t="inlineStr">
@@ -37334,7 +37326,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -37388,15 +37380,15 @@
       <c r="G255" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PALAZZO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. With Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel construction and Chrome or Silver tones, it blends durability with visual warmth.&lt;br&gt;
+PALAZZO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Gold or Black tones, the Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Silver&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - Cross-Shaped Pedestal Base&lt;br&gt;
 - Tiger-Printed Leatherette Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel.&lt;br&gt;
-Color: Chrome or Silver&lt;br&gt;
-Weight: 660.98 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Silver or Chrome or Black or Chrome or Silver or Glam&lt;br&gt;
+Weight: 677.62 or 666.28 or 675.5 or 660.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" s="15" t="inlineStr">
@@ -37480,7 +37472,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37534,14 +37526,15 @@
       <c r="G256" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PALAZZO 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Finished in Glam tones, the Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
+PALAZZO 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Gold or Black tones, the Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - Cross-Shaped Pedestal Base&lt;br&gt;
 - Tiger-Printed Leatherette Upholstered Chairs with Saber Legs&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Sintered Stone Top, Stainless Steel, Stainless Steel.&lt;br&gt;
-Color: Glam&lt;br&gt;
-Weight: 675.5 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Gold or Silver or Chrome or Black or Chrome or Silver or Glam&lt;br&gt;
+Weight: 677.62 or 666.28 or 675.5 or 660.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H256" s="15" t="inlineStr">
@@ -37625,7 +37618,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -37770,7 +37763,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -37915,7 +37908,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -38059,7 +38052,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -38208,7 +38201,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -38351,7 +38344,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -38412,10 +38405,10 @@
 - Horseshoe-Shaped Pedestal Base Design&lt;br&gt;
 - Diamond Pattern Upholstered Chairs w/ Nailhead Trim&lt;br&gt;
 - Square Legs Included items and dimensions:&lt;br&gt;
-- Gold Chair (2 / CTN): color: Black; dimensions: 20" W x 20"D x 36" H (SEAT HT: 19", SEAT DP: 20.5"); feature: Glam&lt;/p&gt;
+- Gold Chair (2 / CTN): color: Gold or Black or Chrome or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone, Stainless Steel.&lt;br&gt;
-Color: Gold or Black&lt;br&gt;
-Weight: 625.16 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Chrome or White&lt;br&gt;
+Weight: 625.16 or 626.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="17" t="inlineStr">
@@ -38499,7 +38492,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -38553,17 +38546,17 @@
       <c r="G263" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PORTANOVA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. With Fabric, Sintered Stone, Stainless Steel construction and Chrome or White tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around PORTANOVA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Sintered Stone, Stainless Steel, then finished in Gold or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 79"W X 39"D X 31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or White&lt;br&gt;
+- Gold or Black&lt;br&gt;
 - Horseshoe-Shaped Pedestal Base Design&lt;br&gt;
 - Diamond Pattern Upholstered Chairs w/ Nailhead Trim&lt;br&gt;
 - Square Legs Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: White; dimensions: 20" W x 20"D x 36" H (SEAT HT: 19", SEAT DP: 20.5"); feature: Glam&lt;/p&gt;
+- Gold Chair (2 / CTN): color: Gold or Black or Chrome or White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Sintered Stone, Stainless Steel.&lt;br&gt;
-Color: Chrome or White&lt;br&gt;
-Weight: 626.02 lbs&lt;/p&gt;</t>
+Color: Gold or Black or Chrome or White&lt;br&gt;
+Weight: 625.16 or 626.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" s="17" t="inlineStr">
@@ -38647,7 +38640,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -38789,7 +38782,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -38936,7 +38929,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -39083,7 +39076,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -39229,7 +39222,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -39374,7 +39367,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -39491,7 +39484,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -39608,7 +39601,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -39669,9 +39662,9 @@
 - 10mm Clear Tempered Glass Top&lt;br&gt;
 - Tapered Legs&lt;br&gt;
 - Bold Legs on Table Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: Silver or Chrome; dimensions: 39 3 or 8" L x 39 3 or 8" W x 36" H; feature: Contemporary&lt;br&gt;
-- II Counter Height Chair (2 / CTN): color: White; dimensions: 21" W x 20"D x 38 1 or 2" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass, Metal.&lt;br&gt;
+- Counter Height Table: color: Silver or Chrome&lt;br&gt;
+- II Counter Height Chair (2 / CTN): color: Silver or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Metal, Others.&lt;br&gt;
 Color: Silver or Chrome&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
@@ -39757,7 +39750,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD271" t="inlineStr">
@@ -39811,16 +39804,16 @@
       <c r="G272" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around RICHFIELD 5 Pc. Round Counter Height Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Glass, Metal, then finished in Silver or Chrome tones to suit a range of interiors.&lt;br&gt;
+RICHFIELD 5 Pc. Round Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Glass, Metal, and finished in Silver or Chrome tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 39 3/8"L X 39 3/8"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Silver or Chrome&lt;br&gt;
 - 10mm Clear Tempered Glass Top&lt;br&gt;
 - Tapered Legs&lt;br&gt;
 - Bold Legs on Table Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: Silver or Chrome; dimensions: 39 3 or 8" L x 39 3 or 8" W x 36" H; feature: Contemporary&lt;br&gt;
-- II Counter Height Chair (2 / CTN): color: Black; dimensions: 21" W x 20"D x 38 1 or 2" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass, Metal.&lt;br&gt;
+- Counter Height Table: color: Silver or Chrome&lt;br&gt;
+- II Counter Height Chair (2 / CTN): color: Silver or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Metal, Others.&lt;br&gt;
 Color: Silver or Chrome&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
@@ -39906,7 +39899,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD272" t="inlineStr">
@@ -39970,10 +39963,10 @@
 - 12mm Clear Tempered Bottom Glass&lt;br&gt;
 - Padded Chair&lt;br&gt;
 - Chrome Legs Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 17" W x 22"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Leatherette, Metal.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
-Weight: 262 lbs&lt;/p&gt;</t>
+- Side Chair (2 / CTN): color: Black or Chrome or Silver or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Metal, Others.&lt;br&gt;
+Color: Black or Chrome or Silver or Chrome&lt;br&gt;
+Weight: 262 or 249.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H273" s="21" t="inlineStr">
@@ -40057,7 +40050,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -40111,19 +40104,20 @@
       <c r="G274" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RICHFIELD 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Silver or Chrome tones, the Glass, Leatherette, Metal, build keeps the look polished and practical.&lt;br&gt;
+RICHFIELD 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Glass, Leatherette, Metal, construction and Black or Chrome tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 59"L X 35 5/8"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Silver or Chrome&lt;br&gt;
+- Black or Chrome&lt;br&gt;
 - Dual Post Chrome Table Base&lt;br&gt;
 - Curved Glass Edges&lt;br&gt;
 - 10mm Clear Tempered Glass Top&lt;br&gt;
 - 12mm Clear Tempered Bottom Glass&lt;br&gt;
-- Padded Chair Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 17" W x 22"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Glass, Leatherette, Metal.&lt;br&gt;
-Color: Silver or Chrome&lt;br&gt;
-Weight: 249.3 lbs&lt;/p&gt;</t>
+- Padded Chair&lt;br&gt;
+- Chrome Legs Included items and dimensions:&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Chrome or Silver or Chrome&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Leatherette, Metal, Others.&lt;br&gt;
+Color: Black or Chrome or Silver or Chrome&lt;br&gt;
+Weight: 262 or 249.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H274" s="21" t="inlineStr">
@@ -40207,7 +40201,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD274" t="inlineStr">
@@ -40349,7 +40343,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -40494,7 +40488,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -40636,7 +40630,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -40778,7 +40772,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -40920,7 +40914,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -41062,7 +41056,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -41205,7 +41199,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -41348,7 +41342,7 @@
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD282" t="inlineStr">
@@ -41491,7 +41485,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -41634,7 +41628,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD284" t="inlineStr">
@@ -41777,7 +41771,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -41920,7 +41914,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD286" t="inlineStr">
@@ -42063,7 +42057,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -42208,7 +42202,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD288" t="inlineStr">
@@ -42357,7 +42351,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -42422,11 +42416,11 @@
 - Beige Linen-like Fabric Chairs&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- 60" Counter Height Table: color: Antique Black; dimensions: 60" L x 30" W x 36" H; feature: Rustic&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 24"D x 42 1 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 173.2 lbs&lt;/p&gt;</t>
+- 60" Counter Height Table: color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others or Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+Weight: 173.2 or 192.6 or 177.4 or 182.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H290" s="25" t="inlineStr">
@@ -42510,7 +42504,7 @@
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
@@ -42564,172 +42558,175 @@
       <c r="G291" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around SANIA 5 Pc. Counter Height Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
+SANIA 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 60"L X 30"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
-- Bold Distressed Details&lt;br&gt;
-- Wingback Inspired Chairs&lt;br&gt;
-- Beige Linen-like Fabric&lt;br&gt;
-- Button Tufted w/ Nailhead Trim Included items and dimensions:&lt;br&gt;
-- 54" Square Counter Height Table: color: Antique Black; dimensions: 54" L x 54" W x 36" H; feature: Rustic&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Gray or Antique Black; dimensions: 20" W x 24"D x 42 1 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 192.6 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H291" s="25" t="inlineStr">
-        <is>
-          <t>SANIA 5 Pc. Counter Height Table Set | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I291" s="25" t="inlineStr">
-        <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J291" s="25" t="inlineStr">
-        <is>
-          <t>SANIA</t>
-        </is>
-      </c>
-      <c r="K291" s="25" t="inlineStr">
-        <is>
-          <t>5 Pc. Counter Height Table Set</t>
-        </is>
-      </c>
-      <c r="L291" s="25" t="n"/>
-      <c r="M291" s="25" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N291" s="25" t="inlineStr">
-        <is>
-          <t>CM3324BK-PT-54-VN, CM3564GY-PC-2PK</t>
-        </is>
-      </c>
-      <c r="O291" s="25" t="inlineStr">
-        <is>
-          <t>CM3324BK-PT.jpg,CM3564GY-PC-1.jpg,CM3324BK-PT-54-CLOSEUP.jpg,CM3324BK-PT-54-TOP.jpg,CM3324BK-PCW-NAIL.jpg,CM3324BK-PCW-FABRIC.jpg</t>
-        </is>
-      </c>
-      <c r="P291" s="25" t="n">
-        <v>569</v>
-      </c>
-      <c r="Q291" s="26" t="n">
-        <v>569</v>
-      </c>
-      <c r="R291" s="25" t="n">
-        <v>1467</v>
-      </c>
-      <c r="S291" s="25" t="n">
-        <v>192.6</v>
-      </c>
-      <c r="T291" s="25" t="inlineStr">
-        <is>
-          <t>60"L X 30"W X 36"H</t>
-        </is>
-      </c>
-      <c r="U291" s="25" t="inlineStr">
-        <is>
-          <t>Rustic</t>
-        </is>
-      </c>
-      <c r="V291" s="25" t="inlineStr">
-        <is>
-          <t>Fabric, Solid Wood, Wood Veneer, Others</t>
-        </is>
-      </c>
-      <c r="W291" s="25" t="inlineStr">
-        <is>
-          <t>Rustic,Antique Black/Gray,Fabric, Solid Wood, Wood Veneer, Others,Bold Distressed Details,Wingback Inspired Chairs,Beige Linen-like Fabric,Button Tufted w/ Nailhead Trim</t>
-        </is>
-      </c>
-      <c r="X291" s="25" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="Y291" s="25" t="n"/>
-      <c r="Z291" s="25" t="n"/>
-      <c r="AA291" s="25" t="n"/>
-      <c r="AB291" s="25" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE291" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG291" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="25" t="inlineStr">
-        <is>
-          <t>Antique Black, Ivory</t>
-        </is>
-      </c>
-      <c r="B292" s="25" t="n"/>
-      <c r="C292" s="25" t="inlineStr">
-        <is>
-          <t>CM3324BK-PT-5PC</t>
-        </is>
-      </c>
-      <c r="D292" s="25" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="E292" s="25" t="inlineStr">
-        <is>
-          <t>Dining Set</t>
-        </is>
-      </c>
-      <c r="F292" s="25" t="inlineStr">
-        <is>
-          <t>SANIA 5 Pc. Counter Height Table Set</t>
-        </is>
-      </c>
-      <c r="G292" s="25" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 5 Pc. Counter Height Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Antique Black, Ivory tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 60"L X 30"W X 36"H&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Rustic&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Center Beam for Support&lt;br&gt;
 - Beam Doubles as Footrest&lt;br&gt;
 - Beige Linen-like Fabric Chairs&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- 60" Counter Height Table: color: Antique Black; dimensions: 60" L x 30" W x 36" H; feature: Rustic&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Antique Black or Beige; dimensions: 19" W x 22 1 or 2"D x 42 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black, Ivory&lt;br&gt;
-Weight: 177.4 lbs&lt;/p&gt;</t>
+- 60" Counter Height Table: color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others or Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+Weight: 173.2 or 192.6 or 177.4 or 182.3 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H291" s="25" t="inlineStr">
+        <is>
+          <t>SANIA 5 Pc. Counter Height Table Set | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I291" s="25" t="inlineStr">
+        <is>
+          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J291" s="25" t="inlineStr">
+        <is>
+          <t>SANIA</t>
+        </is>
+      </c>
+      <c r="K291" s="25" t="inlineStr">
+        <is>
+          <t>5 Pc. Counter Height Table Set</t>
+        </is>
+      </c>
+      <c r="L291" s="25" t="n"/>
+      <c r="M291" s="25" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N291" s="25" t="inlineStr">
+        <is>
+          <t>CM3324BK-PT-54-VN, CM3564GY-PC-2PK</t>
+        </is>
+      </c>
+      <c r="O291" s="25" t="inlineStr">
+        <is>
+          <t>CM3324BK-PT.jpg,CM3564GY-PC-1.jpg,CM3324BK-PT-54-CLOSEUP.jpg,CM3324BK-PT-54-TOP.jpg,CM3324BK-PCW-NAIL.jpg,CM3324BK-PCW-FABRIC.jpg</t>
+        </is>
+      </c>
+      <c r="P291" s="25" t="n">
+        <v>569</v>
+      </c>
+      <c r="Q291" s="26" t="n">
+        <v>569</v>
+      </c>
+      <c r="R291" s="25" t="n">
+        <v>1467</v>
+      </c>
+      <c r="S291" s="25" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="T291" s="25" t="inlineStr">
+        <is>
+          <t>60"L X 30"W X 36"H</t>
+        </is>
+      </c>
+      <c r="U291" s="25" t="inlineStr">
+        <is>
+          <t>Rustic</t>
+        </is>
+      </c>
+      <c r="V291" s="25" t="inlineStr">
+        <is>
+          <t>Fabric, Solid Wood, Wood Veneer, Others</t>
+        </is>
+      </c>
+      <c r="W291" s="25" t="inlineStr">
+        <is>
+          <t>Rustic,Antique Black/Gray,Fabric, Solid Wood, Wood Veneer, Others,Bold Distressed Details,Wingback Inspired Chairs,Beige Linen-like Fabric,Button Tufted w/ Nailhead Trim</t>
+        </is>
+      </c>
+      <c r="X291" s="25" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="Y291" s="25" t="n"/>
+      <c r="Z291" s="25" t="n"/>
+      <c r="AA291" s="25" t="n"/>
+      <c r="AB291" s="25" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="25" t="inlineStr">
+        <is>
+          <t>Antique Black, Ivory</t>
+        </is>
+      </c>
+      <c r="B292" s="25" t="n"/>
+      <c r="C292" s="25" t="inlineStr">
+        <is>
+          <t>CM3324BK-PT-5PC</t>
+        </is>
+      </c>
+      <c r="D292" s="25" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="E292" s="25" t="inlineStr">
+        <is>
+          <t>Dining Set</t>
+        </is>
+      </c>
+      <c r="F292" s="25" t="inlineStr">
+        <is>
+          <t>SANIA 5 Pc. Counter Height Table Set</t>
+        </is>
+      </c>
+      <c r="G292" s="25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANIA 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 60"L X 30"W X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
+- Bold Distressed Details&lt;br&gt;
+- Center Beam for Support&lt;br&gt;
+- Beam Doubles as Footrest&lt;br&gt;
+- Beige Linen-like Fabric Chairs&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Padded Seat Included items and dimensions:&lt;br&gt;
+- 60" Counter Height Table: color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others or Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+Weight: 173.2 or 192.6 or 177.4 or 182.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H292" s="25" t="inlineStr">
@@ -42813,7 +42810,7 @@
       </c>
       <c r="AC292" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD292" t="inlineStr">
@@ -42867,19 +42864,22 @@
       <c r="G293" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Linen-like Fabric, Solid Wood, Wood Veneer, construction and Rustic Oak tones, it blends durability with visual warmth.&lt;br&gt;
+SANIA 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 60"L X 30"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
+- Bold Distressed Details&lt;br&gt;
 - Center Beam for Support&lt;br&gt;
 - Beam Doubles as Footrest&lt;br&gt;
+- Beige Linen-like Fabric Chairs&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: Rustic Oak; dimensions: 60" L x 30" W x 36" H; feature: Rustic&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Rustic Oak; dimensions: 19" W x 22 1 or 2"D x 42 3 or 4" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Oak&lt;br&gt;
-Weight: 182.3 lbs&lt;/p&gt;</t>
+- 60" Counter Height Table: color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others or Linen-like Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray or Antique Black, Ivory or Rustic Oak&lt;br&gt;
+Weight: 173.2 or 192.6 or 177.4 or 182.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H293" s="25" t="inlineStr">
@@ -42963,7 +42963,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -43115,7 +43115,7 @@
       </c>
       <c r="AC294" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD294" t="inlineStr">
@@ -43261,7 +43261,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -43316,18 +43316,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
 - Wingback Design Included items and dimensions:&lt;br&gt;
-- 72" Dining Table: color: Antique Black, Beige; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 238.9 lbs&lt;/p&gt;</t>
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H296" s="27" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD296" t="inlineStr">
@@ -43465,19 +43465,19 @@
       <c r="G297" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around SANIA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Linen-like Fabric, Solid Wood, construction and Antique Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 72"L X 42"W X 30 1/2"H&lt;/p&gt;
+SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
 - Wingback Design Included items and dimensions:&lt;br&gt;
-- 72" Dining Table: color: Antique Black, Beige; dimensions: 72" L x 42" W x 30 1 or 2" H; feature: Rustic&lt;br&gt;
-- III Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 238.9 lbs&lt;/p&gt;</t>
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H297" s="27" t="inlineStr">
@@ -43561,7 +43561,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -43615,19 +43615,19 @@
       <c r="G298" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Antique Black or Ivory tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
-- Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 258.9 lbs&lt;/p&gt;</t>
+- Wingback Design Included items and dimensions:&lt;br&gt;
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H298" s="27" t="inlineStr">
@@ -43711,7 +43711,7 @@
       </c>
       <c r="AC298" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD298" t="inlineStr">
@@ -43765,19 +43765,19 @@
       <c r="G299" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
-- Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- III Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 258.9 lbs&lt;/p&gt;</t>
+- Wingback Design Included items and dimensions:&lt;br&gt;
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H299" s="27" t="inlineStr">
@@ -43861,7 +43861,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -43915,19 +43915,19 @@
       <c r="G300" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around SANIA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
 - Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
-- Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Antique Black or Beige; dimensions: 22 1 or 2" W x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 307.08 lbs&lt;/p&gt;</t>
+- Wingback Design Included items and dimensions:&lt;br&gt;
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H300" s="27" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="AC300" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD300" t="inlineStr">
@@ -44065,19 +44065,19 @@
       <c r="G301" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and Antique Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+SANIA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 72"L X 42"W X 30 1/2"H / 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
-- Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Antique Black or Gray; dimensions: 22 1 or 2" W x 26 3 or 4"D x 42 1 or 2" H (SEAT DP: 17 1 or 2", SEAT HT: 20"); feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 308.4 lbs&lt;/p&gt;</t>
+- Wingback Design Included items and dimensions:&lt;br&gt;
+- 72" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood, Others or Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 238.9 or 258.9 or 307.08 or 308.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H301" s="27" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -44223,11 +44223,11 @@
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
 - Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Side Chair (2 / CTN): color: Beige or Antique Black; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 299.6 lbs&lt;/p&gt;</t>
+- 84" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 299.6 or 363.84 or 365.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H302" s="29" t="inlineStr">
@@ -44311,7 +44311,7 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD302" t="inlineStr">
@@ -44365,157 +44365,7 @@
       <c r="G303" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around SANIA 9 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Antique Black or Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
-- Bold Distressed Details&lt;br&gt;
-- Button Tufted w/ Nailhead Trim&lt;br&gt;
-- Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- III Side Chair (2 / CTN): color: Antique Black or Gray; dimensions: 20" W x 28"D x 42" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 299.6 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H303" s="29" t="inlineStr">
-        <is>
-          <t>SANIA 9 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I303" s="29" t="inlineStr">
-        <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J303" s="29" t="inlineStr">
-        <is>
-          <t>SANIA</t>
-        </is>
-      </c>
-      <c r="K303" s="29" t="inlineStr">
-        <is>
-          <t>9 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="L303" s="29" t="n"/>
-      <c r="M303" s="29" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N303" s="29" t="inlineStr">
-        <is>
-          <t>CM3324BK-T-84-VN, CM3564GY-SC-2PK</t>
-        </is>
-      </c>
-      <c r="O303" s="29" t="inlineStr">
-        <is>
-          <t>CM3324BK-T-84.jpg,CM3324BK-T-84-Z.jpg,CM3324BK-T-84-BENCH-Z.jpg,CM3324BK-T-84-DETAIL.jpg,CM3324BK-T-84-TOP.jpg,CM3324BK-T-DETAIL.jpg,CM3324BK-T-TOP.jpg,CM3324BK-SC.jpg</t>
-        </is>
-      </c>
-      <c r="P303" s="29" t="n">
-        <v>1040</v>
-      </c>
-      <c r="Q303" s="30" t="n">
-        <v>1040</v>
-      </c>
-      <c r="R303" s="29" t="n">
-        <v>2787</v>
-      </c>
-      <c r="S303" s="29" t="n">
-        <v>299.6</v>
-      </c>
-      <c r="T303" s="29" t="inlineStr">
-        <is>
-          <t>84"(66" + 1 X 18"Leaf)L X 42"W X 30"H</t>
-        </is>
-      </c>
-      <c r="U303" s="29" t="inlineStr">
-        <is>
-          <t>Rustic</t>
-        </is>
-      </c>
-      <c r="V303" s="29" t="inlineStr">
-        <is>
-          <t>Solid Wood, Wood Veneer, Others</t>
-        </is>
-      </c>
-      <c r="W303" s="29" t="inlineStr">
-        <is>
-          <t>Rustic,Antique Black/Gray,Solid Wood, Wood Veneer, Others,Bold Distressed Details,Button Tufted w/ Nailhead Trim,Wingback Inspired</t>
-        </is>
-      </c>
-      <c r="X303" s="29" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="Y303" s="29" t="n"/>
-      <c r="Z303" s="29" t="n"/>
-      <c r="AA303" s="29" t="n"/>
-      <c r="AB303" s="29" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="AC303" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD303" t="inlineStr">
-        <is>
-          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE303" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF303" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG303" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="29" t="inlineStr">
-        <is>
-          <t>Antique Black/Ivory</t>
-        </is>
-      </c>
-      <c r="B304" s="29" t="n"/>
-      <c r="C304" s="29" t="inlineStr">
-        <is>
-          <t>CM3324BK-T-84-9PC</t>
-        </is>
-      </c>
-      <c r="D304" s="29" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="E304" s="29" t="inlineStr">
-        <is>
-          <t>Dining Set</t>
-        </is>
-      </c>
-      <c r="F304" s="29" t="inlineStr">
-        <is>
-          <t>SANIA 9 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="G304" s="29" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 9 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
+SANIA 9 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
@@ -44523,11 +44373,161 @@
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
 - Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Antique Black or Beige; dimensions: 22 1 or 2" W x 26 3 or 4"D x 42 1 or 2" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 363.84 lbs&lt;/p&gt;</t>
+- 84" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 299.6 or 363.84 or 365.6 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H303" s="29" t="inlineStr">
+        <is>
+          <t>SANIA 9 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I303" s="29" t="inlineStr">
+        <is>
+          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J303" s="29" t="inlineStr">
+        <is>
+          <t>SANIA</t>
+        </is>
+      </c>
+      <c r="K303" s="29" t="inlineStr">
+        <is>
+          <t>9 Pc. Dining Table Set</t>
+        </is>
+      </c>
+      <c r="L303" s="29" t="n"/>
+      <c r="M303" s="29" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N303" s="29" t="inlineStr">
+        <is>
+          <t>CM3324BK-T-84-VN, CM3564GY-SC-2PK</t>
+        </is>
+      </c>
+      <c r="O303" s="29" t="inlineStr">
+        <is>
+          <t>CM3324BK-T-84.jpg,CM3324BK-T-84-Z.jpg,CM3324BK-T-84-BENCH-Z.jpg,CM3324BK-T-84-DETAIL.jpg,CM3324BK-T-84-TOP.jpg,CM3324BK-T-DETAIL.jpg,CM3324BK-T-TOP.jpg,CM3324BK-SC.jpg</t>
+        </is>
+      </c>
+      <c r="P303" s="29" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q303" s="30" t="n">
+        <v>1040</v>
+      </c>
+      <c r="R303" s="29" t="n">
+        <v>2787</v>
+      </c>
+      <c r="S303" s="29" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="T303" s="29" t="inlineStr">
+        <is>
+          <t>84"(66" + 1 X 18"Leaf)L X 42"W X 30"H</t>
+        </is>
+      </c>
+      <c r="U303" s="29" t="inlineStr">
+        <is>
+          <t>Rustic</t>
+        </is>
+      </c>
+      <c r="V303" s="29" t="inlineStr">
+        <is>
+          <t>Solid Wood, Wood Veneer, Others</t>
+        </is>
+      </c>
+      <c r="W303" s="29" t="inlineStr">
+        <is>
+          <t>Rustic,Antique Black/Gray,Solid Wood, Wood Veneer, Others,Bold Distressed Details,Button Tufted w/ Nailhead Trim,Wingback Inspired</t>
+        </is>
+      </c>
+      <c r="X303" s="29" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="Y303" s="29" t="n"/>
+      <c r="Z303" s="29" t="n"/>
+      <c r="AA303" s="29" t="n"/>
+      <c r="AB303" s="29" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>Dining, Dining Set, SANIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="29" t="inlineStr">
+        <is>
+          <t>Antique Black/Ivory</t>
+        </is>
+      </c>
+      <c r="B304" s="29" t="n"/>
+      <c r="C304" s="29" t="inlineStr">
+        <is>
+          <t>CM3324BK-T-84-9PC</t>
+        </is>
+      </c>
+      <c r="D304" s="29" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="E304" s="29" t="inlineStr">
+        <is>
+          <t>Dining Set</t>
+        </is>
+      </c>
+      <c r="F304" s="29" t="inlineStr">
+        <is>
+          <t>SANIA 9 Pc. Dining Table Set</t>
+        </is>
+      </c>
+      <c r="G304" s="29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANIA 9 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
+- Bold Distressed Details&lt;br&gt;
+- Button Tufted w/ Nailhead Trim&lt;br&gt;
+- Wingback Inspired Included items and dimensions:&lt;br&gt;
+- 84" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 299.6 or 363.84 or 365.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H304" s="29" t="inlineStr">
@@ -44611,7 +44611,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD304" t="inlineStr">
@@ -44665,19 +44665,19 @@
       <c r="G305" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 9 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. With Solid Wood, Wood Veneer, construction and Antique Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+SANIA 9 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Rustic profile gives the space a refined, approachable look. Finished in Antique Black or Ivory tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 84"(66" + 1 X 18"Leaf)L X 42"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Antique Black or Gray&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
 - Bold Distressed Details&lt;br&gt;
 - Button Tufted w/ Nailhead Trim&lt;br&gt;
 - Wingback Inspired Included items and dimensions:&lt;br&gt;
-- 84" Dining Table: color: Antique Black, Beige; dimensions: 84"(66" and 1 x 18" LEAF)L x 42" W x 30" H; feature: Rustic&lt;br&gt;
-- Wingback Chair (2 / CTN): color: Antique Black or Gray; dimensions: 22 1 or 2" W x 26 3 or 4"D x 42 1 or 2" H (SEAT DP: 17 1 or 2", SEAT HT: 20"); feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Gray&lt;br&gt;
-Weight: 365.6 lbs&lt;/p&gt;</t>
+- 84" Dining Table: color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+- Side Chair (2 / CTN): color: Antique Black or Ivory or Antique Black or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Antique Black or Gray&lt;br&gt;
+Weight: 299.6 or 363.84 or 365.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H305" s="29" t="inlineStr">
@@ -44761,7 +44761,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -44907,7 +44907,7 @@
       </c>
       <c r="AC306" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD306" t="inlineStr">
@@ -45053,7 +45053,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -45197,7 +45197,7 @@
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -45315,7 +45315,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -45433,7 +45433,7 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD310" t="inlineStr">
@@ -45552,7 +45552,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">
@@ -45671,7 +45671,7 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD312" t="inlineStr">
@@ -45814,7 +45814,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -45958,7 +45958,7 @@
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD314" t="inlineStr">
@@ -46013,16 +46013,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around STACIE 5 PC. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 60"DIA X 36 1/8"H, FOLDED LEAVES: 46"L X 46"W X 36 1/8"H&lt;/p&gt;
+Product Dimensions: 60"DIA X 36 1/8"H, FOLDED LEAVES: 46"L X 46"W X 36 1/8"H / 60"DIA X 36 1/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Wood Construction&lt;br&gt;
 - Open Shelves&lt;br&gt;
 - Drop Leaves&lt;br&gt;
 - Wine Rack&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Gray; dimensions: 20 1 or 2" W x 20 1 or 2"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Gray or White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or White or Gray&lt;br&gt;
 Weight: 294 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -46107,7 +46107,7 @@
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD315" t="inlineStr">
@@ -46161,18 +46161,17 @@
       <c r="G316" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STACIE 5 PC. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and White or Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 60"DIA X 36 1/8"H&lt;/p&gt;
+Gather around STACIE 5 PC. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 60"DIA X 36 1/8"H, FOLDED LEAVES: 46"L X 46"W X 36 1/8"H / 60"DIA X 36 1/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Gray&lt;br&gt;
 - Wood Construction&lt;br&gt;
 - Open Shelves&lt;br&gt;
 - Drop Leaves&lt;br&gt;
 - Wine Rack&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: White or Gray; dimensions: 20 1 or 2" W x 20 1 or 2"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White or Gray&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Gray or White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or White or Gray&lt;br&gt;
 Weight: 294 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -46257,7 +46256,7 @@
       </c>
       <c r="AC316" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD316" t="inlineStr">
@@ -46318,9 +46317,9 @@
 - Drop Leaves&lt;br&gt;
 - Wine Rack&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: Gray; dimensions: 20 1 or 2" W x 20 1 or 2"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Gray or White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or White or Gray&lt;br&gt;
 Weight: 336 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -46401,7 +46400,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD317" t="inlineStr">
@@ -46455,17 +46454,16 @@
       <c r="G318" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around STACIE 7 PC. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in White or Gray tones for a clean, cohesive look.&lt;/p&gt;
+STACIE 7 PC. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Gray tones, the Fabric, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- White or Gray&lt;br&gt;
 - Wood Construction&lt;br&gt;
 - Open Shelves&lt;br&gt;
 - Drop Leaves&lt;br&gt;
 - Wine Rack&lt;br&gt;
 - Padded Seat Included items and dimensions:&lt;br&gt;
-- Counter Height Chair (2 / CTN): color: White or Gray; dimensions: 20 1 or 2" W x 20 1 or 2"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White or Gray&lt;br&gt;
+- Counter Height Chair (2 / CTN): color: Gray or White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Gray or White or Gray&lt;br&gt;
 Weight: 336 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -46546,7 +46544,7 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD318" t="inlineStr">
@@ -46688,7 +46686,7 @@
       </c>
       <c r="AC319" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD319" t="inlineStr">
@@ -46834,7 +46832,7 @@
       </c>
       <c r="AC320" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD320" t="inlineStr">
@@ -46975,7 +46973,7 @@
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD321" t="inlineStr">
@@ -47118,7 +47116,7 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD322" t="inlineStr">
@@ -47266,7 +47264,7 @@
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD323" t="inlineStr">
@@ -47414,7 +47412,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD324" t="inlineStr">
@@ -47469,14 +47467,14 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 TOTTENHAM 5 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Solid Rubberwood, Oak Veneer, Engineered Wood and finished in Black tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 48"DIA X 30"H&lt;/p&gt;
+Product Dimensions: 48"DIA X 30"H / 59"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Inverted V-Leg Chair w/ Light Gray Upholstery Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 18" W x 25"D x 35.5" H (SEAT HT: 18", SEAT DP: 19"); feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: Black&lt;br&gt;
-Weight: 218.26 lbs&lt;/p&gt;</t>
+Weight: 218.26 or 252.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H325" s="35" t="inlineStr">
@@ -47560,7 +47558,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD325" t="inlineStr">
@@ -47614,15 +47612,15 @@
       <c r="G326" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TOTTENHAM 5 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Solid Rubberwood, Oak Veneer, Engineered Wood, then finished in Black tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 59"DIA X 30"H&lt;/p&gt;
+TOTTENHAM 5 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Solid Rubberwood, Oak Veneer, Engineered Wood and finished in Black tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 48"DIA X 30"H / 59"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Cone-Shaped Pedestal Base&lt;br&gt;
 - Inverted V-Leg Chair w/ Light Gray Upholstery Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 18" W x 25"D x 35.5" H (SEAT HT: 18", SEAT DP: 19"); feature: Contemporary&lt;/p&gt;
+- Side Chair (2 / CTN): color: Black&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
 Color: Black&lt;br&gt;
-Weight: 252.33 lbs&lt;/p&gt;</t>
+Weight: 218.26 or 252.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H326" s="35" t="inlineStr">
@@ -47706,7 +47704,7 @@
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD326" t="inlineStr">
@@ -47849,7 +47847,7 @@
       </c>
       <c r="AC327" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD327" t="inlineStr">
@@ -47991,7 +47989,7 @@
       </c>
       <c r="AC328" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD328" t="inlineStr">
@@ -48133,7 +48131,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -48278,7 +48276,7 @@
       </c>
       <c r="AC330" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD330" t="inlineStr">
@@ -48422,7 +48420,7 @@
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -48565,7 +48563,7 @@
       </c>
       <c r="AC332" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD332" t="inlineStr">
@@ -48620,12 +48618,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 UZWIL 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Mid-Century Modern and finished in Walnut tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Table: 70.9"L X 39.4"W X 29.5"H Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Walnut; dimensions: 71" W x 39.5"D x 29.5" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Walnut or Beige; dimensions: 19" W x 21"D x 31.5" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Mid-Century Modern.&lt;br&gt;
+Product Dimensions: Table: 70.9"L X 39.4"W X 29.5"H&lt;br&gt;
+- Dining Table: color: Walnut&lt;br&gt;
+- Side Chair (2 / CTN): color: Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Mid-Century Modern or Boucle Blend, Solid Wood, Engineered Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Walnut&lt;br&gt;
-Weight: 126.5 lbs&lt;/p&gt;</t>
+Weight: 126.5 or 151.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H333" s="37" t="inlineStr">
@@ -48709,7 +48707,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
@@ -48763,16 +48761,13 @@
       <c r="G334" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around UZWIL 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Boucle Blend, Solid Wood, Engineered Wood, Wood Veneer, then finished in Walnut tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Table: 70.9"L X 39.4"W X 29.5"H&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Padded Back and Seat Cushions&lt;br&gt;
-- Angled Legs Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Walnut; dimensions: 71" W x 39.5"D x 29.5" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Walnut or Beige; dimensions: 19" W x 21"D x 31.5" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Boucle Blend, Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+UZWIL 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Mid-Century Modern and finished in Walnut tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 70.9"L X 39.4"W X 29.5"H&lt;br&gt;
+- Dining Table: color: Walnut&lt;br&gt;
+- Side Chair (2 / CTN): color: Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Mid-Century Modern or Boucle Blend, Solid Wood, Engineered Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Walnut&lt;br&gt;
-Weight: 151.8 lbs&lt;/p&gt;</t>
+Weight: 126.5 or 151.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H334" s="37" t="inlineStr">
@@ -48856,7 +48851,7 @@
       </c>
       <c r="AC334" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD334" t="inlineStr">
@@ -48920,10 +48915,10 @@
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Black; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
+- Chair (2 / CTN): color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;/p&gt;
 &lt;p&gt;Materials: Stainless Steel, Faux Marble, Flannelette.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
-Weight: 467.24 lbs&lt;/p&gt;</t>
+Color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;br&gt;
+Weight: 467.24 or 464.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H335" s="39" t="inlineStr">
@@ -49011,7 +49006,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD335" t="inlineStr">
@@ -49065,20 +49060,20 @@
       <c r="G336" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VALDEVERS 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Stainless Steel, Faux Marble, Flannelette construction and Chrome or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+VALDEVERS 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Stainless Steel, Faux Marble, Flannelette, then finished in Chrome or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 78"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Gray&lt;br&gt;
+- Chrome or Black&lt;br&gt;
 - 18mm Beveled Faux Marble Top&lt;br&gt;
 - Metal Construction&lt;br&gt;
 - V-style Pedestal w/ Rectangular Base&lt;br&gt;
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Gray; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
+- Chair (2 / CTN): color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;/p&gt;
 &lt;p&gt;Materials: Stainless Steel, Faux Marble, Flannelette.&lt;br&gt;
-Color: Chrome or Gray&lt;br&gt;
-Weight: 464.33 lbs&lt;/p&gt;</t>
+Color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;br&gt;
+Weight: 467.24 or 464.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H336" s="39" t="inlineStr">
@@ -49166,7 +49161,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD336" t="inlineStr">
@@ -49220,20 +49215,20 @@
       <c r="G337" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around VALDEVERS 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Chrome or Navy tones, the Stainless Steel, Faux Marble, Flannelette build keeps the look polished and practical.&lt;br&gt;
+VALDEVERS 7 Pc. Dining Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Crafted with Stainless Steel, Faux Marble, Flannelette, then finished in Chrome or Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 78"W X 42"D X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chrome or Navy&lt;br&gt;
+- Chrome or Black&lt;br&gt;
 - 18mm Beveled Faux Marble Top&lt;br&gt;
 - Metal Construction&lt;br&gt;
 - V-style Pedestal w/ Rectangular Base&lt;br&gt;
 - Wingback Chairs&lt;br&gt;
 - Button-tufted Flannelette&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Chair (2 / CTN): color: Blue; dimensions: 23" W x 24 3 or 4"D x 38" H seat depth:18" seat height:19-1 or 2"; feature: Contemporary&lt;/p&gt;
+- Chair (2 / CTN): color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;/p&gt;
 &lt;p&gt;Materials: Stainless Steel, Faux Marble, Flannelette.&lt;br&gt;
-Color: Chrome or Navy&lt;br&gt;
-Weight: 467.24 lbs&lt;/p&gt;</t>
+Color: Chrome or Black or Chrome or Gray or Chrome or Navy&lt;br&gt;
+Weight: 467.24 or 464.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H337" s="39" t="inlineStr">
@@ -49321,7 +49316,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD337" t="inlineStr">
@@ -49467,7 +49462,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD338" t="inlineStr">
@@ -49528,10 +49523,10 @@
 - Marble Table Top&lt;br&gt;
 - Reeded Plinth Base with Gold Trim&lt;br&gt;
 - Removable Back Pillow on 6 Casters Included items and dimensions:&lt;br&gt;
-- Dining Chair w/ Caster: color: White; dimensions: 21.5" W x 27.5"D x 37.5" H; feature: Contemporary&lt;/p&gt;
+- Dining Chair w/ Caster: color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Marble, Engineered Wood, Metal.&lt;br&gt;
 Color: Black or White&lt;br&gt;
-Weight: 351 lbs&lt;/p&gt;</t>
+Weight: 351 or 385.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H339" s="41" t="inlineStr">
@@ -49615,7 +49610,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD339" t="inlineStr">
@@ -49669,17 +49664,17 @@
       <c r="G340" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VARDE 5 Pc. Round Dining Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Boucle Chenille Fabric, Marble, Engineered Wood, Metal construction and Black or White tones, it blends durability with visual warmth.&lt;br&gt;
+VARDE 5 Pc. Round Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Boucle Chenille Fabric, Marble, Engineered Wood, Metal, then finished in Black or White tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 54"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or White&lt;br&gt;
 - Marble Table Top&lt;br&gt;
-- Reeded Plinth Base w/ Gold Trim&lt;br&gt;
-- Swivel Chair Rotates 360° Included items and dimensions:&lt;br&gt;
-- Dining Swivel Chair: color: White; dimensions: 23" W x 23"D x 32.5" H; feature: Contemporary&lt;/p&gt;
+- Reeded Plinth Base with Gold Trim&lt;br&gt;
+- Removable Back Pillow on 6 Casters Included items and dimensions:&lt;br&gt;
+- Dining Chair w/ Caster: color: Black or White&lt;/p&gt;
 &lt;p&gt;Materials: Boucle Chenille Fabric, Marble, Engineered Wood, Metal.&lt;br&gt;
 Color: Black or White&lt;br&gt;
-Weight: 385.8 lbs&lt;/p&gt;</t>
+Weight: 351 or 385.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H340" s="41" t="inlineStr">
@@ -49763,7 +49758,7 @@
       </c>
       <c r="AC340" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD340" t="inlineStr">
@@ -49904,7 +49899,7 @@
       </c>
       <c r="AC341" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD341" t="inlineStr">
@@ -50045,7 +50040,7 @@
       </c>
       <c r="AC342" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD342" t="inlineStr">
@@ -50190,7 +50185,7 @@
       </c>
       <c r="AC343" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD343" t="inlineStr">
@@ -50250,9 +50245,9 @@
 - High Gloss Lacquer Coating&lt;br&gt;
 - X-Shape Table Base&lt;br&gt;
 - 12mm Tempered Glass Top Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 17" W x 25 1 or 2"D x 38 1 or 4" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Glass, Lacquer, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Lacquer, Metal, Others or Leatherette, Lacquer, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 271.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50337,7 +50332,7 @@
       </c>
       <c r="AC344" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD344" t="inlineStr">
@@ -50391,15 +50386,15 @@
       <c r="G345" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around WAILOA 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in White tones, the Leatherette, Lacquer, Tempered Glass, Wood build keeps the look polished and practical.&lt;br&gt;
+WAILOA 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Leatherette, Glass, Lacquer, Metal, construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 59"L X 35 1/2"W X 29 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - High Gloss Lacquer Coating&lt;br&gt;
 - X-Shape Table Base&lt;br&gt;
 - 12mm Tempered Glass Top Included items and dimensions:&lt;br&gt;
-- Side Chair (2 / CTN): color: White; dimensions: 25 1 or 2" W x 16 1 or 2"D x 30 1 or 2" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Lacquer, Tempered Glass, Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Lacquer, Metal, Others or Leatherette, Lacquer, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 271.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50484,7 +50479,7 @@
       </c>
       <c r="AC345" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD345" t="inlineStr">
@@ -50597,7 +50592,7 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD346" t="inlineStr">
@@ -50746,7 +50741,7 @@
       </c>
       <c r="AC347" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD347" t="inlineStr">
@@ -50895,7 +50890,7 @@
       </c>
       <c r="AC348" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD348" t="inlineStr">
@@ -51041,7 +51036,7 @@
       </c>
       <c r="AC349" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD349" t="inlineStr">
@@ -51186,7 +51181,7 @@
       </c>
       <c r="AC350" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD350" t="inlineStr">
@@ -51329,7 +51324,7 @@
       </c>
       <c r="AC351" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD351" t="inlineStr">
@@ -51471,7 +51466,7 @@
       </c>
       <c r="AC352" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD352" t="inlineStr">
@@ -51614,7 +51609,7 @@
       </c>
       <c r="AC353" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD353" t="inlineStr">
@@ -51674,11 +51669,11 @@
 - Spindle Back&lt;br&gt;
 - Molded Seats&lt;br&gt;
 - Shaker Legs Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Black; dimensions: 42"DIA x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Side Chair (2 / CTN): color: Black; dimensions: 22" L x 20" W x 28" H; feature: Mid-Century Modern&lt;/p&gt;
+- Round Dining Table: color: Black or Natural Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Natural Oak&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 121.06 lbs&lt;/p&gt;</t>
+Color: Black or Natural Oak&lt;br&gt;
+Weight: 121.06 or 118.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H354" s="15" t="inlineStr">
@@ -51762,7 +51757,7 @@
       </c>
       <c r="AC354" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD354" t="inlineStr">
@@ -51816,17 +51811,17 @@
       <c r="G355" s="15" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-YATE 5 Pc. Dining Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Finished in Natural Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+YATE 5 Pc. Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Rubberwood, Oak Veneer, Engineered Wood construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: 42"DIA X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Spindle Back&lt;br&gt;
 - Molded Seats&lt;br&gt;
 - Shaker Legs Included items and dimensions:&lt;br&gt;
-- Round Dining Table: color: Natural Oak; dimensions: 42"DIA x 30" H; feature: Mid-Century Modern&lt;br&gt;
-- Dining Chair (2 / CTN): color: Natural Oak; dimensions: 22" L x 20" W x 28" H; feature: Mid-Century Modern&lt;/p&gt;
+- Round Dining Table: color: Black or Natural Oak&lt;br&gt;
+- Side Chair (2 / CTN): color: Black or Natural Oak&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Natural Oak&lt;br&gt;
-Weight: 118.27 lbs&lt;/p&gt;</t>
+Color: Black or Natural Oak&lt;br&gt;
+Weight: 121.06 or 118.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H355" s="15" t="inlineStr">
@@ -51914,7 +51909,7 @@
       </c>
       <c r="AC355" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD355" t="inlineStr">
@@ -52058,7 +52053,7 @@
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD356" t="inlineStr">
@@ -52201,7 +52196,7 @@
       </c>
       <c r="AC357" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD357" t="inlineStr">
@@ -52347,7 +52342,7 @@
       </c>
       <c r="AC358" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD358" t="inlineStr">
@@ -52494,7 +52489,7 @@
       </c>
       <c r="AC359" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD359" t="inlineStr">
@@ -52544,11 +52539,16 @@
       <c r="G360" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-EBIKON 5 Pc. Counter Height Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining counter ht. set is made to fit naturally into the room.&lt;br&gt;
-Product Dimensions: 59"W X 35.5"D X 36"H Included items and dimensions:&lt;br&gt;
-- Counter Height Table: color: Walnut; dimensions: 59" W x 35.5"D x 36" H; feature: Mid-century Modern&lt;br&gt;
-- Counter Stool (2 / CTN): color: Walnut or Beige; dimensions: 21.5" W x 23"D x 34" H; feature: Mid-Century Modern&lt;br&gt;
-Weight: 147.21 lbs&lt;/p&gt;</t>
+EBIKON 5 Pc. Counter Height Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining dining set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Solid Wood, Engineered Wood, Wood Veneer, Boucle, construction and Walnut tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 59.1"L X 21.7"W X 36"H / 59"W X 35.5"D X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Curved Panel Back Chair&lt;br&gt;
+- Padded Seats Included items and dimensions:&lt;br&gt;
+- Counter Height Table: color: Walnut&lt;br&gt;
+- Counter Stool (2 / CTN): color: Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood, Wood Veneer, Boucle, Others.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 120.68 or 147.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H360" s="23" t="inlineStr">
@@ -52620,7 +52620,7 @@
       </c>
       <c r="AC360" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD360" t="inlineStr">
@@ -52737,7 +52737,7 @@
       </c>
       <c r="AC361" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD361" t="inlineStr">
@@ -52854,7 +52854,7 @@
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD362" t="inlineStr">
@@ -52997,7 +52997,7 @@
       </c>
       <c r="AC363" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD363" t="inlineStr">
@@ -53051,17 +53051,18 @@
       <c r="G364" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELLAGIO 7 Pc. Dining Table Set sets the tone for shared meals with a comfortable, coordinated look. This dining dining table is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Fabric, Solid Wood, Wood Veneer, and finished in Brown Cherry tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 60"DIA X 30H&lt;/p&gt;
+Gather around BELLAGIO 7 Pc. Dining Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining dining set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Solid Wood, Wood Veneer, then finished in Brown Cherry tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 108"(72" + 2 X 18"Leaf)L X 44"W X 30"H / 60"DIA X 30H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Pedestal Base&lt;br&gt;
-- Carved Rope Table Edge&lt;br&gt;
+- Two 18" Expandable Leaf&lt;br&gt;
+- Double Pedestal Base&lt;br&gt;
+- Rope Carved Table Edge&lt;br&gt;
 - 2 Chair Options Included items and dimensions:&lt;br&gt;
-- Fabric Side Chair (2 / CTN): color: Brown Cherry or Brown; dimensions: 22 3 or 4" W x 27 1 or 2"D x 44 1 or 4" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Leatherette Side Chair (2 / CTN): color: Brown Cherry&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others or Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Brown Cherry&lt;br&gt;
-Weight: 367.3 lbs&lt;/p&gt;</t>
+Weight: 457.6 or 467.5 or 367.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H364" s="41" t="inlineStr">
@@ -53145,7 +53146,7 @@
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD364" t="inlineStr">
@@ -53290,7 +53291,7 @@
       </c>
       <c r="AC365" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD365" t="inlineStr">
@@ -53435,7 +53436,7 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD366" t="inlineStr">
@@ -53579,7 +53580,7 @@
       </c>
       <c r="AC367" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD367" t="inlineStr">
@@ -53723,7 +53724,7 @@
       </c>
       <c r="AC368" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD368" t="inlineStr">
@@ -53871,7 +53872,7 @@
       </c>
       <c r="AC369" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD369" t="inlineStr">
@@ -54015,7 +54016,7 @@
       </c>
       <c r="AC370" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD370" t="inlineStr">
@@ -54079,11 +54080,11 @@
 - Beam Doubles as Footrest&lt;br&gt;
 - Ivory Linen-like Fabric Chairs&lt;br&gt;
 - Nailhead Trim Included items and dimensions:&lt;br&gt;
-- Bar Table: color: Antique Black; dimensions: 60" L x 30" W x 42" H; feature: Rustic&lt;br&gt;
-- Bar Chair (2 / CTN): color: Antique Black or Beige; dimensions: 19 1 or 8" W x 23"D x 48" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Black or Ivory&lt;br&gt;
-Weight: 189.8 lbs&lt;/p&gt;</t>
+- Bar Table: color: Antique Black or Ivory or Rustic Oak&lt;br&gt;
+- Bar Chair (2 / CTN): color: Antique Black or Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Rustic Oak&lt;br&gt;
+Weight: 189.8 or 189.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H371" s="23" t="inlineStr">
@@ -54171,7 +54172,7 @@
       </c>
       <c r="AC371" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD371" t="inlineStr">
@@ -54225,17 +54226,21 @@
       <c r="G372" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANIA 5 Pc. Bar Table Set anchors the dining area with a cohesive look that feels easy and welcoming. As a dining bar table, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. With Fabric, Solid Wood, Wood Veneer, construction and Rustic Oak tones, it blends durability with visual warmth.&lt;br&gt;
+Gather around SANIA 5 Pc. Bar Table Set, designed to keep the dining space warm, balanced, and inviting. Designed as a dining bar table, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Antique Black or Ivory tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 60"L X 30"W X 42"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
+- Antique Black or Ivory&lt;br&gt;
+- Bold Distressed Details&lt;br&gt;
 - Center Beam for Support&lt;br&gt;
-- Beam Doubles as Footrest Included items and dimensions:&lt;br&gt;
-- Bar Height Table: color: Rustic Oak; dimensions: 60" L x 30" W x 42" H; feature: Rustic&lt;br&gt;
-- Bar Chair (2 / CTN): color: Rustic Oak; dimensions: 19 1 or 8" W x 23"D x 48" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rustic Oak&lt;br&gt;
-Weight: 189.5 lbs&lt;/p&gt;</t>
+- Beam Doubles as Footrest&lt;br&gt;
+- Ivory Linen-like Fabric Chairs&lt;br&gt;
+- Nailhead Trim Included items and dimensions:&lt;br&gt;
+- Bar Table: color: Antique Black or Ivory or Rustic Oak&lt;br&gt;
+- Bar Chair (2 / CTN): color: Antique Black or Ivory or Rustic Oak&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Black or Ivory or Rustic Oak&lt;br&gt;
+Weight: 189.8 or 189.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H372" s="23" t="inlineStr">
@@ -54319,7 +54324,7 @@
       </c>
       <c r="AC372" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD372" t="inlineStr">

--- a/FOA SETS/Dining-Set.xlsx
+++ b/FOA SETS/Dining-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ADALIA 7 Pc. Dining Table Set in Silver Dark Gray | GOODDEGG</t>
+          <t>ADALIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The ADALIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ADALIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ADELINA 5 Pc. Round Dining Table Set in Champagne | GOODDEGG</t>
+          <t>ADELINA 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The ADELINA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ADELINA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ADELINA 7 Pc. Dining Table Set in Champagne Warm Gray | GOODDEGG</t>
+          <t>ADELINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The ADELINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ADELINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ALENA 7 Pc. Dining Table Set in Black, Silver | GOODDEGG</t>
+          <t>ALENA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The ALENA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALENA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ALENA 9 Pc. Dining Table Set in Black, Silver | GOODDEGG</t>
+          <t>ALENA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The ALENA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALENA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ALESSIA 7 Pc. Dining Table Set in White Black | GOODDEGG</t>
+          <t>ALESSIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The ALESSIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALESSIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>ALFRED 5 Pc. Round Dining Table Set in Antique Black Gray | GOODD</t>
+          <t>ALFRED 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>The ALFRED Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>The ALFRED Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>The ALFRED Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>ALFRED 6 Pc. Dining Table Set w/ Bench in Antique Black | GOODDEGG</t>
+          <t>ALFRED 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>ALFRED Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALFRED 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>ALFRED 6 Pc. Dining Table Set w/ Bench in Antique Black | GOODDEGG</t>
+          <t>ALFRED 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>ALFRED Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALFRED 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>ALFRED 7 Pc. Dining Table Set in Antique Black | GOODDEGG</t>
+          <t>ALFRED 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>The ALFRED Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>ALFRED 7 Pc. Dining Table Set in Antique Black | GOODDEGG</t>
+          <t>ALFRED 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>The ALFRED Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>ALFRED 7 Pc. Dining Table Set in Antique Black | GOODDEGG</t>
+          <t>ALFRED 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>The ALFRED Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALFRED 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ALISHA 7 Pc. Dining Table Set in White Gun Metal | GOODDEGG</t>
+          <t>ALISHA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The ALISHA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALISHA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The ALNWICK Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALNWICK 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>ALPENA 7 Pc. Dining Table Set (2AC and 4SC) in Gray | GOODDEGG</t>
+          <t>ALPENA 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>ALPENA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALPENA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>ALPENA 7 Pc. Dining Table Set (2AC and 4SC) in Brown Cherry | GOODDEGG</t>
+          <t>ALPENA 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" s="19" t="inlineStr">
         <is>
-          <t>ALPENA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALPENA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>ALPENA 9 Pc. Dining Table Set (2AC and 6SC) in Gray | GOODDEGG</t>
+          <t>ALPENA 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>ALPENA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALPENA 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>ALPENA 9 Pc. Dining Table Set (2AC and 6SC) in Brown Cherry | GOODDEGG</t>
+          <t>ALPENA 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>ALPENA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ALPENA 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AMINA 5 Pc. Round Dining Table Set in Champagne | GOODDEGG</t>
+          <t>AMINA 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The AMINA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>AMINA 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>AMINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>The AMINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>AMINA 7 Pc. Dining Table Set in Champagne | GOODDEGG</t>
+          <t>AMINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>The AMINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>AMINA 7 Pc. Dining Table Set in Champagne | GOODDEGG</t>
+          <t>AMINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>The AMINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H26" s="25" t="inlineStr">
         <is>
-          <t>AMINA 9 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>AMINA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
         <is>
-          <t>The AMINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" s="25" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>AMINA 9 Pc. Dining Table Set in Champagne | GOODDEGG</t>
+          <t>AMINA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
-          <t>The AMINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMINA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" s="25" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ANTON 7 Pc. Counter Height Table Set in Gray Light Gray | GOODDEG</t>
+          <t>ANTON 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The ANTON Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTON 7 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>The ARCADIA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARCADIA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" s="27" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="H30" s="27" t="inlineStr">
         <is>
-          <t>ARCADIA 5 Pc. Round Dining Table Set in Antique White | GOODDEGG</t>
+          <t>ARCADIA 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr">
         <is>
-          <t>The ARCADIA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARCADIA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="27" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>ARCADIA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ARCADIA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" s="29" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>ARCADIA 7 Pc. Dining Table Set (2AC &amp; 4SC) in Antique White | GOODDEGG</t>
+          <t>ARCADIA 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>ARCADIA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ARCADIA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" s="29" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ARCADIA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ARCADIA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="I34" s="31" t="inlineStr">
         <is>
-          <t>The ARCADIA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARCADIA 7 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" s="31" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="H35" s="31" t="inlineStr">
         <is>
-          <t>ARCADIA 7 Pc. Round Dining Table Set in Antique White | GOODDEGG</t>
+          <t>ARCADIA 7 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" s="31" t="inlineStr">
         <is>
-          <t>The ARCADIA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARCADIA 7 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" s="31" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ARCADIA 9 Pc. Dining Table Set (2AC &amp; 6SC) in Antique White | GOODDEGG</t>
+          <t>ARCADIA 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ARCADIA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ARCADIA 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="I37" s="33" t="inlineStr">
         <is>
-          <t>The AULETTA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AULETTA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" s="33" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="I38" s="33" t="inlineStr">
         <is>
-          <t>The AULETTA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AULETTA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" s="33" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="H39" s="35" t="inlineStr">
         <is>
-          <t>AULETTA 7 Pc. Dining Table Set in Distressed White Gray | GOODDEG</t>
+          <t>AULETTA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" s="35" t="inlineStr">
         <is>
-          <t>The AULETTA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AULETTA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" s="35" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="I40" s="35" t="inlineStr">
         <is>
-          <t>The AULETTA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AULETTA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" s="35" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>BARBARY 6 Pc. Dining Table Set w/ Bench in Black Dark Oak | GO</t>
+          <t>BARBARY 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>BARBARY Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BARBARY 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>BARBARY 7 Pc. Dining Table Set in Black Dark Oak | GOODDEGG</t>
+          <t>BARBARY 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The BARBARY Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BARBARY 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H43" s="37" t="inlineStr">
         <is>
-          <t>BASILICATA 7 Pc. Dining Table Set in Gold Black | GOODDEGG</t>
+          <t>BASILICATA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" s="37" t="inlineStr">
         <is>
-          <t>The BASILICATA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASILICATA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" s="37" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="H44" s="37" t="inlineStr">
         <is>
-          <t>BASILICATA 7 Pc. Dining Table Set in Gold Gray | GOODDEGG</t>
+          <t>BASILICATA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" s="37" t="inlineStr">
         <is>
-          <t>The BASILICATA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASILICATA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" s="37" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="H45" s="37" t="inlineStr">
         <is>
-          <t>BASILICATA 7 Pc. Dining Table Set in Chrome Black | GOODDEGG</t>
+          <t>BASILICATA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="37" t="inlineStr">
         <is>
-          <t>The BASILICATA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASILICATA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="37" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="H46" s="37" t="inlineStr">
         <is>
-          <t>BASILICATA 7 Pc. Dining Table Set in Chrome Gray | GOODDEGG</t>
+          <t>BASILICATA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" s="37" t="inlineStr">
         <is>
-          <t>The BASILICATA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASILICATA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" s="37" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="H47" s="39" t="inlineStr">
         <is>
-          <t>BEALE 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>BEALE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" s="39" t="inlineStr">
         <is>
-          <t>The BEALE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BEALE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" s="39" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="H48" s="39" t="inlineStr">
         <is>
-          <t>BEALE 7 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>BEALE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" s="39" t="inlineStr">
         <is>
-          <t>The BEALE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BEALE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" s="39" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="H49" s="41" t="inlineStr">
         <is>
-          <t>BELLAGIO 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" s="41" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" s="41" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="H50" s="41" t="inlineStr">
         <is>
-          <t>BELLAGIO 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" s="41" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" s="41" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>BELLAGIO 9 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>BELLAGIO 9 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" s="13" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and 4 Leatherette Chairs in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO Table and 4 Leatherette Chairs | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and Leatherette Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BELLAGIO Table and 4 Leatherette supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and 4 Wooden Chairs in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO Table and 4 Wooden Chairs | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and Wooden Chairs makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO Table and 4 Wooden Chairs Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and 6 Leatherette Chairs in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO Table and 6 Leatherette Chairs | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and Leatherette Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BELLAGIO Table and 6 Leatherette supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and 6 Wooden Chairs in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO Table and 6 Wooden Chairs | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BELLAGIO Table and Wooden Chairs makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO Table and 6 Wooden Chairs Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BINGHAM Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BINGHAM 5 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BRENT 7 Pc. Dining Table Set in Dark Cherry Beige | GOODDEGG</t>
+          <t>BRENT 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>The BRENT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRENT 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BRENT II Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BRENT II 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>BRENT II Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set BRENT II 9 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t>The BROAGER Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" s="15" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>The BROAGER Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="15" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t>The BROAGER Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" s="15" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>The BROAGER Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" s="15" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>BROAGER 5 Pc. Square Table Set in Rustic Oak Dark Walnut | GOODDE</t>
+          <t>BROAGER 5 Pc. Square Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>The BROAGER Square Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Square Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" s="17" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>BROAGER 5 Pc. Square Table Set in Rustic Oak Dark Walnut | GOODDE</t>
+          <t>BROAGER 5 Pc. Square Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>The BROAGER Square Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROAGER 5 Pc. Square Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" s="17" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="I67" s="19" t="inlineStr">
         <is>
-          <t>The BRULE Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRULE 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" s="19" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>The BRULE Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRULE 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CALABRIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set CALABRIA 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CANYONVILLE Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set CANYONVILLE 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CANYONVILLE Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set CANYONVILLE 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CARLISLE 5 Pc. Round Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>CARLISLE 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CARLISLE Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CARLISLE 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>CASPER 7 Pc. Dining Table Set in Chrome | GOODDEGG</t>
+          <t>CASPER 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
-          <t>The CASPER Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASPER 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" s="21" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="H74" s="21" t="inlineStr">
         <is>
-          <t>CASPER 7 Pc. Dining Table Set in Chrome | GOODDEGG</t>
+          <t>CASPER 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" s="21" t="inlineStr">
         <is>
-          <t>The CASPER Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASPER 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" s="21" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CATHALINA 7 Pc. Dining Table Set in Silver | GOODDEGG</t>
+          <t>CATHALINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>The CATHALINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CATHALINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CILEGON 5 Pc. Dining Table Set in White, Natural Tone | GOODDEGG</t>
+          <t>CILEGON 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The CILEGON Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CILEGON 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CIMMA 7 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>CIMMA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>The CIMMA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CIMMA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DANIELLA 7 Pc. Dining Table Set in Antique White | GOODDEGG</t>
+          <t>DANIELLA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>The DANIELLA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DANIELLA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>DICKINSON I 7 Pc. Dining Table Set in Dark Cherry | GOODDEGG</t>
+          <t>DICKINSON I 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>The DICKINSON I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DICKINSON I 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>DICKINSON I 9 Pc. Dining Table Set in Dark Cherry | GOODDEGG</t>
+          <t>DICKINSON I 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The DICKINSON I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DICKINSON I 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DICKINSON II 7 Pc. Counter Height Table Set in Dark Cherry | GOODDEGG</t>
+          <t>DICKINSON II 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DICKINSON II Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set DICKINSON II 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DICKINSON II 9 Pc. Counter Height Table Set in Dark Cherry | GOODDEGG</t>
+          <t>DICKINSON II 9 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DICKINSON II Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set DICKINSON II 9 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DIOCLES Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set DIOCLES 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DIOCLES 7 Pc. Dining Table Set in Silver Light Gray | GOODDEGG</t>
+          <t>DIOCLES 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>The DIOCLES Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIOCLES 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DULCE 6 Pc. Dining Table Set w/ Bench in Walnut, Black | GOODDEGG</t>
+          <t>DULCE 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The DULCE Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DULCE 6 Pc. Dining Table Set w/ Bench Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>DULCE 7 Pc. Dining Table Set in Walnut, Black | GOODDEGG</t>
+          <t>DULCE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>The DULCE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DULCE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>EASINGWOLD 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>EASINGWOLD 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>The EASINGWOLD Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EASINGWOLD 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="H88" s="23" t="inlineStr">
         <is>
-          <t>EBIKON 5 Pc. Counter Height Table Set in Walnut | GOODDEGG</t>
+          <t>EBIKON 5 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>EBIKON Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EBIKON 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>The EBIKON Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EBIKON 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -13599,12 +13599,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>EBIKON 5 Pc. Oval Dining Table Set in Walnut | GOODDEGG</t>
+          <t>EBIKON 5 Pc. Oval Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The EBIKON Oval Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EBIKON 5 Pc. Oval Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>EDENBRIDGE 5 Pc. Dining Table Set in Oak Beige | GOODDEGG</t>
+          <t>EDENBRIDGE 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>The EDENBRIDGE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDENBRIDGE 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>EDENBRIDGE 6 Pc. Dining Table Set w/ Bench in Oak Beige | GOOD</t>
+          <t>EDENBRIDGE 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>EDENBRIDGE Dining Table w/ Bench makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set EDENBRIDGE 6 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>EDENBRIDGE 7 Pc. Dining Table Set in Oak Beige | GOODDEGG</t>
+          <t>EDENBRIDGE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The EDENBRIDGE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDENBRIDGE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>EDGEWOOD I 7 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>EDGEWOOD I 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The EDGEWOOD I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDGEWOOD I 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>EDGEWOOD I 9 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>EDGEWOOD I 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>The EDGEWOOD I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDGEWOOD I 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EDGEWOOD II 7 Pc. Counter Height Table Set in Espresso | GOODDEGG</t>
+          <t>EDGEWOOD II 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>EDGEWOOD II Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set EDGEWOOD II 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>EDGEWOOD II 9 Pc. Counter Height Table Set in Espresso | GOODDEGG</t>
+          <t>EDGEWOOD II 9 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EDGEWOOD II Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set EDGEWOOD II 9 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -14746,12 +14746,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ELANA 5 Pc. Round Dining Table Set in Brown Cherry Brown | GOODDE</t>
+          <t>ELANA 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The ELANA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELANA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ELANA 7 Pc. Dining Table Set (2AC and 4SC) in Brown Cherry | GOODDEGG</t>
+          <t>ELANA 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ELANA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ELANA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ELANA 9 Pc. Dining Table Set (2AC and 6SC) in Brown Cherry | GOODDEGG</t>
+          <t>ELANA 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ELANA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ELANA 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="I101" s="25" t="inlineStr">
         <is>
-          <t>The ELFREDO Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELFREDO 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J101" s="25" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I102" s="25" t="inlineStr">
         <is>
-          <t>The ELFREDO Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELFREDO 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J102" s="25" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="I103" s="25" t="inlineStr">
         <is>
-          <t>The ELFREDO Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELFREDO 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J103" s="25" t="inlineStr">
@@ -15631,12 +15631,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ELLESMERE 6 Pc. Dining Table Set w/ Bench in Natural Ash | GOODDEGG</t>
+          <t>ELLESMERE 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ELLESMERE Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set ELLESMERE 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ELLESMERE 7 Pc. Dining Table Set in Natural Ash | GOODDEGG</t>
+          <t>ELLESMERE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>The ELLESMERE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELLESMERE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ESSEN 5 Pc. Round Dining Set in Espresso White | GOODDEGG</t>
+          <t>ESSEN 5 Pc. Round Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>The ESSEN Round Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESSEN 5 Pc. Round Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -16060,12 +16060,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>EVA 7 Pc. Dining Table Set in White Clear | GOODDEGG</t>
+          <t>EVA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The EVA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EVA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>EVANGELINE 7 Pc. Dining Table Set in Black Beige | GOODDEGG</t>
+          <t>EVANGELINE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>The EVANGELINE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EVANGELINE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>The FAULK Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAULK 6 Pc. Dining Table Set w/ Bench Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>FAULK 7 Pc. Dining Table Set in Espresso, Warm Gray | GOODDEGG</t>
+          <t>FAULK 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>The FAULK Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAULK 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>FERRONE 7 Pc. Dining Table Set in Rustic White Oak | GOODDEGG</t>
+          <t>FERRONE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>The FERRONE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERRONE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>FOSKEY Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FOSKEY 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -16931,12 +16931,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>FREDONIA 6 Pc. Counter Height Table Set w/ 2 PC &amp; PBN &amp; 2 BC | G</t>
+          <t>6 Pc. Counter Height Table Set w/ 2 PC and PBN and 2 BC | GOODDEGG</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>FREDONIA Counter Height Table w/ and PBN and BC makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set 6 Pc. Counter Height Table Set w/ 2 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -17075,12 +17075,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>GEORGETOWN 7 Pc. Dining Table Set (2AC and 4SC) in Cherry | GOODDEGG</t>
+          <t>GEORGETOWN 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>GEORGETOWN Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GEORGETOWN 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>GEORGIA Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GEORGIA 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -17366,12 +17366,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>GEORGIA 7 Pc. Dining Table Set in Antique White Gray | GOODDEGG</t>
+          <t>GEORGIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>The GEORGIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GEORGIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="I117" s="27" t="inlineStr">
         <is>
-          <t>GIANNA Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GIANNA 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J117" s="27" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="I118" s="27" t="inlineStr">
         <is>
-          <t>GIANNA Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GIANNA 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J118" s="27" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="H119" s="29" t="inlineStr">
         <is>
-          <t>GIANNA 7 Pc. Dining Table Set in Rustic Pine Brown | GOODDEGG</t>
+          <t>GIANNA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I119" s="29" t="inlineStr">
         <is>
-          <t>The GIANNA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIANNA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J119" s="29" t="inlineStr">
@@ -17968,12 +17968,12 @@
       </c>
       <c r="H120" s="29" t="inlineStr">
         <is>
-          <t>GIANNA 7 Pc. Dining Table Set in Rustic Pine Brown | GOODDEGG</t>
+          <t>GIANNA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I120" s="29" t="inlineStr">
         <is>
-          <t>The GIANNA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIANNA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J120" s="29" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="I121" s="31" t="inlineStr">
         <is>
-          <t>GIANNA Dining Table (w/ Wingback Chairs) makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GIANNA 7 Pc. Dining Table Set (w/ 2 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J121" s="31" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="I122" s="31" t="inlineStr">
         <is>
-          <t>GIANNA Dining Table (w/ Wingback Chairs) makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GIANNA 7 Pc. Dining Table Set (w/ 2 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J122" s="31" t="inlineStr">
@@ -18422,12 +18422,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>GIANNA 9 Pc. Dining Table Set in Rustic Pine Brown | GOODDEGG</t>
+          <t>GIANNA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The GIANNA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIANNA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>GIANNA Dining Table (w/ Wingback Chairs) makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GIANNA 9 Pc. Dining Table Set (w/ 2 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>GLADSTONE Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GLADSTONE 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -18855,12 +18855,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>GLADSTONE 7 Pc. Dining Table Set in Ivory Dark Walnut | GOODDEGG</t>
+          <t>GLADSTONE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The GLADSTONE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLADSTONE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>GLADSTONE Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GLADSTONE 9 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>GLENBROOK Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set GLENBROOK 5 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -19286,12 +19286,12 @@
       </c>
       <c r="H129" s="33" t="inlineStr">
         <is>
-          <t>GLENVIEW 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I129" s="33" t="inlineStr">
         <is>
-          <t>The GLENVIEW Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J129" s="33" t="inlineStr">
@@ -19433,12 +19433,12 @@
       </c>
       <c r="H130" s="33" t="inlineStr">
         <is>
-          <t>GLENVIEW 7 Pc. Dining Table Set in Gray Chrome | GOODDEGG</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I130" s="33" t="inlineStr">
         <is>
-          <t>The GLENVIEW Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J130" s="33" t="inlineStr">
@@ -19580,12 +19580,12 @@
       </c>
       <c r="H131" s="33" t="inlineStr">
         <is>
-          <t>GLENVIEW 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I131" s="33" t="inlineStr">
         <is>
-          <t>The GLENVIEW Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLENVIEW 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J131" s="33" t="inlineStr">
@@ -19726,12 +19726,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>GOSPORT 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>GOSPORT 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The GOSPORT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GOSPORT 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -19867,12 +19867,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>GRASTEN 5 Pc. Counter Height Set in Dark Walnut | GOODDEGG</t>
+          <t>GRASTEN 5 Pc. Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The GRASTEN Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN 5 Pc. Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>GRASTEN 5 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>GRASTEN 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The GRASTEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -20150,12 +20150,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>GRASTEN 7 Pc. Counter Height Set in Dark Walnut | GOODDEGG</t>
+          <t>GRASTEN 7 Pc. Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>The GRASTEN Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN 7 Pc. Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -20291,12 +20291,12 @@
       </c>
       <c r="H136" s="35" t="inlineStr">
         <is>
-          <t>GRASTEN 7 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>GRASTEN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I136" s="35" t="inlineStr">
         <is>
-          <t>The GRASTEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J136" s="35" t="inlineStr">
@@ -20436,12 +20436,12 @@
       </c>
       <c r="H137" s="35" t="inlineStr">
         <is>
-          <t>GRASTEN 7 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>GRASTEN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I137" s="35" t="inlineStr">
         <is>
-          <t>The GRASTEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J137" s="35" t="inlineStr">
@@ -20583,12 +20583,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>GRISTALT 7 Pc. Dining Table Set in Gray Stone Gray | GOODDEGG</t>
+          <t>GRISTALT 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>The GRISTALT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRISTALT 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>GRISTALT 9 Pc. Dining Table Set in Gray Stone Gray | GOODDEGG</t>
+          <t>GRISTALT 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The GRISTALT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRISTALT 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>GUISBOROUGH 7 Pc. Dining Table Set in Oak | GOODDEGG</t>
+          <t>GUISBOROUGH 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>The GUISBOROUGH Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GUISBOROUGH 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>HAGERMAN 6 Pc. Dining Table Set w/ Bench in Natural | GOODDEGG</t>
+          <t>HAGERMAN 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>HAGERMAN Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set HAGERMAN 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -21158,12 +21158,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>HAGERMAN 7 Pc. Dining Table Set in Natural | GOODDEGG</t>
+          <t>HAGERMAN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>The HAGERMAN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HAGERMAN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>The HALEIGH Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEIGH 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>The HALSEY Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALSEY 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -21593,12 +21593,12 @@
       </c>
       <c r="H145" s="37" t="inlineStr">
         <is>
-          <t>HANNORIA 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>HANNORIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I145" s="37" t="inlineStr">
         <is>
-          <t>The HANNORIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANNORIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J145" s="37" t="inlineStr">
@@ -21741,12 +21741,12 @@
       </c>
       <c r="H146" s="37" t="inlineStr">
         <is>
-          <t>HANNORIA 7 Pc. Dining Table Set in Silver | GOODDEGG</t>
+          <t>HANNORIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I146" s="37" t="inlineStr">
         <is>
-          <t>The HANNORIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANNORIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J146" s="37" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>The HARRISBURG Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HARRISBURG 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>The HARRISBURG Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HARRISBURG 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>HEIDELBERG Counter Height Table w/ Bench makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set HEIDELBERG 4 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>The HEPBURNE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPBURNE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -22442,12 +22442,12 @@
       </c>
       <c r="H151" s="39" t="inlineStr">
         <is>
-          <t>HINES 7 Pc. Oval Dining Set in White Oak | GOODDEGG</t>
+          <t>HINES 7 Pc. Oval Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I151" s="39" t="inlineStr">
         <is>
-          <t>The HINES Oval Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINES 7 Pc. Oval Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J151" s="39" t="inlineStr">
@@ -22600,12 +22600,12 @@
       </c>
       <c r="H152" s="39" t="inlineStr">
         <is>
-          <t>HINES 7 Pc. Oval Dining Set (2Bk and 4Nt) in White Oak | GOODDEGG</t>
+          <t>HINES 7 Pc. Oval Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I152" s="39" t="inlineStr">
         <is>
-          <t>The HINES Oval Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINES 7 Pc. Oval Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J152" s="39" t="inlineStr">
@@ -22751,12 +22751,12 @@
       </c>
       <c r="H153" s="41" t="inlineStr">
         <is>
-          <t>HINWITZ 7 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>HINWITZ 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I153" s="41" t="inlineStr">
         <is>
-          <t>The HINWITZ Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINWITZ 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J153" s="41" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="H154" s="41" t="inlineStr">
         <is>
-          <t>HINWITZ 7 Pc. Dining Table Set in White Oak | GOODDEGG</t>
+          <t>HINWITZ 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I154" s="41" t="inlineStr">
         <is>
-          <t>The HINWITZ Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINWITZ 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J154" s="41" t="inlineStr">
@@ -23045,12 +23045,12 @@
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>HINWITZ 9 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>HINWITZ 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
-          <t>The HINWITZ Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINWITZ 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J155" s="13" t="inlineStr">
@@ -23192,12 +23192,12 @@
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>HINWITZ 9 Pc. Dining Table Set in White Oak | GOODDEGG</t>
+          <t>HINWITZ 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
-          <t>The HINWITZ Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HINWITZ 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J156" s="13" t="inlineStr">
@@ -23340,12 +23340,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>HOLCROFT 7 Pc. Dining Table Set in Antique White | GOODDEGG</t>
+          <t>HOLCROFT 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The HOLCROFT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLCROFT 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>HOLCROFT 9 Pc. Dining Table Set in Antique White | GOODDEGG</t>
+          <t>HOLCROFT 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>The HOLCROFT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLCROFT 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -23626,12 +23626,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>HOLSWORTHY 5 Pc. Round Dining Set in Espresso | GOODDEGG</t>
+          <t>HOLSWORTHY 5 Pc. Round Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>The HOLSWORTHY Round Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLSWORTHY 5 Pc. Round Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -23768,12 +23768,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>HOLSWORTHY 7 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>HOLSWORTHY 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The HOLSWORTHY Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLSWORTHY 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -23911,12 +23911,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>HURLEY 6 Pc. Counter Height Table Set w/ Bench in Black | GOODDEGG</t>
+          <t>HURLEY 6 Pc. Counter Height Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>HURLEY Counter Height Table w/ Bench makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set HURLEY 6 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -24053,12 +24053,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>HURLEY 7 Pc. Counter Height Table Set in Black | GOODDEGG</t>
+          <t>HURLEY 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>HURLEY Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HURLEY 7 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>IZZY.Round Dining Table (WH Chairs) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set IZZY 5 Pc.Round Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>IZZY Round Dining Table (BK Chairs) makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set IZZY 5 Pc. Round Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -24484,12 +24484,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>JASMIN 5 Pc. Round Dining Table Set in Black White | GOODDEGG</t>
+          <t>JASMIN 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>The JASMIN Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JASMIN 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -24629,12 +24629,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>JULIA 5 Pc. Round Dining Table Set in Light Oak Beige | GOODDEGG</t>
+          <t>JULIA 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>The JULIA Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JULIA 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>JULIA 7 Pc. Dining Table Set in Light Oak Beige | GOODDEGG</t>
+          <t>JULIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>The JULIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JULIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -24919,12 +24919,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>JULIA 9 Pc. Dining Table Set in Light Oak Beige | GOODDEGG</t>
+          <t>JULIA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>The JULIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JULIA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -25063,12 +25063,12 @@
       </c>
       <c r="H169" s="15" t="inlineStr">
         <is>
-          <t>KALAWAO 7 Pc. Dining Table Set in Chrome Black | GOODDEGG</t>
+          <t>KALAWAO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I169" s="15" t="inlineStr">
         <is>
-          <t>The KALAWAO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KALAWAO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J169" s="15" t="inlineStr">
@@ -25211,12 +25211,12 @@
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>KALAWAO 7 Pc. Dining Table Set in Chrome White | GOODDEGG</t>
+          <t>KALAWAO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>The KALAWAO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KALAWAO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J170" s="15" t="inlineStr">
@@ -25361,12 +25361,12 @@
       </c>
       <c r="H171" s="17" t="inlineStr">
         <is>
-          <t>KATHRYN 5 Pc. Round Dining Table Set in Rustic Oak Beige | GOODDE</t>
+          <t>KATHRYN 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I171" s="17" t="inlineStr">
         <is>
-          <t>The KATHRYN Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KATHRYN 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J171" s="17" t="inlineStr">
@@ -25511,12 +25511,12 @@
       </c>
       <c r="H172" s="17" t="inlineStr">
         <is>
-          <t>KATHRYN 5 Pc. Round Dining Table Set in Antique White | GOODDEGG</t>
+          <t>KATHRYN 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I172" s="17" t="inlineStr">
         <is>
-          <t>The KATHRYN Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KATHRYN 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J172" s="17" t="inlineStr">
@@ -25661,12 +25661,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>KENYADA 7 Pc. Dining Table Set in Espresso | GOODDEGG</t>
+          <t>KENYADA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>The KENYADA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KENYADA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -25805,12 +25805,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>KEYNES 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>KEYNES 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>The KEYNES Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEYNES 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -25948,12 +25948,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>KIAN 7 Pc. Dining Table Set in White Gray | GOODDEGG</t>
+          <t>KIAN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>The KIAN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIAN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>KIAN I. Dining Table ( Chairs) makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set KIAN I 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -26234,12 +26234,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>KIAN I 7 Pc. Dining Table Set (Gray Chairs) in White Gray | GOODD</t>
+          <t>KIAN I 7 Pc. Dining Table Set (Gray Chairs) | GOODDEGG</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>KIAN I. Dining Table ( Chairs) makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set KIAN I 7 Pc. Dining Table Set (Gray supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -26374,12 +26374,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>KIAN II 7 Pc. Counter Height Table Set in White Black | GOODDEGG</t>
+          <t>KIAN II 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>KIAN II Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set KIAN II 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -26512,12 +26512,12 @@
       </c>
       <c r="H179" s="19" t="inlineStr">
         <is>
-          <t>KONA I 5 Pc. Round Dining Table Set in Black | GOODDEGG</t>
+          <t>KONA I 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I179" s="19" t="inlineStr">
         <is>
-          <t>The KONA I. Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KONA I 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J179" s="19" t="inlineStr">
@@ -26659,12 +26659,12 @@
       </c>
       <c r="H180" s="19" t="inlineStr">
         <is>
-          <t>KONA I 5 Pc. Round Dining Table Set in White | GOODDEGG</t>
+          <t>KONA I 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I180" s="19" t="inlineStr">
         <is>
-          <t>The KONA I. Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KONA I 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J180" s="19" t="inlineStr">
@@ -26811,12 +26811,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>LAQUILA 6 Pc. Dining Table Set w/ Bench in Gray | GOODDEGG</t>
+          <t>LAQUILA 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>LAQUILA Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LAQUILA 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -26958,12 +26958,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>LAQUILA 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>LAQUILA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>The LAQUILA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAQUILA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -27102,12 +27102,12 @@
       </c>
       <c r="H183" s="21" t="inlineStr">
         <is>
-          <t>LENVIK 7 Pc. Dining Table Set in Black White | GOODDEGG</t>
+          <t>LENVIK 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I183" s="21" t="inlineStr">
         <is>
-          <t>The LENVIK Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENVIK 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J183" s="21" t="inlineStr">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="H184" s="21" t="inlineStr">
         <is>
-          <t>LENVIK 7 Pc. Dining Table Set in Brown White | GOODDEGG</t>
+          <t>LENVIK 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I184" s="21" t="inlineStr">
         <is>
-          <t>The LENVIK Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENVIK 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J184" s="21" t="inlineStr">
@@ -27395,12 +27395,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>LEOVANNI 7 Pc. Dining Table Set (2AC and 4SC) in Dark Brown | GOODDEGG</t>
+          <t>LEOVANNI 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>LEOVANNI Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LEOVANNI 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -27543,12 +27543,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>LEOVANNI 9 Pc. Dining Table Set (2AC and 6SC) in Dark Brown | GOODDEGG</t>
+          <t>LEOVANNI 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>LEOVANNI Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LEOVANNI 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -27684,12 +27684,12 @@
       </c>
       <c r="H187" s="23" t="inlineStr">
         <is>
-          <t>LODIA I 5 Pc. Round Dining Table Set in Black | GOODDEGG</t>
+          <t>LODIA I 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I187" s="23" t="inlineStr">
         <is>
-          <t>The LODIA I. Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA I 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J187" s="23" t="inlineStr">
@@ -27829,12 +27829,12 @@
       </c>
       <c r="H188" s="23" t="inlineStr">
         <is>
-          <t>LODIA I 5 Pc. Round Dining Table Set in White | GOODDEGG</t>
+          <t>LODIA I 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I188" s="23" t="inlineStr">
         <is>
-          <t>The LODIA I. Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA I 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J188" s="23" t="inlineStr">
@@ -27974,12 +27974,12 @@
       </c>
       <c r="H189" s="25" t="inlineStr">
         <is>
-          <t>LODIA I 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>LODIA I 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I189" s="25" t="inlineStr">
         <is>
-          <t>The LODIA I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA I 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J189" s="25" t="inlineStr">
@@ -28119,12 +28119,12 @@
       </c>
       <c r="H190" s="25" t="inlineStr">
         <is>
-          <t>LODIA I 7 Pc. Dining Table Set in White | GOODDEGG</t>
+          <t>LODIA I 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I190" s="25" t="inlineStr">
         <is>
-          <t>The LODIA I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA I 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J190" s="25" t="inlineStr">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>LODIA II 5 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>LODIA II 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>The LODIA II Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA II 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -28409,12 +28409,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>LODIA II 5 Pc. Round Counter Height Table Set in White | GOODDEGG</t>
+          <t>LODIA II 5 Pc. Round Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>LODIA II Round Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LODIA II 5 Pc. Round Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -28561,7 +28561,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>LOMBARDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LOMBARDY 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>LOMBARDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LOMBARDY 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>LOSONE 6 Pc. Dining Table Set w/ Bench in Brown | GOODDEGG</t>
+          <t>LOSONE 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>LOSONE Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LOSONE 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>LOSONE 7 Pc. Dining Table Set in Brown | GOODDEGG</t>
+          <t>LOSONE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>The LOSONE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOSONE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -29129,12 +29129,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>LUMINAR 7 Pc. Dining Table Set in Black Beige | GOODDEGG</t>
+          <t>LUMINAR 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>The LUMINAR Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUMINAR 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -29273,12 +29273,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>LUMINAR II 5 Pc.Counter Height Table Set in Black Beige | GOODDEG</t>
+          <t>LUMINAR II 5 Pc.Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>LUMINAR II.Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LUMINAR II 5 Pc.Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>LUMINAR II 7 Pc. Counter Height Table Set in Black Beige | GOODDE</t>
+          <t>LUMINAR II 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>LUMINAR II Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set LUMINAR II 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -29559,12 +29559,12 @@
       </c>
       <c r="H200" s="27" t="inlineStr">
         <is>
-          <t>MANHATTAN 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>MANHATTAN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I200" s="27" t="inlineStr">
         <is>
-          <t>The MANHATTAN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANHATTAN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J200" s="27" t="inlineStr">
@@ -29705,12 +29705,12 @@
       </c>
       <c r="H201" s="27" t="inlineStr">
         <is>
-          <t>MANHATTAN 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>MANHATTAN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I201" s="27" t="inlineStr">
         <is>
-          <t>The MANHATTAN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANHATTAN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J201" s="27" t="inlineStr">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>MANHATTAN III 5 Pc. Round Counter Height Table Set in Gray | GOODDEGG</t>
+          <t>MANHATTAN III 5 Pc. Round Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>MANHATTAN III Round Counter Height Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set MANHATTAN III 5 Pc. Round Counter supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>MARINA I 5 Pc. Dining Table Set in Walnut Dark Chocolate | GOODDE</t>
+          <t>MARINA I 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>The MARINA I. Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARINA I 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -30135,12 +30135,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>MARINA II 5 PC. Dining Table Set in Walnut Dark Chocolate | GOODD</t>
+          <t>MARINA II 5 PC. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>The MARINA II Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARINA II 5 PC. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -30279,12 +30279,12 @@
       </c>
       <c r="H205" s="29" t="inlineStr">
         <is>
-          <t>MAUNA 5 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>MAUNA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I205" s="29" t="inlineStr">
         <is>
-          <t>The MAUNA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAUNA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J205" s="29" t="inlineStr">
@@ -30427,12 +30427,12 @@
       </c>
       <c r="H206" s="29" t="inlineStr">
         <is>
-          <t>MAUNA 5 Pc. Dining Table Set in White | GOODDEGG</t>
+          <t>MAUNA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I206" s="29" t="inlineStr">
         <is>
-          <t>The MAUNA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAUNA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J206" s="29" t="inlineStr">
@@ -30576,12 +30576,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>MAYVILLE 7 Pc. Dining Table Set in Black Antique Oak | GOODDEGG</t>
+          <t>MAYVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>The MAYVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAYVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -30721,12 +30721,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>MAYVILLE 9 Pc. Dining Table Set in Black Antique Oak | GOODDEGG</t>
+          <t>MAYVILLE 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>The MAYVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAYVILLE 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -30864,12 +30864,12 @@
       </c>
       <c r="H209" s="31" t="inlineStr">
         <is>
-          <t>MELINA 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>MELINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I209" s="31" t="inlineStr">
         <is>
-          <t>The MELINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MELINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J209" s="31" t="inlineStr">
@@ -31011,12 +31011,12 @@
       </c>
       <c r="H210" s="31" t="inlineStr">
         <is>
-          <t>MELINA 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>MELINA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I210" s="31" t="inlineStr">
         <is>
-          <t>The MELINA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MELINA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J210" s="31" t="inlineStr">
@@ -31159,12 +31159,12 @@
       </c>
       <c r="H211" s="33" t="inlineStr">
         <is>
-          <t>MIDVALE 7 Pc. Dining Table Set in Black Chrome | GOODDEGG</t>
+          <t>MIDVALE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I211" s="33" t="inlineStr">
         <is>
-          <t>The MIDVALE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MIDVALE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J211" s="33" t="inlineStr">
@@ -31307,12 +31307,12 @@
       </c>
       <c r="H212" s="33" t="inlineStr">
         <is>
-          <t>MIDVALE 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>MIDVALE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I212" s="33" t="inlineStr">
         <is>
-          <t>The MIDVALE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MIDVALE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J212" s="33" t="inlineStr">
@@ -31457,12 +31457,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>MODOC 7 Pc. Dining Table Set in Espresso Beige | GOODDEGG</t>
+          <t>MODOC 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The MODOC Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MODOC 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -31600,12 +31600,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>MONCLOVA 7 Pc. Dining Table Set in Rustic Oak Beige | GOODDEGG</t>
+          <t>MONCLOVA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>The MONCLOVA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONCLOVA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -31744,12 +31744,12 @@
       </c>
       <c r="H215" s="35" t="inlineStr">
         <is>
-          <t>MORGES 5 Pc. Dining Table Set in Black White | GOODDEGG</t>
+          <t>MORGES 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I215" s="35" t="inlineStr">
         <is>
-          <t>The MORGES Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORGES 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J215" s="35" t="inlineStr">
@@ -31892,12 +31892,12 @@
       </c>
       <c r="H216" s="35" t="inlineStr">
         <is>
-          <t>MORGES 5 Pc. Dining Table Set in Black White | GOODDEGG</t>
+          <t>MORGES 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I216" s="35" t="inlineStr">
         <is>
-          <t>The MORGES Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORGES 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J216" s="35" t="inlineStr">
@@ -32040,12 +32040,12 @@
       </c>
       <c r="H217" s="35" t="inlineStr">
         <is>
-          <t>MORGES 5 Pc. Dining Table Set in Black White | GOODDEGG</t>
+          <t>MORGES 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I217" s="35" t="inlineStr">
         <is>
-          <t>The MORGES Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORGES 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J217" s="35" t="inlineStr">
@@ -32185,12 +32185,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>NARVIK 7 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>NARVIK 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>The NARVIK Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NARVIK 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>The NEASDEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEASDEN 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -32446,12 +32446,12 @@
       </c>
       <c r="H220" s="37" t="inlineStr">
         <is>
-          <t>NERISSA 5 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>NERISSA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I220" s="37" t="inlineStr">
         <is>
-          <t>The NERISSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NERISSA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J220" s="37" t="inlineStr">
@@ -32594,12 +32594,12 @@
       </c>
       <c r="H221" s="37" t="inlineStr">
         <is>
-          <t>NERISSA 5 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>NERISSA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I221" s="37" t="inlineStr">
         <is>
-          <t>The NERISSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NERISSA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J221" s="37" t="inlineStr">
@@ -32742,12 +32742,12 @@
       </c>
       <c r="H222" s="39" t="inlineStr">
         <is>
-          <t>NERISSA 7 Pc. Dining Table Set in Antique Black | GOODDEGG</t>
+          <t>NERISSA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I222" s="39" t="inlineStr">
         <is>
-          <t>The NERISSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NERISSA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J222" s="39" t="inlineStr">
@@ -32890,12 +32890,12 @@
       </c>
       <c r="H223" s="39" t="inlineStr">
         <is>
-          <t>NERISSA 7 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>NERISSA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I223" s="39" t="inlineStr">
         <is>
-          <t>The NERISSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NERISSA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J223" s="39" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="H224" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in Black Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I224" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J224" s="41" t="inlineStr">
@@ -33190,12 +33190,12 @@
       </c>
       <c r="H225" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in Black Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I225" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J225" s="41" t="inlineStr">
@@ -33344,12 +33344,12 @@
       </c>
       <c r="H226" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in Black Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I226" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J226" s="41" t="inlineStr">
@@ -33494,12 +33494,12 @@
       </c>
       <c r="H227" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I227" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J227" s="41" t="inlineStr">
@@ -33644,12 +33644,12 @@
       </c>
       <c r="H228" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I228" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J228" s="41" t="inlineStr">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="H229" s="41" t="inlineStr">
         <is>
-          <t>NEUVEVILLE 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I229" s="41" t="inlineStr">
         <is>
-          <t>The NEUVEVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEUVEVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J229" s="41" t="inlineStr">
@@ -33947,12 +33947,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>NEWCASTLE 7 Pc. Dining Table Set in Antique Gray Gray | GOODDEGG</t>
+          <t>NEWCASTLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>The NEWCASTLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEWCASTLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -34091,12 +34091,12 @@
       </c>
       <c r="H231" s="13" t="inlineStr">
         <is>
-          <t>NORELLI 7 Pc. Dining Table Set in Gold White | GOODDEGG</t>
+          <t>NORELLI 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I231" s="13" t="inlineStr">
         <is>
-          <t>The NORELLI Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORELLI 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J231" s="13" t="inlineStr">
@@ -34239,12 +34239,12 @@
       </c>
       <c r="H232" s="13" t="inlineStr">
         <is>
-          <t>NORELLI 7 Pc. Dining Table Set in Silver White | GOODDEGG</t>
+          <t>NORELLI 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I232" s="13" t="inlineStr">
         <is>
-          <t>The NORELLI Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORELLI 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J232" s="13" t="inlineStr">
@@ -34395,7 +34395,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>NORMANDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set NORMANDY 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>NORMANDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set NORMANDY 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -34667,7 +34667,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>The NORTHAM Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHAM 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>The NORTHAM Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHAM 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -34899,7 +34899,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>The NORTHOLT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHOLT 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -35015,7 +35015,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>The NORTHOLT Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHOLT 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -35131,7 +35131,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>The NORTHWICH Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -35247,7 +35247,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>The NORTHWICH Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -35376,12 +35376,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>NOUVELLE 7 Pc. Dining Table Set in Brown Cherry Espresso | GOODDE</t>
+          <t>NOUVELLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>The NOUVELLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOUVELLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -35520,12 +35520,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>NOVA 7 Pc. Dining Table Set in Silver Black | GOODDEGG</t>
+          <t>NOVA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>The NOVA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOVA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -35666,12 +35666,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>OAKHAM 7 Pc. Dining Table Set (2AC &amp; 4SC) in Weathered Oak | GOODDEGG</t>
+          <t>OAKHAM 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>OAKHAM Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set OAKHAM 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -35812,12 +35812,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>OAKHAM 9 Pc. Dining Table Set (2AC &amp; 6SC) in Weathered Oak | GOODDEGG</t>
+          <t>OAKHAM 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>OAKHAM Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set OAKHAM 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>The OBERWIL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OBERWIL 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -36100,12 +36100,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>ORBETELLO 5 Pc. Counter Height Set in Distressed Natural | GOODDEGG</t>
+          <t>ORBETELLO 5 Pc. Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>The ORBETELLO Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORBETELLO 5 Pc. Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -36239,12 +36239,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>ORBETELLO 5 Pc. Dining Table Set in Transitional | GOODDEGG</t>
+          <t>ORBETELLO 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>The ORBETELLO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORBETELLO 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -36380,12 +36380,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>ORBETELLO 5 Pc. Round Dining Set in Distressed Natural | GOODDEGG</t>
+          <t>ORBETELLO 5 Pc. Round Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>The ORBETELLO Round Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORBETELLO 5 Pc. Round Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>ORBETELLO 7 Pc. Dining Table Set in Distressed Natural | GOODDEGG</t>
+          <t>ORBETELLO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>The ORBETELLO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORBETELLO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -36667,12 +36667,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>ORLA 7 Pc. Dining Table Set in Silver Black | GOODDEGG</t>
+          <t>ORLA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>The ORLA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORLA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -36808,12 +36808,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>PALAZZO 6 Pc. Dining Table Set in Gold Black | GOODDEGG</t>
+          <t>PALAZZO 6 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 6 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -36955,12 +36955,12 @@
       </c>
       <c r="H252" s="15" t="inlineStr">
         <is>
-          <t>PALAZZO 7 Pc. Dining Table Set in Gold Black | GOODDEGG</t>
+          <t>PALAZZO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I252" s="15" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J252" s="15" t="inlineStr">
@@ -37101,12 +37101,12 @@
       </c>
       <c r="H253" s="15" t="inlineStr">
         <is>
-          <t>PALAZZO 7 Pc. Dining Table Set in Gold Silver | GOODDEGG</t>
+          <t>PALAZZO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I253" s="15" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J253" s="15" t="inlineStr">
@@ -37247,12 +37247,12 @@
       </c>
       <c r="H254" s="15" t="inlineStr">
         <is>
-          <t>PALAZZO 7 Pc. Dining Table Set in Chrome Black | GOODDEGG</t>
+          <t>PALAZZO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I254" s="15" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J254" s="15" t="inlineStr">
@@ -37393,12 +37393,12 @@
       </c>
       <c r="H255" s="15" t="inlineStr">
         <is>
-          <t>PALAZZO 7 Pc. Dining Table Set in Chrome Silver | GOODDEGG</t>
+          <t>PALAZZO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I255" s="15" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J255" s="15" t="inlineStr">
@@ -37539,12 +37539,12 @@
       </c>
       <c r="H256" s="15" t="inlineStr">
         <is>
-          <t>PALAZZO 7 Pc. Dining Table Set in Glam | GOODDEGG</t>
+          <t>PALAZZO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I256" s="15" t="inlineStr">
         <is>
-          <t>The PALAZZO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALAZZO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J256" s="15" t="inlineStr">
@@ -37693,7 +37693,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>The PATIENCE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PATIENCE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -37838,7 +37838,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>The PATIENCE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PATIENCE 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -37977,12 +37977,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>PENDOLA 7 Pc. Dining Table Set in Rustic White | GOODDEGG</t>
+          <t>PENDOLA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>The PENDOLA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PENDOLA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -38131,7 +38131,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>PICARDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set PICARDY 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>PICARDY Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set PICARDY 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -38413,12 +38413,12 @@
       </c>
       <c r="H262" s="17" t="inlineStr">
         <is>
-          <t>PORTANOVA 7 Pc. Dining Table Set in Gold Black | GOODDEGG</t>
+          <t>PORTANOVA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I262" s="17" t="inlineStr">
         <is>
-          <t>The PORTANOVA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PORTANOVA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J262" s="17" t="inlineStr">
@@ -38561,12 +38561,12 @@
       </c>
       <c r="H263" s="17" t="inlineStr">
         <is>
-          <t>PORTANOVA 7 Pc. Dining Table Set in Chrome White | GOODDEGG</t>
+          <t>PORTANOVA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I263" s="17" t="inlineStr">
         <is>
-          <t>The PORTANOVA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PORTANOVA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J263" s="17" t="inlineStr">
@@ -38707,12 +38707,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>POTTON 7 Pc. Counter Height Table Set in Gray | GOODDEGG</t>
+          <t>POTTON 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>POTTON Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>POTTON 7 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -38854,12 +38854,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>PROMENADE 7 Pc. Dining Table Set (2AC &amp; 4SC) in Dark Brown | GOODDEGG</t>
+          <t>PROMENADE 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>PROMENADE Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set PROMENADE 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -39001,12 +39001,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>PROMENADE 9 Pc. Dining Table Set (2AC &amp; 6SC) in Dark Brown | GOODDEGG</t>
+          <t>PROMENADE 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>PROMENADE Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set PROMENADE 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -39152,7 +39152,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>RAPIDVIEW Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set RAPIDVIEW 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -39292,12 +39292,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>RAPIDVIEW 7 Pc. Dining Table Set in Walnut Light Gray | GOODDEGG</t>
+          <t>RAPIDVIEW 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>The RAPIDVIEW Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RAPIDVIEW 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -39429,7 +39429,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>The RHEINFALL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RHEINFALL 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -39546,7 +39546,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>The RHEINFALL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RHEINFALL 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="I271" s="19" t="inlineStr">
         <is>
-          <t>RICHFIELD Round Counter Height Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set RICHFIELD 5 Pc. Round Counter supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J271" s="19" t="inlineStr">
@@ -39825,7 +39825,7 @@
       </c>
       <c r="I272" s="19" t="inlineStr">
         <is>
-          <t>RICHFIELD Round Counter Height Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set RICHFIELD 5 Pc. Round Counter supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J272" s="19" t="inlineStr">
@@ -39971,12 +39971,12 @@
       </c>
       <c r="H273" s="21" t="inlineStr">
         <is>
-          <t>RICHFIELD 7 Pc. Dining Table Set in Black Chrome | GOODDEGG</t>
+          <t>RICHFIELD 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I273" s="21" t="inlineStr">
         <is>
-          <t>The RICHFIELD Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICHFIELD 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J273" s="21" t="inlineStr">
@@ -40122,12 +40122,12 @@
       </c>
       <c r="H274" s="21" t="inlineStr">
         <is>
-          <t>RICHFIELD 7 Pc. Dining Table Set in Silver Chrome | GOODDEGG</t>
+          <t>RICHFIELD 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I274" s="21" t="inlineStr">
         <is>
-          <t>The RICHFIELD Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICHFIELD 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J274" s="21" t="inlineStr">
@@ -40268,12 +40268,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>ROWAN 5 Pc. Dining Table Set in Cherry | GOODDEGG</t>
+          <t>ROWAN 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>The ROWAN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROWAN 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -40413,12 +40413,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>ROXO 5 Pc. Dining Table Set in Silver Black | GOODDEGG</t>
+          <t>ROXO 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>The ROXO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROXO 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>SABRINA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SABRINA 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -40702,7 +40702,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>SABRINA Counter Height Table w/ Stools makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SABRINA 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SABRINA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SABRINA 9 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -40986,7 +40986,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SABRINA Counter Height Table w/ Stools makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SABRINA 9 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -41124,12 +41124,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Rect Counter Height Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Rect Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>The SABRO Rect Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Rect Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -41267,12 +41267,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Rect Dining Table Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Rect Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>The SABRO Rect Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Rect Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -41410,12 +41410,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Round Counter Height Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Round Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>The SABRO Round Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Round Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -41553,12 +41553,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Round Dining Table Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Round Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>The SABRO Round Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Round Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -41696,12 +41696,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Square Counter Height Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Square Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>SABRO Square Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Square Counter Height Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -41839,12 +41839,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>SABRO 5 Pc. Square Dining Table Set in Black White | GOODDEGG</t>
+          <t>SABRO 5 Pc. Square Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>The SABRO Square Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 5 Pc. Square Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -41982,12 +41982,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>SABRO 7 Pc. Rect Dining Table Set in Black White | GOODDEGG</t>
+          <t>SABRO 7 Pc. Rect Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>The SABRO Rect Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABRO 7 Pc. Rect Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -42127,12 +42127,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>SAN ANTONIO 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>SAN ANTONIO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>The SAN ANTONIO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAN ANTONIO 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>SANIA Counter Height Table w/ Bench makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SANIA 4 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -42430,7 +42430,7 @@
       </c>
       <c r="I290" s="25" t="inlineStr">
         <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J290" s="25" t="inlineStr">
@@ -42583,7 +42583,7 @@
       </c>
       <c r="I291" s="25" t="inlineStr">
         <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J291" s="25" t="inlineStr">
@@ -42736,7 +42736,7 @@
       </c>
       <c r="I292" s="25" t="inlineStr">
         <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J292" s="25" t="inlineStr">
@@ -42884,12 +42884,12 @@
       </c>
       <c r="H293" s="25" t="inlineStr">
         <is>
-          <t>SANIA 5 Pc. Counter Height Table Set in Rustic Oak | GOODDEGG</t>
+          <t>SANIA 5 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I293" s="25" t="inlineStr">
         <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J293" s="25" t="inlineStr">
@@ -43040,12 +43040,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>SANIA 6 Pc. Dining Table Set w/ 3 Seater Bench | GOODDEGG</t>
+          <t>SANIA 6 Pc. Dining Table Set w/ 3 | GOODDEGG</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table w/ makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 6 Pc. Dining Table Set w/ 3 Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -43191,7 +43191,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>The SANIA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -43332,12 +43332,12 @@
       </c>
       <c r="H296" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I296" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J296" s="27" t="inlineStr">
@@ -43482,12 +43482,12 @@
       </c>
       <c r="H297" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I297" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J297" s="27" t="inlineStr">
@@ -43632,12 +43632,12 @@
       </c>
       <c r="H298" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I298" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J298" s="27" t="inlineStr">
@@ -43782,12 +43782,12 @@
       </c>
       <c r="H299" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I299" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J299" s="27" t="inlineStr">
@@ -43932,12 +43932,12 @@
       </c>
       <c r="H300" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I300" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J300" s="27" t="inlineStr">
@@ -44082,12 +44082,12 @@
       </c>
       <c r="H301" s="27" t="inlineStr">
         <is>
-          <t>SANIA 7 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>SANIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I301" s="27" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J301" s="27" t="inlineStr">
@@ -44232,12 +44232,12 @@
       </c>
       <c r="H302" s="29" t="inlineStr">
         <is>
-          <t>SANIA 9 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I302" s="29" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J302" s="29" t="inlineStr">
@@ -44382,12 +44382,12 @@
       </c>
       <c r="H303" s="29" t="inlineStr">
         <is>
-          <t>SANIA 9 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>SANIA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I303" s="29" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J303" s="29" t="inlineStr">
@@ -44532,12 +44532,12 @@
       </c>
       <c r="H304" s="29" t="inlineStr">
         <is>
-          <t>SANIA 9 Pc. Dining Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I304" s="29" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J304" s="29" t="inlineStr">
@@ -44682,12 +44682,12 @@
       </c>
       <c r="H305" s="29" t="inlineStr">
         <is>
-          <t>SANIA 9 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>SANIA 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I305" s="29" t="inlineStr">
         <is>
-          <t>The SANIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 9 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J305" s="29" t="inlineStr">
@@ -44837,7 +44837,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>SANIA III Sq Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SANIA III 7 Pc. Sq Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -44983,12 +44983,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>SANIA Table and 4 Chairs and 2 Seater Bench | GOODDEGG</t>
+          <t>SANIA Table and 4 Chairs and 2 | GOODDEGG</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>The SANIA Table and Chairs and makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA Table and 4 Chairs and 2 Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -45122,12 +45122,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>SASKIA 7 Pc. Dining Table Set in Gray | GOODDEGG</t>
+          <t>SASKIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>The SASKIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SASKIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -45260,7 +45260,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>The SILVERIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVERIA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -45378,7 +45378,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>The SILVERIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVERIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -45497,7 +45497,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>The SILVESTRI Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVESTRI 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -45616,7 +45616,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>The SILVESTRI Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVESTRI 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -45739,12 +45739,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>SKIEN 5 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>SKIEN 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>The SKIEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SKIEN 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>The ST GALLEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ST GALLEN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
@@ -46028,12 +46028,12 @@
       </c>
       <c r="H315" s="31" t="inlineStr">
         <is>
-          <t>STACIE 5 PC. Dining Table Set in Gray | GOODDEGG</t>
+          <t>STACIE 5 PC. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I315" s="31" t="inlineStr">
         <is>
-          <t>The STACIE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STACIE 5 PC. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J315" s="31" t="inlineStr">
@@ -46177,12 +46177,12 @@
       </c>
       <c r="H316" s="31" t="inlineStr">
         <is>
-          <t>STACIE 5 PC. Dining Table Set in White Gray | GOODDEGG</t>
+          <t>STACIE 5 PC. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I316" s="31" t="inlineStr">
         <is>
-          <t>The STACIE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STACIE 5 PC. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J316" s="31" t="inlineStr">
@@ -46325,12 +46325,12 @@
       </c>
       <c r="H317" s="33" t="inlineStr">
         <is>
-          <t>STACIE 7 PC. Dining Table Set in Gray | GOODDEGG</t>
+          <t>STACIE 7 PC. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I317" s="33" t="inlineStr">
         <is>
-          <t>The STACIE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STACIE 7 PC. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J317" s="33" t="inlineStr">
@@ -46469,12 +46469,12 @@
       </c>
       <c r="H318" s="33" t="inlineStr">
         <is>
-          <t>STACIE 7 PC. Dining Table Set in White Gray | GOODDEGG</t>
+          <t>STACIE 7 PC. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I318" s="33" t="inlineStr">
         <is>
-          <t>The STACIE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STACIE 7 PC. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J318" s="33" t="inlineStr">
@@ -46611,12 +46611,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>STELLA MIA 7 Pc. Dining Table Set (2AC and 4SC) in Ivory | GOODDEGG</t>
+          <t>STELLA MIA 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>STELLA MIA Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set STELLA MIA 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -46757,12 +46757,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>STELLA MIA 9 Pc. Dining Table Set (2AC and 6SC) in Ivory | GOODDEGG</t>
+          <t>STELLA MIA 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>STELLA MIA Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set STELLA MIA 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -46898,12 +46898,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>STROM 5 Pc. Counter Height Table Set in Dark Walnut | GOODDEGG</t>
+          <t>STROM 5 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>The STROM Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STROM 5 Pc. Counter Height Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -47041,12 +47041,12 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>SUTTON 5 Pc. Dining Table Set in Antique White | GOODDEGG</t>
+          <t>SUTTON 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>The SUTTON Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SUTTON 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>SYLVANA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SYLVANA 7 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -47342,7 +47342,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>SYLVANA Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set SYLVANA 9 Pc. Dining Table Set (2AC supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -47479,12 +47479,12 @@
       </c>
       <c r="H325" s="35" t="inlineStr">
         <is>
-          <t>TOTTENHAM 5 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>TOTTENHAM 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I325" s="35" t="inlineStr">
         <is>
-          <t>The TOTTENHAM Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TOTTENHAM 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J325" s="35" t="inlineStr">
@@ -47625,12 +47625,12 @@
       </c>
       <c r="H326" s="35" t="inlineStr">
         <is>
-          <t>TOTTENHAM 5 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>TOTTENHAM 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I326" s="35" t="inlineStr">
         <is>
-          <t>The TOTTENHAM Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TOTTENHAM 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J326" s="35" t="inlineStr">
@@ -47772,12 +47772,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>TOTTENHAM 7 Pc. Dining Table Set (2AC and 4SC) in Black | GOODDEGG</t>
+          <t>TOTTENHAM 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>TOTTENHAM Dining Table makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set TOTTENHAM 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
@@ -47914,12 +47914,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>TOWNSVILLE 5 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>TOWNSVILLE 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>The TOWNSVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TOWNSVILLE 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -48056,12 +48056,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>TOWNSVILLE 7 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>TOWNSVILLE 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>The TOWNSVILLE Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TOWNSVILLE 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -48201,12 +48201,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>UMBRIA 7 Pc. Dining Table Set in Antique Black Gray | GOODDEGG</t>
+          <t>UMBRIA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>The UMBRIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>UMBRIA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
@@ -48350,7 +48350,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>UPMINSTER Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set UPMINSTER 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
@@ -48488,12 +48488,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>UPMINSTER 7 Pc. Dining Table Set in Natural Tone Beige | GOODDEGG</t>
+          <t>UPMINSTER 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>The UPMINSTER Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>UPMINSTER 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -48628,12 +48628,12 @@
       </c>
       <c r="H333" s="37" t="inlineStr">
         <is>
-          <t>UZWIL 7 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>UZWIL 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I333" s="37" t="inlineStr">
         <is>
-          <t>The UZWIL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>UZWIL 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J333" s="37" t="inlineStr">
@@ -48772,12 +48772,12 @@
       </c>
       <c r="H334" s="37" t="inlineStr">
         <is>
-          <t>UZWIL 7 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>UZWIL 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I334" s="37" t="inlineStr">
         <is>
-          <t>The UZWIL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>UZWIL 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J334" s="37" t="inlineStr">
@@ -48923,12 +48923,12 @@
       </c>
       <c r="H335" s="39" t="inlineStr">
         <is>
-          <t>VALDEVERS 7 Pc. Dining Table Set in Chrome Black | GOODDEGG</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I335" s="39" t="inlineStr">
         <is>
-          <t>The VALDEVERS Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J335" s="39" t="inlineStr">
@@ -49078,12 +49078,12 @@
       </c>
       <c r="H336" s="39" t="inlineStr">
         <is>
-          <t>VALDEVERS 7 Pc. Dining Table Set in Chrome Gray | GOODDEGG</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I336" s="39" t="inlineStr">
         <is>
-          <t>The VALDEVERS Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J336" s="39" t="inlineStr">
@@ -49233,12 +49233,12 @@
       </c>
       <c r="H337" s="39" t="inlineStr">
         <is>
-          <t>VALDEVERS 7 Pc. Dining Table Set in Chrome Navy | GOODDEGG</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I337" s="39" t="inlineStr">
         <is>
-          <t>The VALDEVERS Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALDEVERS 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J337" s="39" t="inlineStr">
@@ -49387,12 +49387,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>VALO 5 Pc. Dining Table Set in Silver Black | GOODDEGG</t>
+          <t>VALO 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>The VALO Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALO 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -49531,12 +49531,12 @@
       </c>
       <c r="H339" s="41" t="inlineStr">
         <is>
-          <t>VARDE 5 Pc. Round Dining Set in Black White | GOODDEGG</t>
+          <t>VARDE 5 Pc. Round Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I339" s="41" t="inlineStr">
         <is>
-          <t>The VARDE Round Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VARDE 5 Pc. Round Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J339" s="41" t="inlineStr">
@@ -49679,12 +49679,12 @@
       </c>
       <c r="H340" s="41" t="inlineStr">
         <is>
-          <t>VARDE 5 Pc. Round Dining Set in Black White | GOODDEGG</t>
+          <t>VARDE 5 Pc. Round Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I340" s="41" t="inlineStr">
         <is>
-          <t>The VARDE Round Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VARDE 5 Pc. Round Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J340" s="41" t="inlineStr">
@@ -49824,12 +49824,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>VIKEN 5 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>VIKEN 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>The VIKEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIKEN 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
@@ -49965,12 +49965,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>VIKEN 7 Pc. Dining Table Set in Walnut | GOODDEGG</t>
+          <t>VIKEN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>The VIKEN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIKEN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
@@ -50110,12 +50110,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>WADENSWIL 7 Pc. Dining Table Set in Chrome | GOODDEGG</t>
+          <t>WADENSWIL 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>The WADENSWIL Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WADENSWIL 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -50253,12 +50253,12 @@
       </c>
       <c r="H344" s="13" t="inlineStr">
         <is>
-          <t>WAILOA 7 Pc. Dining Table Set in Black | GOODDEGG</t>
+          <t>WAILOA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I344" s="13" t="inlineStr">
         <is>
-          <t>The WAILOA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WAILOA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J344" s="13" t="inlineStr">
@@ -50400,12 +50400,12 @@
       </c>
       <c r="H345" s="13" t="inlineStr">
         <is>
-          <t>WAILOA 7 Pc. Dining Table Set in White | GOODDEGG</t>
+          <t>WAILOA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I345" s="13" t="inlineStr">
         <is>
-          <t>The WAILOA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WAILOA 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J345" s="13" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>The WESTERHAM Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WESTERHAM 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -50671,7 +50671,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>WHITEHALL Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WHITEHALL 3 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -50820,7 +50820,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>WHITEHALL Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WHITEHALL 5 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -50966,7 +50966,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>WICHITA Counter Height Table w/ Bench makes it easy to furnish the room with a. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WICHITA 6 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -51111,7 +51111,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>WICHITA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WICHITA 7 Pc. Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -51249,12 +51249,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>WOODSIDE 6 Pc. Dining Table Set w/ Bench in Dark Cherry | GOODDEGG</t>
+          <t>WOODSIDE 6 Pc. Dining Table Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>WOODSIDE Dining Table w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WOODSIDE 6 Pc. Dining Table Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -51391,12 +51391,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>WOODSIDE 7 Pc. Dining Table Set (2AC &amp; 4SC) in Dark Cherry | GOODDEGG</t>
+          <t>WOODSIDE 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>WOODSIDE Dining Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Dining Set WOODSIDE 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -51534,12 +51534,12 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>WOOLWICH 7 Pc. Dining Table Set in Dark Walnut | GOODDEGG</t>
+          <t>WOOLWICH 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>The WOOLWICH Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WOOLWICH 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -51678,12 +51678,12 @@
       </c>
       <c r="H354" s="15" t="inlineStr">
         <is>
-          <t>YATE 5 Pc. Dining Set in Black | GOODDEGG</t>
+          <t>YATE 5 Pc. Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I354" s="15" t="inlineStr">
         <is>
-          <t>The YATE Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YATE 5 Pc. Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J354" s="15" t="inlineStr">
@@ -51826,12 +51826,12 @@
       </c>
       <c r="H355" s="15" t="inlineStr">
         <is>
-          <t>YATE 5 Pc. Dining Set in Natural Oak | GOODDEGG</t>
+          <t>YATE 5 Pc. Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I355" s="15" t="inlineStr">
         <is>
-          <t>The YATE Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YATE 5 Pc. Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J355" s="15" t="inlineStr">
@@ -51978,12 +51978,12 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>YELENA 5 Pc. Dining Table Set in Gray Black | GOODDEGG</t>
+          <t>YELENA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>The YELENA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YELENA 5 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -52121,12 +52121,12 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>ZAIN 7 Pc. Dining Table Set in White Chrome | GOODDEGG</t>
+          <t>ZAIN 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>The ZAIN Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZAIN 7 Pc. Dining Table Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -52267,12 +52267,12 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>ANAYA 7 Pc. Counter Height Table Set in Gray Light Gray | GOODDEG</t>
+          <t>ANAYA 7 Pc. Counter Height Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>The ANAYA Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Counter Ht. Set ANAYA 7 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -52419,7 +52419,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>DAKOTA Round Counter Height Table makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Counter Ht. Set DAKOTA 5 Pc. Round Counter supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -52558,7 +52558,7 @@
       </c>
       <c r="I360" s="23" t="inlineStr">
         <is>
-          <t>EBIKON Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Counter Ht. Set EBIKON 5 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J360" s="23" t="inlineStr">
@@ -52682,7 +52682,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>KLAMATH Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Counter Ht. Set KLAMATH 5 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -52799,7 +52799,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>STREATHAM Counter Height Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Counter Ht. Set STREATHAM 3 Pc. Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -52922,12 +52922,12 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>BELLAGIO 5 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 5 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -53067,12 +53067,12 @@
       </c>
       <c r="H364" s="41" t="inlineStr">
         <is>
-          <t>BELLAGIO 7 Pc. Dining Table Set in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I364" s="41" t="inlineStr">
         <is>
-          <t>The BELLAGIO Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J364" s="41" t="inlineStr">
@@ -53216,12 +53216,12 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>BELLAGIO 7 Pc. Dining Table Set (2AC &amp; 4SC) in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set (2AC and 4SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>BELLAGIO Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 7 Pc. Dining Table Set (2AC and 4SC) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -53361,12 +53361,12 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>BELLAGIO 9 Pc. Dining Table Set (2AC &amp; 6SC) in Brown Cherry | GOODDEGG</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set (2AC and 6SC) | GOODDEGG</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>BELLAGIO Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLAGIO 9 Pc. Dining Table Set (2AC and 6SC) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -53505,12 +53505,12 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>CLEMENTS 7 Pc. Dining Table Set in Oak | GOODDEGG</t>
+          <t>CLEMENTS 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>The CLEMENTS Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLEMENTS 7 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -53649,12 +53649,12 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>CLEMENTS 9 Pc. Dining Table Set in Oak | GOODDEGG</t>
+          <t>CLEMENTS 9 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>The CLEMENTS Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLEMENTS 9 Pc. Dining Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -53797,12 +53797,12 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>ESDARGO 3 Pc. Bar Table Set in Black Distressed Dark Oak | GOODDE</t>
+          <t>ESDARGO 3 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>The ESDARGO Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESDARGO 3 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -53941,12 +53941,12 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>FOSKEY 3 Pc. Bar Table Set in Antique Black, Natural Tone | GOODDEGG</t>
+          <t>FOSKEY 3 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>The FOSKEY Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FOSKEY 3 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -54089,12 +54089,12 @@
       </c>
       <c r="H371" s="23" t="inlineStr">
         <is>
-          <t>SANIA 5 Pc. Bar Table Set in Antique Black Ivory | GOODDEGG</t>
+          <t>SANIA 5 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I371" s="23" t="inlineStr">
         <is>
-          <t>The SANIA Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J371" s="23" t="inlineStr">
@@ -54245,12 +54245,12 @@
       </c>
       <c r="H372" s="23" t="inlineStr">
         <is>
-          <t>SANIA 5 Pc. Bar Table Set in Rustic Oak | GOODDEGG</t>
+          <t>SANIA 5 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I372" s="23" t="inlineStr">
         <is>
-          <t>The SANIA Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANIA 5 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J372" s="23" t="inlineStr">
